--- a/grodent-magnenat-mini-projet-trey/input-data/load_curve/power_profile_cabinet_summer_weekend.xlsx
+++ b/grodent-magnenat-mini-projet-trey/input-data/load_curve/power_profile_cabinet_summer_weekend.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cleme\Documents\heig-vd\s5\ResoHT\mini_projet_trey\courbe de charge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C92CF67-2B06-4286-A150-016432C5EE1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C6AB29-C89A-41DF-B0A1-B342EB213D27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{5FC146A3-AC37-46DC-AD92-E888F69598AC}"/>
   </bookViews>
@@ -634,76 +634,76 @@
         <v>0</v>
       </c>
       <c r="B3">
-        <v>9325.9297852479103</v>
+        <v>9.3259297852479097</v>
       </c>
       <c r="C3">
-        <v>3065.28488642511</v>
+        <v>3.0652848864251099</v>
       </c>
       <c r="D3">
-        <v>13195.206680531301</v>
+        <v>13.1952066805313</v>
       </c>
       <c r="E3">
-        <v>4337.0547004405998</v>
+        <v>4.3370547004405999</v>
       </c>
       <c r="F3">
-        <v>1643.9758161484201</v>
+        <v>1.6439758161484199</v>
       </c>
       <c r="G3">
-        <v>540.34872006643604</v>
+        <v>0.54034872006643597</v>
       </c>
       <c r="H3">
-        <v>6402.1797595190301</v>
+        <v>6.4021797595190302</v>
       </c>
       <c r="I3">
-        <v>2104.2947254517399</v>
+        <v>2.1042947254517399</v>
       </c>
       <c r="J3">
-        <v>2848.8044488977898</v>
+        <v>2.8488044488977899</v>
       </c>
       <c r="K3">
-        <v>936.35674111553601</v>
+        <v>0.93635674111553602</v>
       </c>
       <c r="L3">
-        <v>10247.664273547</v>
+        <v>10.247664273547</v>
       </c>
       <c r="M3">
-        <v>3368.2443619242299</v>
+        <v>3.3682443619242299</v>
       </c>
       <c r="N3">
-        <v>14423.3768957915</v>
+        <v>14.423376895791501</v>
       </c>
       <c r="O3">
-        <v>4740.7347286507402</v>
+        <v>4.7407347286507404</v>
       </c>
       <c r="P3">
-        <v>8481.2485971943897</v>
+        <v>8.4812485971943907</v>
       </c>
       <c r="Q3">
-        <v>2787.6516059683199</v>
+        <v>2.7876516059683198</v>
       </c>
       <c r="R3">
-        <v>639.37548387096695</v>
+        <v>0.63937548387096699</v>
       </c>
       <c r="S3">
-        <v>210.152558789431</v>
+        <v>0.21015255878943101</v>
       </c>
       <c r="T3">
-        <v>5848.1170160320598</v>
+        <v>5.8481170160320604</v>
       </c>
       <c r="U3">
-        <v>1922.18310839578</v>
+        <v>1.9221831083957801</v>
       </c>
       <c r="V3">
-        <v>1561.31612903225</v>
+        <v>1.5613161290322499</v>
       </c>
       <c r="W3">
-        <v>513.17979477229403</v>
+        <v>0.51317979477229403</v>
       </c>
       <c r="X3">
-        <v>1780.68709677419</v>
+        <v>1.7806870967741899</v>
       </c>
       <c r="Y3">
-        <v>585.28354500677301</v>
+        <v>0.58528354500677304</v>
       </c>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4"/>
@@ -758,76 +758,76 @@
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="B4">
-        <v>8732.3885889844205</v>
+        <v>8.7323885889844206</v>
       </c>
       <c r="C4">
-        <v>2870.1973294444601</v>
+        <v>2.8701973294444598</v>
       </c>
       <c r="D4">
-        <v>12461.342332292101</v>
+        <v>12.4613423322921</v>
       </c>
       <c r="E4">
-        <v>4095.8451538169302</v>
+        <v>4.0958451538169296</v>
       </c>
       <c r="F4">
-        <v>1588.7655272642</v>
+        <v>1.5887655272642001</v>
       </c>
       <c r="G4">
-        <v>522.20197566785998</v>
+        <v>0.52220197566785997</v>
       </c>
       <c r="H4">
-        <v>5980.76192384769</v>
+        <v>5.9807619238476901</v>
       </c>
       <c r="I4">
-        <v>1965.78138122769</v>
+        <v>1.9657813812276901</v>
       </c>
       <c r="J4">
-        <v>2661.2844088176298</v>
+        <v>2.6612844088176302</v>
       </c>
       <c r="K4">
-        <v>874.72188453868398</v>
+        <v>0.87472188453868405</v>
       </c>
       <c r="L4">
-        <v>9573.1208116232392</v>
+        <v>9.5731208116232391</v>
       </c>
       <c r="M4">
-        <v>3146.5326477375302</v>
+        <v>3.1465326477375299</v>
       </c>
       <c r="N4">
-        <v>13473.970833667299</v>
+        <v>13.4739708336673</v>
       </c>
       <c r="O4">
-        <v>4428.6800466700397</v>
+        <v>4.4286800466700402</v>
       </c>
       <c r="P4">
-        <v>7922.9778891115502</v>
+        <v>7.9229778891115501</v>
       </c>
       <c r="Q4">
-        <v>2604.1568978345499</v>
+        <v>2.60415689783455</v>
       </c>
       <c r="R4">
-        <v>631.38329032258002</v>
+        <v>0.63138329032258</v>
       </c>
       <c r="S4">
-        <v>207.52565180456301</v>
+        <v>0.207525651804563</v>
       </c>
       <c r="T4">
-        <v>5463.1698717434801</v>
+        <v>5.4631698717434798</v>
       </c>
       <c r="U4">
-        <v>1795.6571007341299</v>
+        <v>1.79565710073413</v>
       </c>
       <c r="V4">
-        <v>1541.79967741935</v>
+        <v>1.5417996774193501</v>
       </c>
       <c r="W4">
-        <v>506.76504733764</v>
+        <v>0.50676504733764005</v>
       </c>
       <c r="X4">
-        <v>1758.42850806451</v>
+        <v>1.7584285080645099</v>
       </c>
       <c r="Y4">
-        <v>577.96750069418795</v>
+        <v>0.57796750069418801</v>
       </c>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
@@ -882,76 +882,76 @@
         <v>2.0833333333333301E-2</v>
       </c>
       <c r="B5">
-        <v>8220.6228837998497</v>
+        <v>8.2206228837998498</v>
       </c>
       <c r="C5">
-        <v>2701.9880765746402</v>
+        <v>2.70198807657464</v>
       </c>
       <c r="D5">
-        <v>11832.834067769199</v>
+        <v>11.8328340677692</v>
       </c>
       <c r="E5">
-        <v>3889.2644772947001</v>
+        <v>3.8892644772947</v>
       </c>
       <c r="F5">
-        <v>1543.81147524888</v>
+        <v>1.5438114752488801</v>
       </c>
       <c r="G5">
-        <v>507.42629330704</v>
+        <v>0.50742629330704003</v>
       </c>
       <c r="H5">
-        <v>5616.65691382765</v>
+        <v>5.6166569138276499</v>
       </c>
       <c r="I5">
-        <v>1846.1058518181101</v>
+        <v>1.8461058518181099</v>
       </c>
       <c r="J5">
-        <v>2499.2670941883698</v>
+        <v>2.4992670941883701</v>
       </c>
       <c r="K5">
-        <v>821.46936845628397</v>
+        <v>0.82146936845628404</v>
       </c>
       <c r="L5">
-        <v>8990.3152605210398</v>
+        <v>8.9903152605210401</v>
       </c>
       <c r="M5">
-        <v>2954.9737266802299</v>
+        <v>2.9549737266802301</v>
       </c>
       <c r="N5">
-        <v>12653.6839959919</v>
+        <v>12.6536839959919</v>
       </c>
       <c r="O5">
-        <v>4159.0648014387198</v>
+        <v>4.1590648014387197</v>
       </c>
       <c r="P5">
-        <v>7440.6319973279897</v>
+        <v>7.4406319973279897</v>
       </c>
       <c r="Q5">
-        <v>2445.61747000696</v>
+        <v>2.4456174700069599</v>
       </c>
       <c r="R5">
-        <v>626.24545161290303</v>
+        <v>0.62624545161290301</v>
       </c>
       <c r="S5">
-        <v>205.83692588572001</v>
+        <v>0.20583692588572</v>
       </c>
       <c r="T5">
-        <v>5130.5755390781496</v>
+        <v>5.1305755390781496</v>
       </c>
       <c r="U5">
-        <v>1686.3386301144601</v>
+        <v>1.6863386301144601</v>
       </c>
       <c r="V5">
-        <v>1529.25338709677</v>
+        <v>1.5292533870967699</v>
       </c>
       <c r="W5">
-        <v>502.64128112964801</v>
+        <v>0.50264128112964801</v>
       </c>
       <c r="X5">
-        <v>1744.1194153225799</v>
+        <v>1.7441194153225801</v>
       </c>
       <c r="Y5">
-        <v>573.26432935038395</v>
+        <v>0.57326432935038396</v>
       </c>
       <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
@@ -1006,76 +1006,76 @@
         <v>3.125E-2</v>
       </c>
       <c r="B6">
-        <v>7741.4882062512097</v>
+        <v>7.7414882062512103</v>
       </c>
       <c r="C6">
-        <v>2544.5041238243998</v>
+        <v>2.5445041238243999</v>
       </c>
       <c r="D6">
-        <v>11234.5943063138</v>
+        <v>11.234594306313801</v>
       </c>
       <c r="E6">
-        <v>3692.6325766183099</v>
+        <v>3.6926325766183101</v>
       </c>
       <c r="F6">
-        <v>1500.36593537882</v>
+        <v>1.5003659353788199</v>
       </c>
       <c r="G6">
-        <v>493.14643491083598</v>
+        <v>0.49314643491083598</v>
       </c>
       <c r="H6">
-        <v>5276.1513026052098</v>
+        <v>5.2761513026052098</v>
       </c>
       <c r="I6">
-        <v>1734.1870696850799</v>
+        <v>1.7341870696850801</v>
       </c>
       <c r="J6">
-        <v>2347.7509018035998</v>
+        <v>2.3477509018035998</v>
       </c>
       <c r="K6">
-        <v>771.66840434218705</v>
+        <v>0.77166840434218698</v>
       </c>
       <c r="L6">
-        <v>8445.2841432865698</v>
+        <v>8.4452841432865693</v>
       </c>
       <c r="M6">
-        <v>2775.83066161738</v>
+        <v>2.77583066161738</v>
       </c>
       <c r="N6">
-        <v>11886.5638977955</v>
+        <v>11.886563897795501</v>
       </c>
       <c r="O6">
-        <v>3906.92461839832</v>
+        <v>3.9069246183983202</v>
       </c>
       <c r="P6">
-        <v>6989.5492651970599</v>
+        <v>6.9895492651970601</v>
       </c>
       <c r="Q6">
-        <v>2297.3537458348701</v>
+        <v>2.2973537458348701</v>
       </c>
       <c r="R6">
-        <v>620.53674193548397</v>
+        <v>0.62053674193548403</v>
       </c>
       <c r="S6">
-        <v>203.96056375367101</v>
+        <v>0.203960563753671</v>
       </c>
       <c r="T6">
-        <v>4819.5382464929799</v>
+        <v>4.8195382464929803</v>
       </c>
       <c r="U6">
-        <v>1584.1056159238501</v>
+        <v>1.58410561592385</v>
       </c>
       <c r="V6">
-        <v>1515.31306451612</v>
+        <v>1.5153130645161199</v>
       </c>
       <c r="W6">
-        <v>498.05931867632398</v>
+        <v>0.49805931867632403</v>
       </c>
       <c r="X6">
-        <v>1728.22042338709</v>
+        <v>1.7282204233870899</v>
       </c>
       <c r="Y6">
-        <v>568.03858341282398</v>
+        <v>0.56803858341282398</v>
       </c>
       <c r="Z6" s="4"/>
       <c r="AA6" s="4"/>
@@ -1130,76 +1130,76 @@
         <v>4.1666666666666699E-2</v>
       </c>
       <c r="B7">
-        <v>7231.3690764432004</v>
+        <v>7.2313690764432099</v>
       </c>
       <c r="C7">
-        <v>2376.83607410883</v>
+        <v>2.3768360741088301</v>
       </c>
       <c r="D7">
-        <v>10579.296540270499</v>
+        <v>10.5792965402705</v>
       </c>
       <c r="E7">
-        <v>3477.2466167606499</v>
+        <v>3.4772466167606502</v>
       </c>
       <c r="F7">
-        <v>1447.76684938425</v>
+        <v>1.4477668493842499</v>
       </c>
       <c r="G7">
-        <v>475.85795139748399</v>
+        <v>0.47585795139748499</v>
       </c>
       <c r="H7">
-        <v>4915.4176352705399</v>
+        <v>4.9154176352705399</v>
       </c>
       <c r="I7">
-        <v>1615.6196470293</v>
+        <v>1.6156196470293001</v>
       </c>
       <c r="J7">
-        <v>2187.23374749499</v>
+        <v>2.1872337474949899</v>
       </c>
       <c r="K7">
-        <v>718.90896711240202</v>
+        <v>0.71890896711240204</v>
       </c>
       <c r="L7">
-        <v>7867.8749398797599</v>
+        <v>7.8678749398797603</v>
       </c>
       <c r="M7">
-        <v>2586.0454342735802</v>
+        <v>2.5860454342735801</v>
       </c>
       <c r="N7">
-        <v>11073.872308617199</v>
+        <v>11.073872308617201</v>
       </c>
       <c r="O7">
-        <v>3639.80581062284</v>
+        <v>3.6398058106228399</v>
       </c>
       <c r="P7">
-        <v>6511.6695390781497</v>
+        <v>6.5116695390781496</v>
       </c>
       <c r="Q7">
-        <v>2140.2822756723599</v>
+        <v>2.1402822756723601</v>
       </c>
       <c r="R7">
-        <v>610.26106451612895</v>
+        <v>0.61026106451612905</v>
       </c>
       <c r="S7">
-        <v>200.58311191598401</v>
+        <v>0.20058311191598399</v>
       </c>
       <c r="T7">
-        <v>4490.0234909819601</v>
+        <v>4.4900234909819599</v>
       </c>
       <c r="U7">
-        <v>1475.7993533654801</v>
+        <v>1.4757993533654801</v>
       </c>
       <c r="V7">
-        <v>1490.2204838709599</v>
+        <v>1.4902204838709601</v>
       </c>
       <c r="W7">
-        <v>489.81178626034102</v>
+        <v>0.489811786260341</v>
       </c>
       <c r="X7">
-        <v>1699.6022379032199</v>
+        <v>1.6996022379032201</v>
       </c>
       <c r="Y7">
-        <v>558.63224072521496</v>
+        <v>0.558632240725215</v>
       </c>
       <c r="Z7" s="4"/>
       <c r="AA7" s="4"/>
@@ -1254,76 +1254,76 @@
         <v>5.2083333333333301E-2</v>
       </c>
       <c r="B8">
-        <v>6729.64914577542</v>
+        <v>6.7296491457754204</v>
       </c>
       <c r="C8">
-        <v>2211.92870764689</v>
+        <v>2.2119287076468899</v>
       </c>
       <c r="D8">
-        <v>9916.5056582792204</v>
+        <v>9.9165056582792204</v>
       </c>
       <c r="E8">
-        <v>3259.3977887926399</v>
+        <v>3.25939778879264</v>
       </c>
       <c r="F8">
-        <v>1393.18989301183</v>
+        <v>1.39318989301183</v>
       </c>
       <c r="G8">
-        <v>457.91937332882901</v>
+        <v>0.45791937332882898</v>
       </c>
       <c r="H8">
-        <v>4561.4266533066102</v>
+        <v>4.5614266533066097</v>
       </c>
       <c r="I8">
-        <v>1499.2684378811</v>
+        <v>1.4992684378811001</v>
       </c>
       <c r="J8">
-        <v>2029.7169138276499</v>
+        <v>2.0297169138276501</v>
       </c>
       <c r="K8">
-        <v>667.13568758784595</v>
+        <v>0.66713568758784603</v>
       </c>
       <c r="L8">
-        <v>7301.25843186372</v>
+        <v>7.3012584318637197</v>
       </c>
       <c r="M8">
-        <v>2399.8075943567501</v>
+        <v>2.3998075943567501</v>
       </c>
       <c r="N8">
-        <v>10276.371216432801</v>
+        <v>10.2763712164328</v>
       </c>
       <c r="O8">
-        <v>3377.6798777590602</v>
+        <v>3.3776798777590602</v>
       </c>
       <c r="P8">
-        <v>6042.7221442885702</v>
+        <v>6.0427221442885699</v>
       </c>
       <c r="Q8">
-        <v>1986.1467208399899</v>
+        <v>1.9861467208399901</v>
       </c>
       <c r="R8">
-        <v>598.272774193548</v>
+        <v>0.59827277419354796</v>
       </c>
       <c r="S8">
-        <v>196.64275143868201</v>
+        <v>0.19664275143868201</v>
       </c>
       <c r="T8">
-        <v>4166.66788977955</v>
+        <v>4.1666678897795499</v>
       </c>
       <c r="U8">
-        <v>1369.5175069296899</v>
+        <v>1.3695175069296901</v>
       </c>
       <c r="V8">
-        <v>1460.94580645161</v>
+        <v>1.4609458064516101</v>
       </c>
       <c r="W8">
-        <v>480.189665108361</v>
+        <v>0.48018966510836097</v>
       </c>
       <c r="X8">
-        <v>1666.2143548387</v>
+        <v>1.6662143548387001</v>
       </c>
       <c r="Y8">
-        <v>547.65817425633804</v>
+        <v>0.547658174256338</v>
       </c>
       <c r="Z8" s="4"/>
       <c r="AA8" s="4"/>
@@ -1378,76 +1378,76 @@
         <v>6.25E-2</v>
       </c>
       <c r="B9">
-        <v>6261.58145242097</v>
+        <v>6.2615814524209696</v>
       </c>
       <c r="C9">
-        <v>2058.0822966935498</v>
+        <v>2.0580822966935499</v>
       </c>
       <c r="D9">
-        <v>9286.8654030384805</v>
+        <v>9.2868654030384796</v>
       </c>
       <c r="E9">
-        <v>3052.44504491424</v>
+        <v>3.05244504491424</v>
       </c>
       <c r="F9">
-        <v>1342.7838883007901</v>
+        <v>1.3427838883007901</v>
       </c>
       <c r="G9">
-        <v>441.35172077474101</v>
+        <v>0.441351720774741</v>
       </c>
       <c r="H9">
-        <v>4231.0350701402804</v>
+        <v>4.2310350701402797</v>
       </c>
       <c r="I9">
-        <v>1390.6739760094399</v>
+        <v>1.39067397600944</v>
       </c>
       <c r="J9">
-        <v>1882.7012024047999</v>
+        <v>1.8827012024048</v>
       </c>
       <c r="K9">
-        <v>618.81396003159398</v>
+        <v>0.61881396003159395</v>
       </c>
       <c r="L9">
-        <v>6772.4163577154304</v>
+        <v>6.7724163577154304</v>
       </c>
       <c r="M9">
-        <v>2225.9856104343899</v>
+        <v>2.2259856104343898</v>
       </c>
       <c r="N9">
-        <v>9532.0368637274496</v>
+        <v>9.5320368637274502</v>
       </c>
       <c r="O9">
-        <v>3133.0290070861902</v>
+        <v>3.1330290070861899</v>
       </c>
       <c r="P9">
-        <v>5605.0379091516297</v>
+        <v>5.6050379091516298</v>
       </c>
       <c r="Q9">
-        <v>1842.2868696631101</v>
+        <v>1.8422868696631101</v>
       </c>
       <c r="R9">
-        <v>587.42622580645104</v>
+        <v>0.58742622580645099</v>
       </c>
       <c r="S9">
-        <v>193.07766338779001</v>
+        <v>0.19307766338779001</v>
       </c>
       <c r="T9">
-        <v>3864.8693286573098</v>
+        <v>3.8648693286573099</v>
       </c>
       <c r="U9">
-        <v>1270.3211169229601</v>
+        <v>1.27032111692296</v>
       </c>
       <c r="V9">
-        <v>1434.45919354838</v>
+        <v>1.4344591935483799</v>
       </c>
       <c r="W9">
-        <v>471.48393644704498</v>
+        <v>0.471483936447045</v>
       </c>
       <c r="X9">
-        <v>1636.0062701612901</v>
+        <v>1.6360062701612901</v>
       </c>
       <c r="Y9">
-        <v>537.72925697497305</v>
+        <v>0.53772925697497298</v>
       </c>
       <c r="Z9" s="4"/>
       <c r="AA9" s="4"/>
@@ -1502,76 +1502,76 @@
         <v>7.2916666666666699E-2</v>
       </c>
       <c r="B10">
-        <v>5871.2598521882401</v>
+        <v>5.8712598521882402</v>
       </c>
       <c r="C10">
-        <v>1929.7897907890699</v>
+        <v>1.92978979078907</v>
       </c>
       <c r="D10">
-        <v>8747.2896802130199</v>
+        <v>8.7472896802130204</v>
       </c>
       <c r="E10">
-        <v>2875.0950812811202</v>
+        <v>2.87509508128112</v>
       </c>
       <c r="F10">
-        <v>1304.0667955669401</v>
+        <v>1.3040667955669401</v>
       </c>
       <c r="G10">
-        <v>428.62602779438703</v>
+        <v>0.42862602779438702</v>
       </c>
       <c r="H10">
-        <v>3954.58496993988</v>
+        <v>3.9545849699398801</v>
       </c>
       <c r="I10">
-        <v>1299.80922219847</v>
+        <v>1.2998092221984701</v>
       </c>
       <c r="J10">
-        <v>1759.68805611222</v>
+        <v>1.7596880561122199</v>
       </c>
       <c r="K10">
-        <v>578.38149411717905</v>
+        <v>0.57838149411717898</v>
       </c>
       <c r="L10">
-        <v>6329.9158466933804</v>
+        <v>6.32991584669338</v>
       </c>
       <c r="M10">
-        <v>2080.5427259279199</v>
+        <v>2.0805427259279199</v>
       </c>
       <c r="N10">
-        <v>8909.2264869739392</v>
+        <v>8.9092264869739406</v>
       </c>
       <c r="O10">
-        <v>2928.3211357068499</v>
+        <v>2.9283211357068502</v>
       </c>
       <c r="P10">
-        <v>5238.8123246492896</v>
+        <v>5.2388123246492899</v>
       </c>
       <c r="Q10">
-        <v>1721.9143411273501</v>
+        <v>1.7219143411273501</v>
       </c>
       <c r="R10">
-        <v>580.575774193548</v>
+        <v>0.580575774193548</v>
       </c>
       <c r="S10">
-        <v>190.82602882933199</v>
+        <v>0.190826028829332</v>
       </c>
       <c r="T10">
-        <v>3612.3440020039998</v>
+        <v>3.6123440020039999</v>
       </c>
       <c r="U10">
-        <v>1187.3200558969199</v>
+        <v>1.1873200558969199</v>
       </c>
       <c r="V10">
-        <v>1417.7308064516101</v>
+        <v>1.4177308064516101</v>
       </c>
       <c r="W10">
-        <v>465.98558150305598</v>
+        <v>0.46598558150305602</v>
       </c>
       <c r="X10">
-        <v>1616.9274798387</v>
+        <v>1.6169274798387001</v>
       </c>
       <c r="Y10">
-        <v>531.45836184990003</v>
+        <v>0.53145836184990003</v>
       </c>
       <c r="Z10" s="4"/>
       <c r="AA10" s="4"/>
@@ -1626,76 +1626,76 @@
         <v>8.3333333333333301E-2</v>
       </c>
       <c r="B11">
-        <v>5596.7063835735898</v>
+        <v>5.59670638357359</v>
       </c>
       <c r="C11">
-        <v>1839.5484296337099</v>
+        <v>1.8395484296337099</v>
       </c>
       <c r="D11">
-        <v>8354.1967692639791</v>
+        <v>8.3541967692639805</v>
       </c>
       <c r="E11">
-        <v>2745.89168959368</v>
+        <v>2.7458916895936798</v>
       </c>
       <c r="F11">
-        <v>1280.66437120208</v>
+        <v>1.28066437120208</v>
       </c>
       <c r="G11">
-        <v>420.934022883007</v>
+        <v>0.42093402288300702</v>
       </c>
       <c r="H11">
-        <v>3759.04709418837</v>
+        <v>3.7590470941883698</v>
       </c>
       <c r="I11">
-        <v>1235.5390304785101</v>
+        <v>1.2355390304785101</v>
       </c>
       <c r="J11">
-        <v>1672.6787575150299</v>
+        <v>1.6726787575150299</v>
       </c>
       <c r="K11">
-        <v>549.78292066552001</v>
+        <v>0.54978292066552004</v>
       </c>
       <c r="L11">
-        <v>6016.9276803607199</v>
+        <v>6.0169276803607197</v>
       </c>
       <c r="M11">
-        <v>1977.6684905452901</v>
+        <v>1.9776684905452899</v>
       </c>
       <c r="N11">
-        <v>8468.7020741482902</v>
+        <v>8.4687020741482897</v>
       </c>
       <c r="O11">
-        <v>2783.5277632678099</v>
+        <v>2.7835277632678102</v>
       </c>
       <c r="P11">
-        <v>4979.7747160988602</v>
+        <v>4.9797747160988601</v>
       </c>
       <c r="Q11">
-        <v>1636.7727965532799</v>
+        <v>1.6367727965532799</v>
       </c>
       <c r="R11">
-        <v>578.29229032258002</v>
+        <v>0.57829229032258</v>
       </c>
       <c r="S11">
-        <v>190.075483976512</v>
+        <v>0.190075483976512</v>
       </c>
       <c r="T11">
-        <v>3433.7285270541001</v>
+        <v>3.4337285270540998</v>
       </c>
       <c r="U11">
-        <v>1128.6119883419101</v>
+        <v>1.1286119883419099</v>
       </c>
       <c r="V11">
-        <v>1412.15467741935</v>
+        <v>1.4121546774193501</v>
       </c>
       <c r="W11">
-        <v>464.15279652172597</v>
+        <v>0.46415279652172597</v>
       </c>
       <c r="X11">
-        <v>1610.5678830645099</v>
+        <v>1.61056788306451</v>
       </c>
       <c r="Y11">
-        <v>529.36806347487595</v>
+        <v>0.52936806347487597</v>
       </c>
       <c r="Z11" s="4"/>
       <c r="AA11" s="4"/>
@@ -1750,76 +1750,76 @@
         <v>9.375E-2</v>
       </c>
       <c r="B12">
-        <v>5414.0296213071297</v>
+        <v>5.4140296213071197</v>
       </c>
       <c r="C12">
-        <v>1779.50548149119</v>
+        <v>1.7795054814911899</v>
       </c>
       <c r="D12">
-        <v>8078.1474168371296</v>
+        <v>8.0781474168371297</v>
       </c>
       <c r="E12">
-        <v>2655.1586552060498</v>
+        <v>2.65515865520605</v>
       </c>
       <c r="F12">
-        <v>1269.97771252181</v>
+        <v>1.2699777125218099</v>
       </c>
       <c r="G12">
-        <v>417.42148803733301</v>
+        <v>0.41742148803733298</v>
       </c>
       <c r="H12">
-        <v>3627.5647294589098</v>
+        <v>3.6275647294589102</v>
       </c>
       <c r="I12">
-        <v>1192.3228670806</v>
+        <v>1.1923228670806001</v>
       </c>
       <c r="J12">
-        <v>1614.1725050100099</v>
+        <v>1.61417250501001</v>
       </c>
       <c r="K12">
-        <v>530.55284541354195</v>
+        <v>0.53055284541354197</v>
       </c>
       <c r="L12">
-        <v>5806.4701202404804</v>
+        <v>5.8064701202404798</v>
       </c>
       <c r="M12">
-        <v>1908.49443571904</v>
+        <v>1.9084944357190401</v>
       </c>
       <c r="N12">
-        <v>8172.4873827655301</v>
+        <v>8.1724873827655298</v>
       </c>
       <c r="O12">
-        <v>2686.1667024898302</v>
+        <v>2.6861667024898299</v>
       </c>
       <c r="P12">
-        <v>4805.5942551770204</v>
+        <v>4.8055942551770201</v>
       </c>
       <c r="Q12">
-        <v>1579.5224476155399</v>
+        <v>1.5795224476155401</v>
       </c>
       <c r="R12">
-        <v>580.00490322580595</v>
+        <v>0.580004903225806</v>
       </c>
       <c r="S12">
-        <v>190.63839261612699</v>
+        <v>0.190638392616127</v>
       </c>
       <c r="T12">
-        <v>3313.6250180360698</v>
+        <v>3.31362501803607</v>
       </c>
       <c r="U12">
-        <v>1089.1358739514801</v>
+        <v>1.08913587395148</v>
       </c>
       <c r="V12">
-        <v>1416.3367741935399</v>
+        <v>1.41633677419354</v>
       </c>
       <c r="W12">
-        <v>465.52738525772401</v>
+        <v>0.46552738525772402</v>
       </c>
       <c r="X12">
-        <v>1615.33758064516</v>
+        <v>1.61533758064516</v>
       </c>
       <c r="Y12">
-        <v>530.93578725614395</v>
+        <v>0.53093578725614399</v>
       </c>
       <c r="Z12" s="4"/>
       <c r="AA12" s="4"/>
@@ -1874,76 +1874,76 @@
         <v>0.104166666666667</v>
       </c>
       <c r="B13">
-        <v>5287.87531194647</v>
+        <v>5.2878753119464701</v>
       </c>
       <c r="C13">
-        <v>1738.0405652045199</v>
+        <v>1.7380405652045201</v>
       </c>
       <c r="D13">
-        <v>7877.2161895720501</v>
+        <v>7.8772161895720503</v>
       </c>
       <c r="E13">
-        <v>2589.1157545699398</v>
+        <v>2.5891157545699399</v>
       </c>
       <c r="F13">
-        <v>1263.3984686712099</v>
+        <v>1.2633984686712101</v>
       </c>
       <c r="G13">
-        <v>415.25899515954302</v>
+        <v>0.41525899515954301</v>
       </c>
       <c r="H13">
-        <v>3536.5384769539</v>
+        <v>3.5365384769539001</v>
       </c>
       <c r="I13">
-        <v>1162.4039847282099</v>
+        <v>1.1624039847282099</v>
       </c>
       <c r="J13">
-        <v>1573.6681763526999</v>
+        <v>1.5736681763527001</v>
       </c>
       <c r="K13">
-        <v>517.239716392942</v>
+        <v>0.51723971639294197</v>
       </c>
       <c r="L13">
-        <v>5660.7687324649296</v>
+        <v>5.6607687324649296</v>
       </c>
       <c r="M13">
-        <v>1860.60470545472</v>
+        <v>1.8606047054547199</v>
       </c>
       <c r="N13">
-        <v>7967.4156733466898</v>
+        <v>7.9674156733466903</v>
       </c>
       <c r="O13">
-        <v>2618.7628911820002</v>
+        <v>2.618762891182</v>
       </c>
       <c r="P13">
-        <v>4685.0077822311196</v>
+        <v>4.6850077822311196</v>
       </c>
       <c r="Q13">
-        <v>1539.88759065864</v>
+        <v>1.53988759065864</v>
       </c>
       <c r="R13">
-        <v>581.71751612903199</v>
+        <v>0.581717516129032</v>
       </c>
       <c r="S13">
-        <v>191.20130125574099</v>
+        <v>0.191201301255741</v>
       </c>
       <c r="T13">
-        <v>3230.4764348697399</v>
+        <v>3.2304764348697401</v>
       </c>
       <c r="U13">
-        <v>1061.8062562965599</v>
+        <v>1.06180625629656</v>
       </c>
       <c r="V13">
-        <v>1420.51887096774</v>
+        <v>1.4205188709677401</v>
       </c>
       <c r="W13">
-        <v>466.90197399372101</v>
+        <v>0.46690197399372102</v>
       </c>
       <c r="X13">
-        <v>1620.1072782258</v>
+        <v>1.6201072782257999</v>
       </c>
       <c r="Y13">
-        <v>532.50351103741195</v>
+        <v>0.532503511037412</v>
       </c>
       <c r="Z13" s="4"/>
       <c r="AA13" s="4"/>
@@ -1998,76 +1998,76 @@
         <v>0.114583333333333</v>
       </c>
       <c r="B14">
-        <v>5206.78062731915</v>
+        <v>5.2067806273191497</v>
       </c>
       <c r="C14">
-        <v>1711.3860313530299</v>
+        <v>1.71138603135303</v>
       </c>
       <c r="D14">
-        <v>7741.12876150588</v>
+        <v>7.7411287615058804</v>
       </c>
       <c r="E14">
-        <v>2544.3859800499199</v>
+        <v>2.54438598004992</v>
       </c>
       <c r="F14">
-        <v>1254.91719147973</v>
+        <v>1.2549171914797299</v>
       </c>
       <c r="G14">
-        <v>412.47133415508802</v>
+        <v>0.41247133415508802</v>
       </c>
       <c r="H14">
-        <v>3479.2256513026</v>
+        <v>3.4792256513025999</v>
       </c>
       <c r="I14">
-        <v>1143.5661699137399</v>
+        <v>1.14356616991374</v>
       </c>
       <c r="J14">
-        <v>1548.1654509018001</v>
+        <v>1.5481654509017999</v>
       </c>
       <c r="K14">
-        <v>508.85737589848998</v>
+        <v>0.50885737589849001</v>
       </c>
       <c r="L14">
-        <v>5569.0308216432804</v>
+        <v>5.5690308216432802</v>
       </c>
       <c r="M14">
-        <v>1830.4519123253301</v>
+        <v>1.83045191232533</v>
       </c>
       <c r="N14">
-        <v>7838.2964488977896</v>
+        <v>7.8382964488977898</v>
       </c>
       <c r="O14">
-        <v>2576.3234544326301</v>
+        <v>2.5763234544326301</v>
       </c>
       <c r="P14">
-        <v>4609.0829659318597</v>
+        <v>4.6090829659318597</v>
       </c>
       <c r="Q14">
-        <v>1514.93231035245</v>
+        <v>1.5149323103524499</v>
       </c>
       <c r="R14">
-        <v>580.00490322580595</v>
+        <v>0.580004903225806</v>
       </c>
       <c r="S14">
-        <v>190.63839261612699</v>
+        <v>0.190638392616127</v>
       </c>
       <c r="T14">
-        <v>3178.1236232464898</v>
+        <v>3.1781236232464898</v>
       </c>
       <c r="U14">
-        <v>1044.5987192545799</v>
+        <v>1.04459871925457</v>
       </c>
       <c r="V14">
-        <v>1416.3367741935399</v>
+        <v>1.41633677419354</v>
       </c>
       <c r="W14">
-        <v>465.52738525772401</v>
+        <v>0.46552738525772402</v>
       </c>
       <c r="X14">
-        <v>1615.33758064516</v>
+        <v>1.61533758064516</v>
       </c>
       <c r="Y14">
-        <v>530.93578725614395</v>
+        <v>0.53093578725614399</v>
       </c>
       <c r="Z14" s="4"/>
       <c r="AA14" s="4"/>
@@ -2122,76 +2122,76 @@
         <v>0.125</v>
       </c>
       <c r="B15">
-        <v>5137.0933301118303</v>
+        <v>5.1370933301118296</v>
       </c>
       <c r="C15">
-        <v>1688.48092442811</v>
+        <v>1.68848092442811</v>
       </c>
       <c r="D15">
-        <v>7625.5300165437902</v>
+        <v>7.6255300165437898</v>
       </c>
       <c r="E15">
-        <v>2506.3905100022498</v>
+        <v>2.5063905100022499</v>
       </c>
       <c r="F15">
-        <v>1240.36292928599</v>
+        <v>1.2403629292859899</v>
       </c>
       <c r="G15">
-        <v>407.68757950939897</v>
+        <v>0.40768757950939899</v>
       </c>
       <c r="H15">
-        <v>3432.0268537074098</v>
+        <v>3.4320268537074101</v>
       </c>
       <c r="I15">
-        <v>1128.05267536065</v>
+        <v>1.1280526753606499</v>
       </c>
       <c r="J15">
-        <v>1527.16320641282</v>
+        <v>1.52716320641282</v>
       </c>
       <c r="K15">
-        <v>501.95427196188302</v>
+        <v>0.50195427196188303</v>
       </c>
       <c r="L15">
-        <v>5493.4819539078098</v>
+        <v>5.4934819539078097</v>
       </c>
       <c r="M15">
-        <v>1805.6202003364201</v>
+        <v>1.8056202003364199</v>
       </c>
       <c r="N15">
-        <v>7731.9629699398702</v>
+        <v>7.7319629699398797</v>
       </c>
       <c r="O15">
-        <v>2541.3733300507902</v>
+        <v>2.5413733300507899</v>
       </c>
       <c r="P15">
-        <v>4546.55664662658</v>
+        <v>4.5465566466265797</v>
       </c>
       <c r="Q15">
-        <v>1494.38090304147</v>
+        <v>1.4943809030414701</v>
       </c>
       <c r="R15">
-        <v>573.72532258064496</v>
+        <v>0.57372532258064501</v>
       </c>
       <c r="S15">
-        <v>188.574394270874</v>
+        <v>0.188574394270874</v>
       </c>
       <c r="T15">
-        <v>3135.0095430861702</v>
+        <v>3.13500954308617</v>
       </c>
       <c r="U15">
-        <v>1030.42780639647</v>
+        <v>1.03042780639647</v>
       </c>
       <c r="V15">
-        <v>1401.00241935483</v>
+        <v>1.4010024193548301</v>
       </c>
       <c r="W15">
-        <v>460.48722655906698</v>
+        <v>0.46048722655906699</v>
       </c>
       <c r="X15">
-        <v>1597.84868951612</v>
+        <v>1.5978486895161199</v>
       </c>
       <c r="Y15">
-        <v>525.18746672482803</v>
+        <v>0.52518746672482797</v>
       </c>
       <c r="Z15" s="4"/>
       <c r="AA15" s="4"/>
@@ -2246,76 +2246,76 @@
         <v>0.13541666666666699</v>
       </c>
       <c r="B16">
-        <v>5083.5236247333296</v>
+        <v>5.0835236247333304</v>
       </c>
       <c r="C16">
-        <v>1670.8734137510801</v>
+        <v>1.6708734137510799</v>
       </c>
       <c r="D16">
-        <v>7536.6630446888803</v>
+        <v>7.53666304468888</v>
       </c>
       <c r="E16">
-        <v>2477.18134887817</v>
+        <v>2.4771813488781702</v>
       </c>
       <c r="F16">
-        <v>1220.07796665912</v>
+        <v>1.2200779666591199</v>
       </c>
       <c r="G16">
-        <v>401.02023471980101</v>
+        <v>0.40102023471980103</v>
       </c>
       <c r="H16">
-        <v>3398.3134268537001</v>
+        <v>3.3983134268536999</v>
       </c>
       <c r="I16">
-        <v>1116.97160782272</v>
+        <v>1.1169716078227201</v>
       </c>
       <c r="J16">
-        <v>1512.1616032064101</v>
+        <v>1.51216160320641</v>
       </c>
       <c r="K16">
-        <v>497.02348343573402</v>
+        <v>0.49702348343573399</v>
       </c>
       <c r="L16">
-        <v>5439.5184769539001</v>
+        <v>5.4395184769539</v>
       </c>
       <c r="M16">
-        <v>1787.8832632014801</v>
+        <v>1.7878832632014801</v>
       </c>
       <c r="N16">
-        <v>7656.0104849699401</v>
+        <v>7.65601048496994</v>
       </c>
       <c r="O16">
-        <v>2516.4089554923298</v>
+        <v>2.5164089554923299</v>
       </c>
       <c r="P16">
-        <v>4501.89498997996</v>
+        <v>4.5018949899799603</v>
       </c>
       <c r="Q16">
-        <v>1479.70132639077</v>
+        <v>1.4797013263907699</v>
       </c>
       <c r="R16">
-        <v>562.878774193548</v>
+        <v>0.56287877419354804</v>
       </c>
       <c r="S16">
-        <v>185.009306219981</v>
+        <v>0.18500930621998099</v>
       </c>
       <c r="T16">
-        <v>3104.2137715430799</v>
+        <v>3.1042137715430802</v>
       </c>
       <c r="U16">
-        <v>1020.30572578354</v>
+        <v>1.02030572578354</v>
       </c>
       <c r="V16">
-        <v>1374.5158064516099</v>
+        <v>1.3745158064516101</v>
       </c>
       <c r="W16">
-        <v>451.78149789775102</v>
+        <v>0.45178149789775102</v>
       </c>
       <c r="X16">
-        <v>1567.6406048387</v>
+        <v>1.5676406048386999</v>
       </c>
       <c r="Y16">
-        <v>515.25854944346304</v>
+        <v>0.51525854944346305</v>
       </c>
       <c r="Z16" s="4"/>
       <c r="AA16" s="4"/>
@@ -2370,76 +2370,76 @@
         <v>0.14583333333333301</v>
       </c>
       <c r="B17">
-        <v>5043.4037261296698</v>
+        <v>5.0434037261296698</v>
       </c>
       <c r="C17">
-        <v>1657.6866407786699</v>
+        <v>1.6576866407786699</v>
       </c>
       <c r="D17">
-        <v>7469.0276351414004</v>
+        <v>7.4690276351413996</v>
       </c>
       <c r="E17">
-        <v>2454.9506648126498</v>
+        <v>2.45495066481265</v>
       </c>
       <c r="F17">
-        <v>1199.04489806225</v>
+        <v>1.1990448980622499</v>
       </c>
       <c r="G17">
-        <v>394.106999388872</v>
+        <v>0.394106999388872</v>
       </c>
       <c r="H17">
-        <v>3374.7140280561098</v>
+        <v>3.3747140280561099</v>
       </c>
       <c r="I17">
-        <v>1109.21486054618</v>
+        <v>1.10921486054618</v>
       </c>
       <c r="J17">
-        <v>1501.66048096192</v>
+        <v>1.5016604809619201</v>
       </c>
       <c r="K17">
-        <v>493.571931467431</v>
+        <v>0.493571931467431</v>
       </c>
       <c r="L17">
-        <v>5401.7440430861698</v>
+        <v>5.4017440430861701</v>
       </c>
       <c r="M17">
-        <v>1775.46740720703</v>
+        <v>1.77546740720703</v>
       </c>
       <c r="N17">
-        <v>7602.8437454909799</v>
+        <v>7.6028437454909801</v>
       </c>
       <c r="O17">
-        <v>2498.9338933014201</v>
+        <v>2.49893389330142</v>
       </c>
       <c r="P17">
-        <v>4470.6318303273201</v>
+        <v>4.4706318303273198</v>
       </c>
       <c r="Q17">
-        <v>1469.4256227352701</v>
+        <v>1.46942562273527</v>
       </c>
       <c r="R17">
-        <v>550.89048387096705</v>
+        <v>0.55089048387096695</v>
       </c>
       <c r="S17">
-        <v>181.06894574268</v>
+        <v>0.18106894574268001</v>
       </c>
       <c r="T17">
-        <v>3082.6567314629201</v>
+        <v>3.0826567314629201</v>
       </c>
       <c r="U17">
-        <v>1013.22026935449</v>
+        <v>1.0132202693544901</v>
       </c>
       <c r="V17">
-        <v>1345.24112903225</v>
+        <v>1.3452411290322499</v>
       </c>
       <c r="W17">
-        <v>442.159376745771</v>
+        <v>0.44215937674577099</v>
       </c>
       <c r="X17">
-        <v>1534.2527217741899</v>
+        <v>1.5342527217741899</v>
       </c>
       <c r="Y17">
-        <v>504.28448297458601</v>
+        <v>0.50428448297458595</v>
       </c>
       <c r="Z17" s="4"/>
       <c r="AA17" s="4"/>
@@ -2494,76 +2494,76 @@
         <v>0.15625</v>
       </c>
       <c r="B18">
-        <v>5022.8054516128996</v>
+        <v>5.0228054516128999</v>
       </c>
       <c r="C18">
-        <v>1650.9163153509</v>
+        <v>1.6509163153509001</v>
       </c>
       <c r="D18">
-        <v>7426.5098047337196</v>
+        <v>7.4265098047337199</v>
       </c>
       <c r="E18">
-        <v>2440.9757297709498</v>
+        <v>2.4409757297709498</v>
       </c>
       <c r="F18">
-        <v>1181.1559274193501</v>
+        <v>1.1811559274193499</v>
       </c>
       <c r="G18">
-        <v>388.22717908054</v>
+        <v>0.38822717908054</v>
       </c>
       <c r="H18">
-        <v>3364.6</v>
+        <v>3.3645999999999998</v>
       </c>
       <c r="I18">
-        <v>1105.8905402848</v>
+        <v>1.1058905402848</v>
       </c>
       <c r="J18">
-        <v>1497.16</v>
+        <v>1.49716</v>
       </c>
       <c r="K18">
-        <v>492.09269490958599</v>
+        <v>0.49209269490958601</v>
       </c>
       <c r="L18">
-        <v>5385.5550000000003</v>
+        <v>5.3855550000000001</v>
       </c>
       <c r="M18">
-        <v>1770.14632606655</v>
+        <v>1.77014632606655</v>
       </c>
       <c r="N18">
-        <v>7580.05799999999</v>
+        <v>7.5800579999999904</v>
       </c>
       <c r="O18">
-        <v>2491.4445809338799</v>
+        <v>2.4914445809338801</v>
       </c>
       <c r="P18">
-        <v>4457.2333333333299</v>
+        <v>4.4572333333333303</v>
       </c>
       <c r="Q18">
-        <v>1465.0217497400599</v>
+        <v>1.4650217497400599</v>
       </c>
       <c r="R18">
-        <v>540.043935483871</v>
+        <v>0.54004393548387097</v>
       </c>
       <c r="S18">
-        <v>177.503857691787</v>
+        <v>0.177503857691787</v>
       </c>
       <c r="T18">
-        <v>3073.4180000000001</v>
+        <v>3.0734180000000002</v>
       </c>
       <c r="U18">
-        <v>1010.18364517061</v>
+        <v>1.0101836451706101</v>
       </c>
       <c r="V18">
-        <v>1318.75451612903</v>
+        <v>1.3187545161290299</v>
       </c>
       <c r="W18">
-        <v>433.45364808445498</v>
+        <v>0.43345364808445502</v>
       </c>
       <c r="X18">
-        <v>1504.04463709677</v>
+        <v>1.5040446370967699</v>
       </c>
       <c r="Y18">
-        <v>494.35556569322102</v>
+        <v>0.49435556569322098</v>
       </c>
       <c r="Z18" s="4"/>
       <c r="AA18" s="4"/>
@@ -2618,76 +2618,76 @@
         <v>0.16666666666666699</v>
       </c>
       <c r="B19">
-        <v>5028.1410217208604</v>
+        <v>5.0281410217208604</v>
       </c>
       <c r="C19">
-        <v>1652.6700324374499</v>
+        <v>1.6526700324374499</v>
       </c>
       <c r="D19">
-        <v>7415.4252530326403</v>
+        <v>7.4154252530326401</v>
       </c>
       <c r="E19">
-        <v>2437.33241381377</v>
+        <v>2.43733241381377</v>
       </c>
       <c r="F19">
-        <v>1171.1907384931101</v>
+        <v>1.17119073849311</v>
       </c>
       <c r="G19">
-        <v>384.95177987538102</v>
+        <v>0.38495177987538098</v>
       </c>
       <c r="H19">
-        <v>3371.3426853707401</v>
+        <v>3.37134268537074</v>
       </c>
       <c r="I19">
-        <v>1108.10675379238</v>
+        <v>1.1081067537923801</v>
       </c>
       <c r="J19">
-        <v>1500.1603206412799</v>
+        <v>1.5001603206412799</v>
       </c>
       <c r="K19">
-        <v>493.07885261481601</v>
+        <v>0.49307885261481599</v>
       </c>
       <c r="L19">
-        <v>5396.3476953907802</v>
+        <v>5.3963476953907801</v>
       </c>
       <c r="M19">
-        <v>1773.6937134935299</v>
+        <v>1.77369371349353</v>
       </c>
       <c r="N19">
-        <v>7595.2484969939796</v>
+        <v>7.59524849699398</v>
       </c>
       <c r="O19">
-        <v>2496.4374558455702</v>
+        <v>2.49643745584557</v>
       </c>
       <c r="P19">
-        <v>4466.1656646626498</v>
+        <v>4.4661656646626504</v>
       </c>
       <c r="Q19">
-        <v>1467.9576650701999</v>
+        <v>1.4679576650702</v>
       </c>
       <c r="R19">
-        <v>533.19348387096704</v>
+        <v>0.53319348387096699</v>
       </c>
       <c r="S19">
-        <v>175.25222313332901</v>
+        <v>0.175252223133329</v>
       </c>
       <c r="T19">
-        <v>3079.5771543086098</v>
+        <v>3.0795771543086099</v>
       </c>
       <c r="U19">
-        <v>1012.20806129319</v>
+        <v>1.0122080612931901</v>
       </c>
       <c r="V19">
-        <v>1302.0261290322501</v>
+        <v>1.3020261290322499</v>
       </c>
       <c r="W19">
-        <v>427.95529314046598</v>
+        <v>0.42795529314046599</v>
       </c>
       <c r="X19">
-        <v>1484.9658467741899</v>
+        <v>1.48496584677419</v>
       </c>
       <c r="Y19">
-        <v>488.084670568148</v>
+        <v>0.48808467056814803</v>
       </c>
       <c r="Z19" s="4"/>
       <c r="AA19" s="4"/>
@@ -2742,76 +2742,76 @@
         <v>0.17708333333333301</v>
       </c>
       <c r="B20">
-        <v>5045.2798232270998</v>
+        <v>5.0452798232270997</v>
       </c>
       <c r="C20">
-        <v>1658.3032840743699</v>
+        <v>1.6583032840743701</v>
       </c>
       <c r="D20">
-        <v>7421.3231989882497</v>
+        <v>7.42132319898825</v>
       </c>
       <c r="E20">
-        <v>2439.2709749025898</v>
+        <v>2.4392709749025898</v>
       </c>
       <c r="F20">
-        <v>1168.12247757611</v>
+        <v>1.1681224775761101</v>
       </c>
       <c r="G20">
-        <v>383.943291281423</v>
+        <v>0.38394329128142302</v>
       </c>
       <c r="H20">
-        <v>3384.8280561122201</v>
+        <v>3.3848280561122199</v>
       </c>
       <c r="I20">
-        <v>1112.5391808075501</v>
+        <v>1.11253918080755</v>
       </c>
       <c r="J20">
-        <v>1506.16096192384</v>
+        <v>1.5061609619238401</v>
       </c>
       <c r="K20">
-        <v>495.05116802527499</v>
+        <v>0.49505116802527499</v>
       </c>
       <c r="L20">
-        <v>5417.9330861723402</v>
+        <v>5.41793308617234</v>
       </c>
       <c r="M20">
-        <v>1780.7884883475101</v>
+        <v>1.78078848834751</v>
       </c>
       <c r="N20">
-        <v>7625.6294909819599</v>
+        <v>7.62562949098196</v>
       </c>
       <c r="O20">
-        <v>2506.4232056689498</v>
+        <v>2.5064232056689502</v>
       </c>
       <c r="P20">
-        <v>4484.0303273213003</v>
+        <v>4.4840303273212996</v>
       </c>
       <c r="Q20">
-        <v>1473.8294957304799</v>
+        <v>1.4738294957304801</v>
       </c>
       <c r="R20">
-        <v>530.33912903225803</v>
+        <v>0.53033912903225799</v>
       </c>
       <c r="S20">
-        <v>174.314042067305</v>
+        <v>0.174314042067305</v>
       </c>
       <c r="T20">
-        <v>3091.8954629258501</v>
+        <v>3.0918954629258502</v>
       </c>
       <c r="U20">
-        <v>1016.25689353837</v>
+        <v>1.01625689353837</v>
       </c>
       <c r="V20">
-        <v>1295.0559677419301</v>
+        <v>1.29505596774193</v>
       </c>
       <c r="W20">
-        <v>425.664311913804</v>
+        <v>0.42566431191380399</v>
       </c>
       <c r="X20">
-        <v>1477.01635080645</v>
+        <v>1.47701635080645</v>
       </c>
       <c r="Y20">
-        <v>485.47179759936802</v>
+        <v>0.48547179759936798</v>
       </c>
       <c r="Z20" s="4"/>
       <c r="AA20" s="4"/>
@@ -2866,76 +2866,76 @@
         <v>0.1875</v>
       </c>
       <c r="B21">
-        <v>5065.48225376559</v>
+        <v>5.0654822537655901</v>
       </c>
       <c r="C21">
-        <v>1664.9435018783499</v>
+        <v>1.6649435018783501</v>
       </c>
       <c r="D21">
-        <v>7434.2923644560497</v>
+        <v>7.4342923644560397</v>
       </c>
       <c r="E21">
-        <v>2443.5337334492901</v>
+        <v>2.4435337334492901</v>
       </c>
       <c r="F21">
-        <v>1173.0415352075099</v>
+        <v>1.1730415352075101</v>
       </c>
       <c r="G21">
-        <v>385.56010733732001</v>
+        <v>0.38556010733731999</v>
       </c>
       <c r="H21">
-        <v>3398.3134268537001</v>
+        <v>3.3983134268536999</v>
       </c>
       <c r="I21">
-        <v>1116.97160782272</v>
+        <v>1.1169716078227201</v>
       </c>
       <c r="J21">
-        <v>1512.1616032064101</v>
+        <v>1.51216160320641</v>
       </c>
       <c r="K21">
-        <v>497.02348343573499</v>
+        <v>0.49702348343573499</v>
       </c>
       <c r="L21">
-        <v>5439.5184769539001</v>
+        <v>5.4395184769539</v>
       </c>
       <c r="M21">
-        <v>1787.8832632014801</v>
+        <v>1.7878832632014801</v>
       </c>
       <c r="N21">
-        <v>7656.0104849699401</v>
+        <v>7.65601048496994</v>
       </c>
       <c r="O21">
-        <v>2516.4089554923298</v>
+        <v>2.5164089554923299</v>
       </c>
       <c r="P21">
-        <v>4501.89498997996</v>
+        <v>4.5018949899799603</v>
       </c>
       <c r="Q21">
-        <v>1479.70132639077</v>
+        <v>1.4797013263907699</v>
       </c>
       <c r="R21">
-        <v>532.62261290322499</v>
+        <v>0.53262261290322499</v>
       </c>
       <c r="S21">
-        <v>175.06458692012399</v>
+        <v>0.175064586920124</v>
       </c>
       <c r="T21">
-        <v>3104.2137715430799</v>
+        <v>3.1042137715430802</v>
       </c>
       <c r="U21">
-        <v>1020.30572578354</v>
+        <v>1.02030572578354</v>
       </c>
       <c r="V21">
-        <v>1300.6320967741899</v>
+        <v>1.30063209677419</v>
       </c>
       <c r="W21">
-        <v>427.49709689513401</v>
+        <v>0.42749709689513399</v>
       </c>
       <c r="X21">
-        <v>1483.3759475806401</v>
+        <v>1.4833759475806401</v>
       </c>
       <c r="Y21">
-        <v>487.56209597439198</v>
+        <v>0.48756209597439198</v>
       </c>
       <c r="Z21" s="4"/>
       <c r="AA21" s="4"/>
@@ -2990,76 +2990,76 @@
         <v>0.19791666666666699</v>
       </c>
       <c r="B22">
-        <v>5065.1972912922602</v>
+        <v>5.06519729129226</v>
       </c>
       <c r="C22">
-        <v>1664.84983924279</v>
+        <v>1.66484983924279</v>
       </c>
       <c r="D22">
-        <v>7432.9980330520502</v>
+        <v>7.4329980330520504</v>
       </c>
       <c r="E22">
-        <v>2443.1083072899601</v>
+        <v>2.4431083072899602</v>
       </c>
       <c r="F22">
-        <v>1184.23648854159</v>
+        <v>1.1842364885415899</v>
       </c>
       <c r="G22">
-        <v>389.23971055645399</v>
+        <v>0.38923971055645401</v>
       </c>
       <c r="H22">
-        <v>3394.94208416833</v>
+        <v>3.39494208416833</v>
       </c>
       <c r="I22">
-        <v>1115.86350106893</v>
+        <v>1.11586350106893</v>
       </c>
       <c r="J22">
-        <v>1510.6614428857699</v>
+        <v>1.5106614428857701</v>
       </c>
       <c r="K22">
-        <v>496.53040458312</v>
+        <v>0.49653040458311998</v>
       </c>
       <c r="L22">
-        <v>5434.1221292585096</v>
+        <v>5.43412212925851</v>
       </c>
       <c r="M22">
-        <v>1786.10956948799</v>
+        <v>1.78610956948799</v>
       </c>
       <c r="N22">
-        <v>7648.4152364729398</v>
+        <v>7.6484152364729399</v>
       </c>
       <c r="O22">
-        <v>2513.9125180364899</v>
+        <v>2.5139125180364901</v>
       </c>
       <c r="P22">
-        <v>4497.4288243152896</v>
+        <v>4.49742882431529</v>
       </c>
       <c r="Q22">
-        <v>1478.2333687256901</v>
+        <v>1.4782333687256899</v>
       </c>
       <c r="R22">
-        <v>540.043935483871</v>
+        <v>0.54004393548387097</v>
       </c>
       <c r="S22">
-        <v>177.503857691787</v>
+        <v>0.177503857691787</v>
       </c>
       <c r="T22">
-        <v>3101.1341943887701</v>
+        <v>3.10113419438877</v>
       </c>
       <c r="U22">
-        <v>1019.29351772224</v>
+        <v>1.01929351772225</v>
       </c>
       <c r="V22">
-        <v>1318.75451612903</v>
+        <v>1.3187545161290299</v>
       </c>
       <c r="W22">
-        <v>433.45364808445498</v>
+        <v>0.43345364808445502</v>
       </c>
       <c r="X22">
-        <v>1504.04463709677</v>
+        <v>1.5040446370967699</v>
       </c>
       <c r="Y22">
-        <v>494.35556569322102</v>
+        <v>0.49435556569322098</v>
       </c>
       <c r="Z22" s="4"/>
       <c r="AA22" s="4"/>
@@ -3114,76 +3114,76 @@
         <v>0.20833333333333301</v>
       </c>
       <c r="B23">
-        <v>5054.5261510763403</v>
+        <v>5.05452615107634</v>
       </c>
       <c r="C23">
-        <v>1661.3424050696899</v>
+        <v>1.6613424050696901</v>
       </c>
       <c r="D23">
-        <v>7426.9716515357604</v>
+        <v>7.4269716515357604</v>
       </c>
       <c r="E23">
-        <v>2441.12753147381</v>
+        <v>2.4411275314738101</v>
       </c>
       <c r="F23">
-        <v>1204.16686639407</v>
+        <v>1.2041668663940699</v>
       </c>
       <c r="G23">
-        <v>395.79050896677302</v>
+        <v>0.39579050896677298</v>
       </c>
       <c r="H23">
-        <v>3381.45671342685</v>
+        <v>3.3814567134268501</v>
       </c>
       <c r="I23">
-        <v>1111.4310740537601</v>
+        <v>1.1114310740537601</v>
       </c>
       <c r="J23">
-        <v>1504.6608016032001</v>
+        <v>1.5046608016031999</v>
       </c>
       <c r="K23">
-        <v>494.55808917266</v>
+        <v>0.49455808917265998</v>
       </c>
       <c r="L23">
-        <v>5412.5367384769497</v>
+        <v>5.41253673847695</v>
       </c>
       <c r="M23">
-        <v>1779.0147946340101</v>
+        <v>1.77901479463402</v>
       </c>
       <c r="N23">
-        <v>7618.0342424849696</v>
+        <v>7.6180342424849696</v>
       </c>
       <c r="O23">
-        <v>2503.9267682131099</v>
+        <v>2.5039267682131099</v>
       </c>
       <c r="P23">
-        <v>4479.56416165664</v>
+        <v>4.47956416165664</v>
       </c>
       <c r="Q23">
-        <v>1472.3615380654101</v>
+        <v>1.47236153806541</v>
       </c>
       <c r="R23">
-        <v>553.74483870967697</v>
+        <v>0.55374483870967695</v>
       </c>
       <c r="S23">
-        <v>182.00712680870399</v>
+        <v>0.18200712680870401</v>
       </c>
       <c r="T23">
-        <v>3088.8158857715398</v>
+        <v>3.08881588577154</v>
       </c>
       <c r="U23">
-        <v>1015.24468547707</v>
+        <v>1.01524468547707</v>
       </c>
       <c r="V23">
-        <v>1352.21129032258</v>
+        <v>1.35221129032258</v>
       </c>
       <c r="W23">
-        <v>444.45035797243298</v>
+        <v>0.44445035797243299</v>
       </c>
       <c r="X23">
-        <v>1542.2022177419301</v>
+        <v>1.5422022177419299</v>
       </c>
       <c r="Y23">
-        <v>506.89735594336599</v>
+        <v>0.50689735594336605</v>
       </c>
       <c r="Z23" s="4"/>
       <c r="AA23" s="4"/>
@@ -3238,76 +3238,76 @@
         <v>0.21875</v>
       </c>
       <c r="B24">
-        <v>5042.5488387096702</v>
+        <v>5.0425488387096697</v>
       </c>
       <c r="C24">
-        <v>1657.405652872</v>
+        <v>1.657405652872</v>
       </c>
       <c r="D24">
-        <v>7419.5615454851504</v>
+        <v>7.4195615454851502</v>
       </c>
       <c r="E24">
-        <v>2438.6919473972898</v>
+        <v>2.4386919473972899</v>
       </c>
       <c r="F24">
-        <v>1232.62975806451</v>
+        <v>1.23262975806451</v>
       </c>
       <c r="G24">
-        <v>405.145809046274</v>
+        <v>0.40514580904627401</v>
       </c>
       <c r="H24">
-        <v>3364.6</v>
+        <v>3.3645999999999998</v>
       </c>
       <c r="I24">
-        <v>1105.8905402848</v>
+        <v>1.1058905402848</v>
       </c>
       <c r="J24">
-        <v>1497.16</v>
+        <v>1.49716</v>
       </c>
       <c r="K24">
-        <v>492.09269490958599</v>
+        <v>0.49209269490958601</v>
       </c>
       <c r="L24">
-        <v>5385.5550000000003</v>
+        <v>5.3855550000000001</v>
       </c>
       <c r="M24">
-        <v>1770.14632606655</v>
+        <v>1.77014632606655</v>
       </c>
       <c r="N24">
-        <v>7580.05799999999</v>
+        <v>7.5800579999999904</v>
       </c>
       <c r="O24">
-        <v>2491.4445809338799</v>
+        <v>2.4914445809338801</v>
       </c>
       <c r="P24">
-        <v>4457.2333333333299</v>
+        <v>4.4572333333333303</v>
       </c>
       <c r="Q24">
-        <v>1465.0217497400599</v>
+        <v>1.4650217497400599</v>
       </c>
       <c r="R24">
-        <v>573.15445161290302</v>
+        <v>0.57315445161290302</v>
       </c>
       <c r="S24">
-        <v>188.386758057669</v>
+        <v>0.188386758057669</v>
       </c>
       <c r="T24">
-        <v>3073.4180000000001</v>
+        <v>3.0734180000000002</v>
       </c>
       <c r="U24">
-        <v>1010.18364517061</v>
+        <v>1.0101836451706101</v>
       </c>
       <c r="V24">
-        <v>1399.60838709677</v>
+        <v>1.3996083870967699</v>
       </c>
       <c r="W24">
-        <v>460.02903031373501</v>
+        <v>0.46002903031373499</v>
       </c>
       <c r="X24">
-        <v>1596.2587903225799</v>
+        <v>1.59625879032258</v>
       </c>
       <c r="Y24">
-        <v>524.66489213107195</v>
+        <v>0.52466489213107104</v>
       </c>
       <c r="Z24" s="4"/>
       <c r="AA24" s="4"/>
@@ -3362,76 +3362,76 @@
         <v>0.22916666666666699</v>
       </c>
       <c r="B25">
-        <v>5067.9681991402103</v>
+        <v>5.0679681991402097</v>
       </c>
       <c r="C25">
-        <v>1665.7605926093299</v>
+        <v>1.66576059260933</v>
       </c>
       <c r="D25">
-        <v>7449.9436029628896</v>
+        <v>7.4499436029628896</v>
       </c>
       <c r="E25">
-        <v>2448.6780467728499</v>
+        <v>2.4486780467728502</v>
       </c>
       <c r="F25">
-        <v>1275.0258796221401</v>
+        <v>1.2750258796221401</v>
       </c>
       <c r="G25">
-        <v>419.08074032349799</v>
+        <v>0.41908074032349801</v>
       </c>
       <c r="H25">
-        <v>3371.3426853707401</v>
+        <v>3.37134268537074</v>
       </c>
       <c r="I25">
-        <v>1108.10675379238</v>
+        <v>1.1081067537923801</v>
       </c>
       <c r="J25">
-        <v>1500.1603206412799</v>
+        <v>1.5001603206412799</v>
       </c>
       <c r="K25">
-        <v>493.07885261481601</v>
+        <v>0.49307885261481599</v>
       </c>
       <c r="L25">
-        <v>5396.3476953907802</v>
+        <v>5.3963476953907801</v>
       </c>
       <c r="M25">
-        <v>1773.6937134935299</v>
+        <v>1.77369371349353</v>
       </c>
       <c r="N25">
-        <v>7595.2484969939796</v>
+        <v>7.59524849699398</v>
       </c>
       <c r="O25">
-        <v>2496.4374558455702</v>
+        <v>2.49643745584557</v>
       </c>
       <c r="P25">
-        <v>4466.1656646626498</v>
+        <v>4.4661656646626504</v>
       </c>
       <c r="Q25">
-        <v>1467.9576650701999</v>
+        <v>1.4679576650702</v>
       </c>
       <c r="R25">
-        <v>599.98538709677405</v>
+        <v>0.59998538709677396</v>
       </c>
       <c r="S25">
-        <v>197.205660078297</v>
+        <v>0.19720566007829701</v>
       </c>
       <c r="T25">
-        <v>3079.5771543086098</v>
+        <v>3.0795771543086099</v>
       </c>
       <c r="U25">
-        <v>1012.20806129319</v>
+        <v>1.0122080612931901</v>
       </c>
       <c r="V25">
-        <v>1465.1279032258001</v>
+        <v>1.4651279032258</v>
       </c>
       <c r="W25">
-        <v>481.56425384435801</v>
+        <v>0.48156425384435803</v>
       </c>
       <c r="X25">
-        <v>1670.9840524193501</v>
+        <v>1.67098405241935</v>
       </c>
       <c r="Y25">
-        <v>549.22589803760604</v>
+        <v>0.54922589803760602</v>
       </c>
       <c r="Z25" s="4"/>
       <c r="AA25" s="4"/>
@@ -3486,76 +3486,76 @@
         <v>0.23958333333333301</v>
       </c>
       <c r="B26">
-        <v>5163.4152600038697</v>
+        <v>5.1634152600038696</v>
       </c>
       <c r="C26">
-        <v>1697.1325244012601</v>
+        <v>1.6971325244012601</v>
       </c>
       <c r="D26">
-        <v>7545.1579391016603</v>
+        <v>7.5451579391016601</v>
       </c>
       <c r="E26">
-        <v>2479.9734856468199</v>
+        <v>2.4799734856468199</v>
       </c>
       <c r="F26">
-        <v>1332.86374321223</v>
+        <v>1.3328637432122299</v>
       </c>
       <c r="G26">
-        <v>438.09112676306199</v>
+        <v>0.438091126763062</v>
       </c>
       <c r="H26">
-        <v>3425.2841683366701</v>
+        <v>3.4252841683366699</v>
       </c>
       <c r="I26">
-        <v>1125.83646185306</v>
+        <v>1.1258364618530601</v>
       </c>
       <c r="J26">
-        <v>1524.16288577154</v>
+        <v>1.5241628857715399</v>
       </c>
       <c r="K26">
-        <v>500.968114256653</v>
+        <v>0.500968114256653</v>
       </c>
       <c r="L26">
-        <v>5482.6892585170299</v>
+        <v>5.4826892585170297</v>
       </c>
       <c r="M26">
-        <v>1802.07281290943</v>
+        <v>1.8020728129094301</v>
       </c>
       <c r="N26">
-        <v>7716.7724729458896</v>
+        <v>7.7167724729458902</v>
       </c>
       <c r="O26">
-        <v>2536.3804551390999</v>
+        <v>2.5363804551391</v>
       </c>
       <c r="P26">
-        <v>4537.6243152972602</v>
+        <v>4.5376243152972604</v>
       </c>
       <c r="Q26">
-        <v>1491.44498771133</v>
+        <v>1.4914449877113301</v>
       </c>
       <c r="R26">
-        <v>633.66677419354801</v>
+        <v>0.633666774193548</v>
       </c>
       <c r="S26">
-        <v>208.276196657383</v>
+        <v>0.20827619665738301</v>
       </c>
       <c r="T26">
-        <v>3128.8503887775501</v>
+        <v>3.1288503887775501</v>
       </c>
       <c r="U26">
-        <v>1028.4033902738799</v>
+        <v>1.0284033902738801</v>
       </c>
       <c r="V26">
-        <v>1547.3758064516101</v>
+        <v>1.5473758064516101</v>
       </c>
       <c r="W26">
-        <v>508.59783231897001</v>
+        <v>0.50859783231897004</v>
       </c>
       <c r="X26">
-        <v>1764.7881048387001</v>
+        <v>1.7647881048387</v>
       </c>
       <c r="Y26">
-        <v>580.05779906921305</v>
+        <v>0.58005779906921295</v>
       </c>
       <c r="Z26" s="4"/>
       <c r="AA26" s="4"/>
@@ -3610,76 +3610,76 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>5345.7438603335704</v>
+        <v>5.3457438603335703</v>
       </c>
       <c r="C27">
-        <v>1757.0610372491401</v>
+        <v>1.75706103724914</v>
       </c>
       <c r="D27">
-        <v>7721.6493603037597</v>
+        <v>7.7216493603037604</v>
       </c>
       <c r="E27">
-        <v>2537.9834104963802</v>
+        <v>2.5379834104963801</v>
       </c>
       <c r="F27">
-        <v>1414.27004125185</v>
+        <v>1.4142700412518501</v>
       </c>
       <c r="G27">
-        <v>464.84808299014003</v>
+        <v>0.46484808299014002</v>
       </c>
       <c r="H27">
-        <v>3536.5384769539</v>
+        <v>3.5365384769539001</v>
       </c>
       <c r="I27">
-        <v>1162.4039847282099</v>
+        <v>1.1624039847282099</v>
       </c>
       <c r="J27">
-        <v>1573.6681763526999</v>
+        <v>1.5736681763527001</v>
       </c>
       <c r="K27">
-        <v>517.239716392942</v>
+        <v>0.51723971639294197</v>
       </c>
       <c r="L27">
-        <v>5660.7687324649296</v>
+        <v>5.6607687324649296</v>
       </c>
       <c r="M27">
-        <v>1860.60470545472</v>
+        <v>1.8606047054547199</v>
       </c>
       <c r="N27">
-        <v>7967.4156733466898</v>
+        <v>7.9674156733466903</v>
       </c>
       <c r="O27">
-        <v>2618.7628911820002</v>
+        <v>2.618762891182</v>
       </c>
       <c r="P27">
-        <v>4685.0077822311196</v>
+        <v>4.6850077822311196</v>
       </c>
       <c r="Q27">
-        <v>1539.88759065864</v>
+        <v>1.53988759065864</v>
       </c>
       <c r="R27">
-        <v>678.76558064516098</v>
+        <v>0.67876558064516102</v>
       </c>
       <c r="S27">
-        <v>223.09945750056599</v>
+        <v>0.22309945750056601</v>
       </c>
       <c r="T27">
-        <v>3230.4764348697399</v>
+        <v>3.2304764348697401</v>
       </c>
       <c r="U27">
-        <v>1061.8062562965599</v>
+        <v>1.06180625629656</v>
       </c>
       <c r="V27">
-        <v>1657.5043548387</v>
+        <v>1.6575043548387001</v>
       </c>
       <c r="W27">
-        <v>544.79533570023</v>
+        <v>0.54479533570022998</v>
       </c>
       <c r="X27">
-        <v>1890.3901411290301</v>
+        <v>1.89039014112903</v>
       </c>
       <c r="Y27">
-        <v>621.34119197593998</v>
+        <v>0.62134119197593995</v>
       </c>
       <c r="Z27" s="4"/>
       <c r="AA27" s="4"/>
@@ -3734,76 +3734,76 @@
         <v>0.26041666666666702</v>
       </c>
       <c r="B28">
-        <v>5640.6583230331598</v>
+        <v>5.6406583230331604</v>
       </c>
       <c r="C28">
-        <v>1853.9947335258601</v>
+        <v>1.85399473352586</v>
       </c>
       <c r="D28">
-        <v>8013.3228930609503</v>
+        <v>8.0133228930609501</v>
       </c>
       <c r="E28">
-        <v>2633.8518646150301</v>
+        <v>2.6338518646150302</v>
       </c>
       <c r="F28">
-        <v>1550.44594196457</v>
+        <v>1.55044594196457</v>
       </c>
       <c r="G28">
-        <v>509.60693706282501</v>
+        <v>0.50960693706282501</v>
       </c>
       <c r="H28">
-        <v>3715.2196392785499</v>
+        <v>3.7152196392785499</v>
       </c>
       <c r="I28">
-        <v>1221.13364267921</v>
+        <v>1.2211336426792101</v>
       </c>
       <c r="J28">
-        <v>1653.17667334669</v>
+        <v>1.6531766733466899</v>
       </c>
       <c r="K28">
-        <v>543.37289558152702</v>
+        <v>0.54337289558152702</v>
       </c>
       <c r="L28">
-        <v>5946.7751603206398</v>
+        <v>5.94677516032064</v>
       </c>
       <c r="M28">
-        <v>1954.6104722698799</v>
+        <v>1.9546104722698801</v>
       </c>
       <c r="N28">
-        <v>8369.9638436873702</v>
+        <v>8.3699638436873691</v>
       </c>
       <c r="O28">
-        <v>2751.0740763418198</v>
+        <v>2.75107407634182</v>
       </c>
       <c r="P28">
-        <v>4921.7145624582499</v>
+        <v>4.9217145624582503</v>
       </c>
       <c r="Q28">
-        <v>1617.68934690736</v>
+        <v>1.6176893469073701</v>
       </c>
       <c r="R28">
-        <v>754.69141935483799</v>
+        <v>0.75469141935483797</v>
       </c>
       <c r="S28">
-        <v>248.05507385681099</v>
+        <v>0.248055073856811</v>
       </c>
       <c r="T28">
-        <v>3393.6940240480899</v>
+        <v>3.3936940240480902</v>
       </c>
       <c r="U28">
-        <v>1115.4532835451</v>
+        <v>1.1154532835451001</v>
       </c>
       <c r="V28">
-        <v>1842.9106451612899</v>
+        <v>1.84291064516129</v>
       </c>
       <c r="W28">
-        <v>605.73543632943995</v>
+        <v>0.60573543632943905</v>
       </c>
       <c r="X28">
-        <v>2101.8467338709602</v>
+        <v>2.1018467338709601</v>
       </c>
       <c r="Y28">
-        <v>690.84361294549501</v>
+        <v>0.69084361294549501</v>
       </c>
       <c r="Z28" s="4"/>
       <c r="AA28" s="4"/>
@@ -3858,76 +3858,76 @@
         <v>0.27083333333333298</v>
       </c>
       <c r="B29">
-        <v>6071.8759924041597</v>
+        <v>6.0718759924041601</v>
       </c>
       <c r="C29">
-        <v>1995.72912732038</v>
+        <v>1.9957291273203801</v>
       </c>
       <c r="D29">
-        <v>8467.1495001764197</v>
+        <v>8.4671495001764203</v>
       </c>
       <c r="E29">
-        <v>2783.0174568811399</v>
+        <v>2.7830174568811401</v>
       </c>
       <c r="F29">
-        <v>1779.35016771446</v>
+        <v>1.7793501677144601</v>
       </c>
       <c r="G29">
-        <v>584.84411767508698</v>
+        <v>0.58484411767508704</v>
       </c>
       <c r="H29">
-        <v>3968.07034068136</v>
+        <v>3.96807034068136</v>
       </c>
       <c r="I29">
-        <v>1304.2416492136399</v>
+        <v>1.3042416492136399</v>
       </c>
       <c r="J29">
-        <v>1765.6886973947801</v>
+        <v>1.7656886973947801</v>
       </c>
       <c r="K29">
-        <v>580.35380952763796</v>
+        <v>0.58035380952763804</v>
       </c>
       <c r="L29">
-        <v>6351.5012374749404</v>
+        <v>6.3515012374749498</v>
       </c>
       <c r="M29">
-        <v>2087.6375007818901</v>
+        <v>2.0876375007818901</v>
       </c>
       <c r="N29">
-        <v>8939.6074809619204</v>
+        <v>8.9396074809619197</v>
       </c>
       <c r="O29">
-        <v>2938.3068855302399</v>
+        <v>2.9383068855302401</v>
       </c>
       <c r="P29">
-        <v>5256.6769873079402</v>
+        <v>5.2566769873079497</v>
       </c>
       <c r="Q29">
-        <v>1727.7861717876301</v>
+        <v>1.7277861717876299</v>
       </c>
       <c r="R29">
-        <v>885.42087096774196</v>
+        <v>0.88542087096774202</v>
       </c>
       <c r="S29">
-        <v>291.023766680721</v>
+        <v>0.291023766680722</v>
       </c>
       <c r="T29">
-        <v>3624.6623106212401</v>
+        <v>3.6246623106212401</v>
       </c>
       <c r="U29">
-        <v>1191.3688881420901</v>
+        <v>1.1913688881420901</v>
       </c>
       <c r="V29">
-        <v>2162.1440322580602</v>
+        <v>2.1621440322580598</v>
       </c>
       <c r="W29">
-        <v>710.66237651055997</v>
+        <v>0.71066237651055997</v>
       </c>
       <c r="X29">
-        <v>2465.9336491935401</v>
+        <v>2.46593364919354</v>
       </c>
       <c r="Y29">
-        <v>810.51319491563004</v>
+        <v>0.81051319491563001</v>
       </c>
       <c r="Z29" s="4"/>
       <c r="AA29" s="4"/>
@@ -3982,76 +3982,76 @@
         <v>0.28125</v>
       </c>
       <c r="B30">
-        <v>6648.30279307001</v>
+        <v>6.6483027930700098</v>
       </c>
       <c r="C30">
-        <v>2185.1914544983501</v>
+        <v>2.1851914544983502</v>
       </c>
       <c r="D30">
-        <v>9097.30104498326</v>
+        <v>9.0973010449832596</v>
       </c>
       <c r="E30">
-        <v>2990.1382535130601</v>
+        <v>2.9901382535130598</v>
       </c>
       <c r="F30">
-        <v>2136.1396274807598</v>
+        <v>2.1361396274807598</v>
       </c>
       <c r="G30">
-        <v>702.115141995626</v>
+        <v>0.70211514199562597</v>
       </c>
       <c r="H30">
-        <v>4291.7192384769496</v>
+        <v>4.2917192384769498</v>
       </c>
       <c r="I30">
-        <v>1410.6198975777099</v>
+        <v>1.41061989757771</v>
       </c>
       <c r="J30">
-        <v>1909.7040881763501</v>
+        <v>1.9097040881763501</v>
       </c>
       <c r="K30">
-        <v>627.68937937866099</v>
+        <v>0.62768937937866098</v>
       </c>
       <c r="L30">
-        <v>6869.55061623246</v>
+        <v>6.86955061623246</v>
       </c>
       <c r="M30">
-        <v>2257.9120972772698</v>
+        <v>2.2579120972772699</v>
       </c>
       <c r="N30">
-        <v>9668.7513366733492</v>
+        <v>9.6687513366733402</v>
       </c>
       <c r="O30">
-        <v>3177.9648812914102</v>
+        <v>3.1779648812914099</v>
       </c>
       <c r="P30">
-        <v>5685.42889111556</v>
+        <v>5.6854288911155599</v>
       </c>
       <c r="Q30">
-        <v>1868.7101076343699</v>
+        <v>1.86871010763437</v>
       </c>
       <c r="R30">
-        <v>1093.7887741935399</v>
+        <v>1.0937887741935399</v>
       </c>
       <c r="S30">
-        <v>359.51098450049199</v>
+        <v>0.35951098450049201</v>
       </c>
       <c r="T30">
-        <v>3920.3017174348602</v>
+        <v>3.92030171743487</v>
       </c>
       <c r="U30">
-        <v>1288.5408620262399</v>
+        <v>1.28854086202624</v>
       </c>
       <c r="V30">
-        <v>2670.9658064516102</v>
+        <v>2.6709658064516102</v>
       </c>
       <c r="W30">
-        <v>877.90400605688797</v>
+        <v>0.87790400605688801</v>
       </c>
       <c r="X30">
-        <v>3046.2468548387001</v>
+        <v>3.0462468548386998</v>
       </c>
       <c r="Y30">
-        <v>1001.25292163658</v>
+        <v>1.00125292163658</v>
       </c>
       <c r="Z30" s="4"/>
       <c r="AA30" s="4"/>
@@ -4106,76 +4106,76 @@
         <v>0.29166666666666702</v>
       </c>
       <c r="B31">
-        <v>7386.1671983644701</v>
+        <v>7.3861671983644701</v>
       </c>
       <c r="C31">
-        <v>2427.7157562958901</v>
+        <v>2.42771575629589</v>
       </c>
       <c r="D31">
-        <v>9934.8298545988891</v>
+        <v>9.93482985459889</v>
       </c>
       <c r="E31">
-        <v>3265.4206608630898</v>
+        <v>3.2654206608630898</v>
       </c>
       <c r="F31">
-        <v>2639.2484871759598</v>
+        <v>2.6392484871759598</v>
       </c>
       <c r="G31">
-        <v>867.47902735210005</v>
+        <v>0.86747902735210003</v>
       </c>
       <c r="H31">
-        <v>4692.9090180360699</v>
+        <v>4.6929090180360697</v>
       </c>
       <c r="I31">
-        <v>1542.4846012789999</v>
+        <v>1.5424846012789999</v>
       </c>
       <c r="J31">
-        <v>2088.2231663326602</v>
+        <v>2.0882231663326598</v>
       </c>
       <c r="K31">
-        <v>686.36576283982401</v>
+        <v>0.68636576283982398</v>
       </c>
       <c r="L31">
-        <v>7511.7159919839596</v>
+        <v>7.5117159919839596</v>
       </c>
       <c r="M31">
-        <v>2468.9816491830002</v>
+        <v>2.4689816491830001</v>
       </c>
       <c r="N31">
-        <v>10572.585907815601</v>
+        <v>10.572585907815601</v>
       </c>
       <c r="O31">
-        <v>3475.0409385370299</v>
+        <v>3.4750409385370302</v>
       </c>
       <c r="P31">
-        <v>6216.90260521042</v>
+        <v>6.2169026052104197</v>
       </c>
       <c r="Q31">
-        <v>2043.3970697777299</v>
+        <v>2.0433970697777299</v>
       </c>
       <c r="R31">
-        <v>1391.21254838709</v>
+        <v>1.3912125483870901</v>
       </c>
       <c r="S31">
-        <v>457.269451580218</v>
+        <v>0.45726945158021798</v>
       </c>
       <c r="T31">
-        <v>4286.7713987975903</v>
+        <v>4.2867713987975904</v>
       </c>
       <c r="U31">
-        <v>1408.9936213201299</v>
+        <v>1.40899362132013</v>
       </c>
       <c r="V31">
-        <v>3397.2566129032198</v>
+        <v>3.3972566129032198</v>
       </c>
       <c r="W31">
-        <v>1116.6242498750701</v>
+        <v>1.11662424987507</v>
       </c>
       <c r="X31">
-        <v>3874.58433467741</v>
+        <v>3.8745843346774098</v>
       </c>
       <c r="Y31">
-        <v>1273.5142849834799</v>
+        <v>1.27351428498348</v>
       </c>
       <c r="Z31" s="4"/>
       <c r="AA31" s="4"/>
@@ -4230,76 +4230,76 @@
         <v>0.30208333333333298</v>
       </c>
       <c r="B32">
-        <v>8263.0025953843106</v>
+        <v>8.2630025953843091</v>
       </c>
       <c r="C32">
-        <v>2715.9176141545099</v>
+        <v>2.7159176141545101</v>
       </c>
       <c r="D32">
-        <v>10956.003194621901</v>
+        <v>10.9560031946219</v>
       </c>
       <c r="E32">
-        <v>3601.0641063610901</v>
+        <v>3.6010641063610902</v>
       </c>
       <c r="F32">
-        <v>3230.1030774452101</v>
+        <v>3.23010307744521</v>
       </c>
       <c r="G32">
-        <v>1061.6835396455699</v>
+        <v>1.0616835396455699</v>
       </c>
       <c r="H32">
-        <v>5171.6396793587101</v>
+        <v>5.1716396793587096</v>
       </c>
       <c r="I32">
-        <v>1699.83576031752</v>
+        <v>1.69983576031752</v>
       </c>
       <c r="J32">
-        <v>2301.2459318637202</v>
+        <v>2.3012459318637202</v>
       </c>
       <c r="K32">
-        <v>756.38295991112795</v>
+        <v>0.75638295991112803</v>
       </c>
       <c r="L32">
-        <v>8277.9973647294592</v>
+        <v>8.27799736472946</v>
       </c>
       <c r="M32">
-        <v>2720.8461564990798</v>
+        <v>2.72084615649909</v>
       </c>
       <c r="N32">
-        <v>11651.111194388701</v>
+        <v>11.651111194388699</v>
       </c>
       <c r="O32">
-        <v>3829.53505726711</v>
+        <v>3.8295350572671101</v>
       </c>
       <c r="P32">
-        <v>6851.0981295925103</v>
+        <v>6.8510981295925104</v>
       </c>
       <c r="Q32">
-        <v>2251.8470582177001</v>
+        <v>2.2518470582177001</v>
       </c>
       <c r="R32">
-        <v>1740.0147096774101</v>
+        <v>1.7400147096774099</v>
       </c>
       <c r="S32">
-        <v>571.91517784838197</v>
+        <v>0.57191517784838197</v>
       </c>
       <c r="T32">
-        <v>4724.0713547094101</v>
+        <v>4.7240713547094098</v>
       </c>
       <c r="U32">
-        <v>1552.72716602376</v>
+        <v>1.55272716602376</v>
       </c>
       <c r="V32">
-        <v>4249.0103225806397</v>
+        <v>4.2490103225806397</v>
       </c>
       <c r="W32">
-        <v>1396.5821557731699</v>
+        <v>1.3965821557731699</v>
       </c>
       <c r="X32">
-        <v>4846.0127419354803</v>
+        <v>4.8460127419354802</v>
       </c>
       <c r="Y32">
-        <v>1592.8073617684299</v>
+        <v>1.59280736176843</v>
       </c>
       <c r="Z32" s="4"/>
       <c r="AA32" s="4"/>
@@ -4354,76 +4354,76 @@
         <v>0.3125</v>
       </c>
       <c r="B33">
-        <v>9238.7522849893303</v>
+        <v>9.2387522849893298</v>
       </c>
       <c r="C33">
-        <v>3036.63102776089</v>
+        <v>3.0366310277608899</v>
       </c>
       <c r="D33">
-        <v>12112.962003918599</v>
+        <v>12.1129620039186</v>
       </c>
       <c r="E33">
-        <v>3981.3380773235799</v>
+        <v>3.98133807732358</v>
       </c>
       <c r="F33">
-        <v>3828.1456436663598</v>
+        <v>3.8281456436663599</v>
       </c>
       <c r="G33">
-        <v>1258.2506253828401</v>
+        <v>1.25825062538284</v>
       </c>
       <c r="H33">
-        <v>5721.1685370741397</v>
+        <v>5.7211685370741403</v>
       </c>
       <c r="I33">
-        <v>1880.45716118568</v>
+        <v>1.88045716118568</v>
       </c>
       <c r="J33">
-        <v>2545.7720641282499</v>
+        <v>2.5457720641282502</v>
       </c>
       <c r="K33">
-        <v>836.75481288734295</v>
+        <v>0.83675481288734299</v>
       </c>
       <c r="L33">
-        <v>9157.6020390781505</v>
+        <v>9.1576020390781494</v>
       </c>
       <c r="M33">
-        <v>3009.9582317985301</v>
+        <v>3.0099582317985298</v>
       </c>
       <c r="N33">
-        <v>12889.136699398699</v>
+        <v>12.8891366993987</v>
       </c>
       <c r="O33">
-        <v>4236.4543625699298</v>
+        <v>4.2364543625699298</v>
       </c>
       <c r="P33">
-        <v>7579.0831329325301</v>
+        <v>7.5790831329325297</v>
       </c>
       <c r="Q33">
-        <v>2491.12415762414</v>
+        <v>2.4911241576241401</v>
       </c>
       <c r="R33">
-        <v>2088.8168709677402</v>
+        <v>2.0888168709677402</v>
       </c>
       <c r="S33">
-        <v>686.56090411654498</v>
+        <v>0.68656090411654502</v>
       </c>
       <c r="T33">
-        <v>5226.0424308617203</v>
+        <v>5.2260424308617202</v>
       </c>
       <c r="U33">
-        <v>1717.71708001455</v>
+        <v>1.71771708001455</v>
       </c>
       <c r="V33">
-        <v>5100.7640322580601</v>
+        <v>5.1007640322580601</v>
       </c>
       <c r="W33">
-        <v>1676.54006167127</v>
+        <v>1.67654006167127</v>
       </c>
       <c r="X33">
-        <v>5817.4411491935398</v>
+        <v>5.8174411491935398</v>
       </c>
       <c r="Y33">
-        <v>1912.1004385533699</v>
+        <v>1.91210043855337</v>
       </c>
       <c r="Z33" s="4"/>
       <c r="AA33" s="4"/>
@@ -4478,76 +4478,76 @@
         <v>0.32291666666666702</v>
       </c>
       <c r="B34">
-        <v>10283.8011865343</v>
+        <v>10.2838011865343</v>
       </c>
       <c r="C34">
-        <v>3380.1219908333701</v>
+        <v>3.3801219908333699</v>
       </c>
       <c r="D34">
-        <v>13366.0549124019</v>
+        <v>13.3660549124019</v>
       </c>
       <c r="E34">
-        <v>4393.2097986543804</v>
+        <v>4.3932097986543797</v>
       </c>
       <c r="F34">
-        <v>4356.1654398716701</v>
+        <v>4.3561654398716696</v>
       </c>
       <c r="G34">
-        <v>1431.8023396153101</v>
+        <v>1.4318023396153099</v>
       </c>
       <c r="H34">
-        <v>6341.4955911823599</v>
+        <v>6.3414955911823601</v>
       </c>
       <c r="I34">
-        <v>2084.3488038834798</v>
+        <v>2.0843488038834801</v>
       </c>
       <c r="J34">
-        <v>2821.8015631262501</v>
+        <v>2.8218015631262499</v>
       </c>
       <c r="K34">
-        <v>927.481321768469</v>
+        <v>0.92748132176846898</v>
       </c>
       <c r="L34">
-        <v>10150.530015030001</v>
+        <v>10.15053001503</v>
       </c>
       <c r="M34">
-        <v>3336.3178750813399</v>
+        <v>3.33631787508134</v>
       </c>
       <c r="N34">
-        <v>14286.6624228456</v>
+        <v>14.2866624228456</v>
       </c>
       <c r="O34">
-        <v>4695.7988544455202</v>
+        <v>4.6957988544455196</v>
       </c>
       <c r="P34">
-        <v>8400.8576152304595</v>
+        <v>8.4008576152304499</v>
       </c>
       <c r="Q34">
-        <v>2761.2283679970601</v>
+        <v>2.76122836799706</v>
       </c>
       <c r="R34">
-        <v>2387.95325806451</v>
+        <v>2.3879532580645102</v>
       </c>
       <c r="S34">
-        <v>784.88227983588604</v>
+        <v>0.78488227983588599</v>
       </c>
       <c r="T34">
-        <v>5792.6846272544999</v>
+        <v>5.7926846272545003</v>
       </c>
       <c r="U34">
-        <v>1903.9633632924999</v>
+        <v>1.9039633632924999</v>
       </c>
       <c r="V34">
-        <v>5831.2369354838702</v>
+        <v>5.8312369354838696</v>
       </c>
       <c r="W34">
-        <v>1916.6348942254499</v>
+        <v>1.9166348942254501</v>
       </c>
       <c r="X34">
-        <v>6650.5483266129004</v>
+        <v>6.6505483266129</v>
       </c>
       <c r="Y34">
-        <v>2185.9295256815399</v>
+        <v>2.1859295256815399</v>
       </c>
       <c r="Z34" s="4"/>
       <c r="AA34" s="4"/>
@@ -4602,76 +4602,76 @@
         <v>0.33333333333333298</v>
       </c>
       <c r="B35">
-        <v>11367.2280472234</v>
+        <v>11.367228047223399</v>
       </c>
       <c r="C35">
-        <v>3736.2271790657201</v>
+        <v>3.73622717906572</v>
       </c>
       <c r="D35">
-        <v>14689.729803754</v>
+        <v>14.689729803754</v>
       </c>
       <c r="E35">
-        <v>4828.2806958661904</v>
+        <v>4.8282806958661899</v>
       </c>
       <c r="F35">
-        <v>4745.4842339113702</v>
+        <v>4.7454842339113696</v>
       </c>
       <c r="G35">
-        <v>1559.7652390635601</v>
+        <v>1.5597652390635599</v>
       </c>
       <c r="H35">
-        <v>7029.2494989979896</v>
+        <v>7.0292494989979897</v>
       </c>
       <c r="I35">
-        <v>2310.4025816571202</v>
+        <v>2.3104025816571201</v>
       </c>
       <c r="J35">
-        <v>3127.8342685370699</v>
+        <v>3.1278342685370699</v>
       </c>
       <c r="K35">
-        <v>1028.06940770189</v>
+        <v>1.0280694077018899</v>
       </c>
       <c r="L35">
-        <v>11251.3849448897</v>
+        <v>11.251384944889701</v>
       </c>
       <c r="M35">
-        <v>3698.1513926340199</v>
+        <v>3.6981513926340202</v>
       </c>
       <c r="N35">
-        <v>15836.0931162324</v>
+        <v>15.8360931162324</v>
       </c>
       <c r="O35">
-        <v>5205.0720954380204</v>
+        <v>5.2050720954380196</v>
       </c>
       <c r="P35">
-        <v>9311.9554108216398</v>
+        <v>9.3119554108216391</v>
       </c>
       <c r="Q35">
-        <v>3060.6917316713798</v>
+        <v>3.0606917316713802</v>
       </c>
       <c r="R35">
-        <v>2593.46680645161</v>
+        <v>2.5934668064516102</v>
       </c>
       <c r="S35">
-        <v>852.43131658963205</v>
+        <v>0.852431316589632</v>
       </c>
       <c r="T35">
-        <v>6420.9183667334601</v>
+        <v>6.4209183667334599</v>
       </c>
       <c r="U35">
-        <v>2110.4538077963098</v>
+        <v>2.11045380779631</v>
       </c>
       <c r="V35">
-        <v>6333.0885483870898</v>
+        <v>6.3330885483870896</v>
       </c>
       <c r="W35">
-        <v>2081.58554254511</v>
+        <v>2.0815855425451102</v>
       </c>
       <c r="X35">
-        <v>7222.9120362903204</v>
+        <v>7.2229120362903201</v>
       </c>
       <c r="Y35">
-        <v>2374.0563794337199</v>
+        <v>2.3740563794337199</v>
       </c>
       <c r="Z35" s="4"/>
       <c r="AA35" s="4"/>
@@ -4726,76 +4726,76 @@
         <v>0.34375</v>
       </c>
       <c r="B36">
-        <v>12440.5137693128</v>
+        <v>12.440513769312799</v>
       </c>
       <c r="C36">
-        <v>4088.9991362319101</v>
+        <v>4.0889991362319096</v>
       </c>
       <c r="D36">
-        <v>16038.495090345599</v>
+        <v>16.038495090345599</v>
       </c>
       <c r="E36">
-        <v>5271.5984071858602</v>
+        <v>5.2715984071858601</v>
       </c>
       <c r="F36">
-        <v>4977.0468275664198</v>
+        <v>4.9770468275664204</v>
       </c>
       <c r="G36">
-        <v>1635.8761829519599</v>
+        <v>1.6358761829519599</v>
       </c>
       <c r="H36">
-        <v>7754.0881763527004</v>
+        <v>7.7540881763526999</v>
       </c>
       <c r="I36">
-        <v>2548.6455337224902</v>
+        <v>2.5486455337224898</v>
       </c>
       <c r="J36">
-        <v>3450.3687374749402</v>
+        <v>3.4503687374749399</v>
       </c>
       <c r="K36">
-        <v>1134.0813610140699</v>
+        <v>1.1340813610140701</v>
       </c>
       <c r="L36">
-        <v>12411.599699398699</v>
+        <v>12.4115996993987</v>
       </c>
       <c r="M36">
-        <v>4079.4955410351399</v>
+        <v>4.0794955410351399</v>
       </c>
       <c r="N36">
-        <v>17469.071543086098</v>
+        <v>17.469071543086098</v>
       </c>
       <c r="O36">
-        <v>5741.8061484448199</v>
+        <v>5.7418061484448204</v>
       </c>
       <c r="P36">
-        <v>10272.181028724101</v>
+        <v>10.2721810287241</v>
       </c>
       <c r="Q36">
-        <v>3376.3026296614698</v>
+        <v>3.37630262966147</v>
       </c>
       <c r="R36">
-        <v>2695.0818387096701</v>
+        <v>2.6950818387096702</v>
       </c>
       <c r="S36">
-        <v>885.830562540095</v>
+        <v>0.88583056254009496</v>
       </c>
       <c r="T36">
-        <v>7083.0274549098103</v>
+        <v>7.0830274549098098</v>
       </c>
       <c r="U36">
-        <v>2328.0785409743498</v>
+        <v>2.3280785409743499</v>
       </c>
       <c r="V36">
-        <v>6581.2262903225801</v>
+        <v>6.5812262903225802</v>
       </c>
       <c r="W36">
-        <v>2163.1444742142799</v>
+        <v>2.1631444742142798</v>
       </c>
       <c r="X36">
-        <v>7505.9140927419303</v>
+        <v>7.5059140927419303</v>
       </c>
       <c r="Y36">
-        <v>2467.0746571222999</v>
+        <v>2.4670746571222999</v>
       </c>
       <c r="Z36" s="4"/>
       <c r="AA36" s="4"/>
@@ -4850,76 +4850,76 @@
         <v>0.35416666666666702</v>
       </c>
       <c r="B37">
-        <v>13463.2534917253</v>
+        <v>13.4632534917253</v>
       </c>
       <c r="C37">
-        <v>4425.1574267239603</v>
+        <v>4.4251574267239597</v>
       </c>
       <c r="D37">
-        <v>17386.6638370654</v>
+        <v>17.386663837065399</v>
       </c>
       <c r="E37">
-        <v>5714.72004533156</v>
+        <v>5.7147200453315596</v>
       </c>
       <c r="F37">
-        <v>5041.0151055740498</v>
+        <v>5.0410151055740497</v>
       </c>
       <c r="G37">
-        <v>1656.9015391687301</v>
+        <v>1.6569015391687301</v>
       </c>
       <c r="H37">
-        <v>8489.0408817635198</v>
+        <v>8.4890408817635201</v>
       </c>
       <c r="I37">
-        <v>2790.21280604923</v>
+        <v>2.7902128060492299</v>
       </c>
       <c r="J37">
-        <v>3777.40368737474</v>
+        <v>3.7774036873747399</v>
       </c>
       <c r="K37">
-        <v>1241.5725508841001</v>
+        <v>1.2415725508841</v>
       </c>
       <c r="L37">
-        <v>13588.003496993901</v>
+        <v>13.588003496993901</v>
       </c>
       <c r="M37">
-        <v>4466.1607705767301</v>
+        <v>4.4661607705767299</v>
       </c>
       <c r="N37">
-        <v>19124.8357154308</v>
+        <v>19.124835715430802</v>
       </c>
       <c r="O37">
-        <v>6286.0295138191505</v>
+        <v>6.28602951381915</v>
       </c>
       <c r="P37">
-        <v>11245.805143620501</v>
+        <v>11.245805143620499</v>
       </c>
       <c r="Q37">
-        <v>3696.3174006467798</v>
+        <v>3.6963174006467798</v>
       </c>
       <c r="R37">
-        <v>2688.23138709677</v>
+        <v>2.6882313870967698</v>
       </c>
       <c r="S37">
-        <v>883.57892798163698</v>
+        <v>0.88357892798163695</v>
       </c>
       <c r="T37">
-        <v>7754.3752745490901</v>
+        <v>7.7543752745490897</v>
       </c>
       <c r="U37">
-        <v>2548.73989833627</v>
+        <v>2.5487398983362701</v>
       </c>
       <c r="V37">
-        <v>6564.4979032257997</v>
+        <v>6.5644979032258002</v>
       </c>
       <c r="W37">
-        <v>2157.64611927029</v>
+        <v>2.1576461192702898</v>
       </c>
       <c r="X37">
-        <v>7486.8353024193502</v>
+        <v>7.4868353024193501</v>
       </c>
       <c r="Y37">
-        <v>2460.8037619972201</v>
+        <v>2.4608037619972198</v>
       </c>
       <c r="Z37" s="4"/>
       <c r="AA37" s="4"/>
@@ -4974,76 +4974,76 @@
         <v>0.36458333333333298</v>
       </c>
       <c r="B38">
-        <v>14389.991745749499</v>
+        <v>14.3899917457495</v>
       </c>
       <c r="C38">
-        <v>4729.7615604829198</v>
+        <v>4.7297615604829204</v>
       </c>
       <c r="D38">
-        <v>18700.239383882901</v>
+        <v>18.700239383882899</v>
       </c>
       <c r="E38">
-        <v>6146.4714485221102</v>
+        <v>6.1464714485221101</v>
       </c>
       <c r="F38">
-        <v>4926.3211882636197</v>
+        <v>4.9263211882636204</v>
       </c>
       <c r="G38">
-        <v>1619.2034715881</v>
+        <v>1.6192034715881001</v>
       </c>
       <c r="H38">
-        <v>9203.7655310621194</v>
+        <v>9.2037655310621194</v>
       </c>
       <c r="I38">
-        <v>3025.1314378532102</v>
+        <v>3.0251314378532101</v>
       </c>
       <c r="J38">
-        <v>4095.4376753506999</v>
+        <v>4.0954376753507002</v>
       </c>
       <c r="K38">
-        <v>1346.10526763844</v>
+        <v>1.34610526763844</v>
       </c>
       <c r="L38">
-        <v>14732.0292084168</v>
+        <v>14.732029208416799</v>
       </c>
       <c r="M38">
-        <v>4842.1838378373604</v>
+        <v>4.8421838378373598</v>
       </c>
       <c r="N38">
-        <v>20735.028396793499</v>
+        <v>20.735028396793499</v>
       </c>
       <c r="O38">
-        <v>6815.2742544584098</v>
+        <v>6.8152742544584104</v>
       </c>
       <c r="P38">
-        <v>12192.632264529</v>
+        <v>12.192632264528999</v>
       </c>
       <c r="Q38">
-        <v>4007.5244256416599</v>
+        <v>4.0075244256416598</v>
       </c>
       <c r="R38">
-        <v>2567.77761290322</v>
+        <v>2.5677776129032202</v>
       </c>
       <c r="S38">
-        <v>843.98768699541404</v>
+        <v>0.84398768699541404</v>
       </c>
       <c r="T38">
-        <v>8407.24563126252</v>
+        <v>8.4072456312625192</v>
       </c>
       <c r="U38">
-        <v>2763.32800733042</v>
+        <v>2.76332800733043</v>
       </c>
       <c r="V38">
-        <v>6270.3570967741898</v>
+        <v>6.2703570967741902</v>
       </c>
       <c r="W38">
-        <v>2060.9667115051502</v>
+        <v>2.0609667115051602</v>
       </c>
       <c r="X38">
-        <v>7151.3665725806404</v>
+        <v>7.1513665725806401</v>
       </c>
       <c r="Y38">
-        <v>2350.5405227146998</v>
+        <v>2.3505405227147</v>
       </c>
       <c r="Z38" s="4"/>
       <c r="AA38" s="4"/>
@@ -5098,76 +5098,76 @@
         <v>0.375</v>
       </c>
       <c r="B39">
-        <v>15177.370922781</v>
+        <v>15.177370922781</v>
       </c>
       <c r="C39">
-        <v>4988.5605807219799</v>
+        <v>4.9885605807219804</v>
       </c>
       <c r="D39">
-        <v>19942.009323574999</v>
+        <v>19.942009323575</v>
       </c>
       <c r="E39">
-        <v>6554.6214899877996</v>
+        <v>6.5546214899877997</v>
       </c>
       <c r="F39">
-        <v>4639.30450816956</v>
+        <v>4.6393045081695599</v>
       </c>
       <c r="G39">
-        <v>1524.86565091997</v>
+        <v>1.5248656509199701</v>
       </c>
       <c r="H39">
-        <v>9864.54869739479</v>
+        <v>9.86454869739479</v>
       </c>
       <c r="I39">
-        <v>3242.3203615965199</v>
+        <v>3.2423203615965202</v>
       </c>
       <c r="J39">
-        <v>4389.4690981963904</v>
+        <v>4.3894690981963898</v>
       </c>
       <c r="K39">
-        <v>1442.74872275095</v>
+        <v>1.4427487227509499</v>
       </c>
       <c r="L39">
-        <v>15789.713356713401</v>
+        <v>15.789713356713399</v>
       </c>
       <c r="M39">
-        <v>5189.82780568209</v>
+        <v>5.1898278056820901</v>
       </c>
       <c r="N39">
-        <v>22223.697102204402</v>
+        <v>22.223697102204401</v>
       </c>
       <c r="O39">
-        <v>7304.5759958041499</v>
+        <v>7.3045759958041501</v>
       </c>
       <c r="P39">
-        <v>13068.000734802899</v>
+        <v>13.068000734802901</v>
       </c>
       <c r="Q39">
-        <v>4295.2441279954301</v>
+        <v>4.2952441279954297</v>
       </c>
       <c r="R39">
-        <v>2340.0000967741898</v>
+        <v>2.3400000967741899</v>
       </c>
       <c r="S39">
-        <v>769.12083792667897</v>
+        <v>0.76912083792667896</v>
       </c>
       <c r="T39">
-        <v>9010.8427535070095</v>
+        <v>9.0108427535070099</v>
       </c>
       <c r="U39">
-        <v>2961.7207873438902</v>
+        <v>2.9617207873438902</v>
       </c>
       <c r="V39">
-        <v>5714.1382258064496</v>
+        <v>5.7141382258064501</v>
       </c>
       <c r="W39">
-        <v>1878.14640961753</v>
+        <v>1.87814640961753</v>
       </c>
       <c r="X39">
-        <v>6516.9967943548299</v>
+        <v>6.5169967943548297</v>
       </c>
       <c r="Y39">
-        <v>2142.0332598060299</v>
+        <v>2.1420332598060399</v>
       </c>
       <c r="Z39" s="4"/>
       <c r="AA39" s="4"/>
@@ -5222,76 +5222,76 @@
         <v>0.38541666666666702</v>
       </c>
       <c r="B40">
-        <v>15832.7612535716</v>
+        <v>15.832761253571601</v>
       </c>
       <c r="C40">
-        <v>5203.9769651407696</v>
+        <v>5.2039769651407699</v>
       </c>
       <c r="D40">
-        <v>21099.0938838041</v>
+        <v>21.099093883804098</v>
       </c>
       <c r="E40">
-        <v>6934.93679328299</v>
+        <v>6.93493679328299</v>
       </c>
       <c r="F40">
-        <v>4246.9318745959599</v>
+        <v>4.2469318745959601</v>
       </c>
       <c r="G40">
-        <v>1395.8990029571601</v>
+        <v>1.3958990029571601</v>
       </c>
       <c r="H40">
-        <v>10457.90501002</v>
+        <v>10.457905010019999</v>
       </c>
       <c r="I40">
-        <v>3437.34715026398</v>
+        <v>3.4373471502639799</v>
       </c>
       <c r="J40">
-        <v>4653.4973146292496</v>
+        <v>4.6534973146292504</v>
       </c>
       <c r="K40">
-        <v>1529.53060081116</v>
+        <v>1.52953060081116</v>
       </c>
       <c r="L40">
-        <v>16739.4705511022</v>
+        <v>16.739470551102201</v>
       </c>
       <c r="M40">
-        <v>5501.9978992569504</v>
+        <v>5.50199789925695</v>
       </c>
       <c r="N40">
-        <v>23560.460837675299</v>
+        <v>23.560460837675301</v>
       </c>
       <c r="O40">
-        <v>7743.9489880329702</v>
+        <v>7.7439489880329697</v>
       </c>
       <c r="P40">
-        <v>13854.0458917835</v>
+        <v>13.8540458917835</v>
       </c>
       <c r="Q40">
-        <v>4553.6046770477797</v>
+        <v>4.5536046770477796</v>
       </c>
       <c r="R40">
-        <v>2048.8559032257999</v>
+        <v>2.0488559032258</v>
       </c>
       <c r="S40">
-        <v>673.42636919220502</v>
+        <v>0.673426369192205</v>
       </c>
       <c r="T40">
-        <v>9552.8483326653295</v>
+        <v>9.5528483326653308</v>
       </c>
       <c r="U40">
-        <v>3139.86940613149</v>
+        <v>3.1398694061314898</v>
       </c>
       <c r="V40">
-        <v>5003.1817741935402</v>
+        <v>5.00318177419354</v>
       </c>
       <c r="W40">
-        <v>1644.4663244979999</v>
+        <v>1.644466324498</v>
       </c>
       <c r="X40">
-        <v>5706.1482056451596</v>
+        <v>5.7061482056451602</v>
       </c>
       <c r="Y40">
-        <v>1875.5202169904501</v>
+        <v>1.8755202169904499</v>
       </c>
       <c r="Z40" s="4"/>
       <c r="AA40" s="4"/>
@@ -5346,76 +5346,76 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B41">
-        <v>16346.109204893601</v>
+        <v>16.346109204893601</v>
       </c>
       <c r="C41">
-        <v>5372.7062771664496</v>
+        <v>5.3727062771664498</v>
       </c>
       <c r="D41">
-        <v>22130.279965900299</v>
+        <v>22.1302799659003</v>
       </c>
       <c r="E41">
-        <v>7273.8712679496903</v>
+        <v>7.2738712679496897</v>
       </c>
       <c r="F41">
-        <v>3830.4333110980001</v>
+        <v>3.830433311098</v>
       </c>
       <c r="G41">
-        <v>1259.00254530555</v>
+        <v>1.25900254530555</v>
       </c>
       <c r="H41">
-        <v>10953.492384769501</v>
+        <v>10.9534923847695</v>
       </c>
       <c r="I41">
-        <v>3600.23884307146</v>
+        <v>3.6002388430714598</v>
       </c>
       <c r="J41">
-        <v>4874.0208817635203</v>
+        <v>4.8740208817635198</v>
       </c>
       <c r="K41">
-        <v>1602.01319214553</v>
+        <v>1.6020131921455301</v>
       </c>
       <c r="L41">
-        <v>17532.733662324601</v>
+        <v>17.532733662324599</v>
       </c>
       <c r="M41">
-        <v>5762.7308751404998</v>
+        <v>5.7627308751405097</v>
       </c>
       <c r="N41">
-        <v>24676.962366733402</v>
+        <v>24.676962366733399</v>
       </c>
       <c r="O41">
-        <v>8110.9252940422703</v>
+        <v>8.1109252940422696</v>
       </c>
       <c r="P41">
-        <v>14510.5722444889</v>
+        <v>14.5105722444889</v>
       </c>
       <c r="Q41">
-        <v>4769.3944538131</v>
+        <v>4.7693944538131001</v>
       </c>
       <c r="R41">
-        <v>1748.5777741935401</v>
+        <v>1.74857777419354</v>
       </c>
       <c r="S41">
-        <v>574.72972104645396</v>
+        <v>0.57472972104645403</v>
       </c>
       <c r="T41">
-        <v>10005.546174348599</v>
+        <v>10.0055461743486</v>
       </c>
       <c r="U41">
-        <v>3288.66399114159</v>
+        <v>3.2886639911415898</v>
       </c>
       <c r="V41">
-        <v>4269.9208064516097</v>
+        <v>4.2699208064516103</v>
       </c>
       <c r="W41">
-        <v>1403.4550994531501</v>
+        <v>1.4034550994531501</v>
       </c>
       <c r="X41">
-        <v>4869.8612298387097</v>
+        <v>4.8698612298387101</v>
       </c>
       <c r="Y41">
-        <v>1600.64598067477</v>
+        <v>1.6006459806747699</v>
       </c>
       <c r="Z41" s="4"/>
       <c r="AA41" s="4"/>
@@ -5470,76 +5470,76 @@
         <v>0.40625</v>
       </c>
       <c r="B42">
-        <v>16731.2526687891</v>
+        <v>16.7312526687891</v>
       </c>
       <c r="C42">
-        <v>5499.2968119624402</v>
+        <v>5.4992968119624397</v>
       </c>
       <c r="D42">
-        <v>23023.793724547901</v>
+        <v>23.0237937245479</v>
       </c>
       <c r="E42">
-        <v>7567.5550381757503</v>
+        <v>7.5675550381757501</v>
       </c>
       <c r="F42">
-        <v>3473.6377439152402</v>
+        <v>3.4736377439152402</v>
       </c>
       <c r="G42">
-        <v>1141.7295135743</v>
+        <v>1.1417295135743</v>
       </c>
       <c r="H42">
-        <v>11337.825450901801</v>
+        <v>11.3378254509018</v>
       </c>
       <c r="I42">
-        <v>3726.5630130037998</v>
+        <v>3.7265630130037999</v>
       </c>
       <c r="J42">
-        <v>5045.0391583166302</v>
+        <v>5.0450391583166301</v>
       </c>
       <c r="K42">
-        <v>1658.2241813436201</v>
+        <v>1.65822418134362</v>
       </c>
       <c r="L42">
-        <v>18147.917299599201</v>
+        <v>18.1479172995992</v>
       </c>
       <c r="M42">
-        <v>5964.93195847877</v>
+        <v>5.9649319584787701</v>
       </c>
       <c r="N42">
-        <v>25542.820695390699</v>
+        <v>25.542820695390699</v>
       </c>
       <c r="O42">
-        <v>8395.5191640086596</v>
+        <v>8.3955191640086593</v>
       </c>
       <c r="P42">
-        <v>15019.7151302605</v>
+        <v>15.019715130260501</v>
       </c>
       <c r="Q42">
-        <v>4936.7416276311096</v>
+        <v>4.9367416276311102</v>
       </c>
       <c r="R42">
-        <v>1493.96932258064</v>
+        <v>1.4939693225806401</v>
       </c>
       <c r="S42">
-        <v>491.04396995709101</v>
+        <v>0.49104396995709099</v>
       </c>
       <c r="T42">
-        <v>10356.6179699398</v>
+        <v>10.3566179699398</v>
       </c>
       <c r="U42">
-        <v>3404.0557101290201</v>
+        <v>3.4040557101290201</v>
       </c>
       <c r="V42">
-        <v>3648.18241935483</v>
+        <v>3.6481824193548298</v>
       </c>
       <c r="W42">
-        <v>1199.0995740348999</v>
+        <v>1.1990995740349</v>
       </c>
       <c r="X42">
-        <v>4160.76618951612</v>
+        <v>4.1607661895161199</v>
       </c>
       <c r="Y42">
-        <v>1367.5777118595699</v>
+        <v>1.36757771185957</v>
       </c>
       <c r="Z42" s="4"/>
       <c r="AA42" s="4"/>
@@ -5594,76 +5594,76 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B43">
-        <v>16998.570064289801</v>
+        <v>16.998570064289801</v>
       </c>
       <c r="C43">
-        <v>5587.1597909013199</v>
+        <v>5.5871597909013202</v>
       </c>
       <c r="D43">
-        <v>23762.682086398701</v>
+        <v>23.762682086398701</v>
       </c>
       <c r="E43">
-        <v>7810.4158982177696</v>
+        <v>7.8104158982177703</v>
       </c>
       <c r="F43">
-        <v>3239.4168677273901</v>
+        <v>3.2394168677273898</v>
       </c>
       <c r="G43">
-        <v>1064.74483447029</v>
+        <v>1.0647448344702899</v>
       </c>
       <c r="H43">
-        <v>11600.7901803607</v>
+        <v>11.600790180360701</v>
       </c>
       <c r="I43">
-        <v>3812.9953397996001</v>
+        <v>3.8129953397995999</v>
       </c>
       <c r="J43">
-        <v>5162.0516633266498</v>
+        <v>5.1620516633266504</v>
       </c>
       <c r="K43">
-        <v>1696.6843318475801</v>
+        <v>1.6966843318475799</v>
       </c>
       <c r="L43">
-        <v>18568.8324198396</v>
+        <v>18.568832419839602</v>
       </c>
       <c r="M43">
-        <v>6103.2800681312601</v>
+        <v>6.1032800681312596</v>
       </c>
       <c r="N43">
-        <v>26135.250078156299</v>
+        <v>26.1352500781563</v>
       </c>
       <c r="O43">
-        <v>8590.2412855646198</v>
+        <v>8.5902412855646197</v>
       </c>
       <c r="P43">
-        <v>15368.076052104199</v>
+        <v>15.3680760521042</v>
       </c>
       <c r="Q43">
-        <v>5051.2423255065796</v>
+        <v>5.0512423255065801</v>
       </c>
       <c r="R43">
-        <v>1326.1332580645101</v>
+        <v>1.32613325806451</v>
       </c>
       <c r="S43">
-        <v>435.878923274866</v>
+        <v>0.43587892327486599</v>
       </c>
       <c r="T43">
-        <v>10596.824987975901</v>
+        <v>10.5968249879759</v>
       </c>
       <c r="U43">
-        <v>3483.0079389098901</v>
+        <v>3.48300793890989</v>
       </c>
       <c r="V43">
-        <v>3238.3369354838701</v>
+        <v>3.2383369354838698</v>
       </c>
       <c r="W43">
-        <v>1064.3898779071701</v>
+        <v>1.0643898779071701</v>
       </c>
       <c r="X43">
-        <v>3693.3358266128998</v>
+        <v>3.6933358266129002</v>
       </c>
       <c r="Y43">
-        <v>1213.94078129529</v>
+        <v>1.21394078129529</v>
       </c>
       <c r="Z43" s="4"/>
       <c r="AA43" s="4"/>
@@ -5718,76 +5718,76 @@
         <v>0.42708333333333298</v>
       </c>
       <c r="B44">
-        <v>17191.4189999999</v>
+        <v>17.191419</v>
       </c>
       <c r="C44">
-        <v>5650.5461707698996</v>
+        <v>5.6505461707698998</v>
       </c>
       <c r="D44">
-        <v>24375.4720451965</v>
+        <v>24.375472045196499</v>
       </c>
       <c r="E44">
-        <v>8011.8302174878099</v>
+        <v>8.0118302174878107</v>
       </c>
       <c r="F44">
-        <v>3121.4312500000001</v>
+        <v>3.1214312500000001</v>
       </c>
       <c r="G44">
-        <v>1025.96483728359</v>
+        <v>1.0259648372835899</v>
       </c>
       <c r="H44">
-        <v>11776.1</v>
+        <v>11.7761</v>
       </c>
       <c r="I44">
-        <v>3870.6168909968101</v>
+        <v>3.8706168909968102</v>
       </c>
       <c r="J44">
-        <v>5240.0600000000004</v>
+        <v>5.2400599999999997</v>
       </c>
       <c r="K44">
-        <v>1722.32443218355</v>
+        <v>1.72232443218355</v>
       </c>
       <c r="L44">
-        <v>18849.442500000001</v>
+        <v>18.849442499999999</v>
       </c>
       <c r="M44">
-        <v>6195.5121412329299</v>
+        <v>6.1955121412329301</v>
       </c>
       <c r="N44">
-        <v>26530.203000000001</v>
+        <v>26.530203</v>
       </c>
       <c r="O44">
-        <v>8720.0560332685909</v>
+        <v>8.7200560332685892</v>
       </c>
       <c r="P44">
-        <v>15600.3166666666</v>
+        <v>15.6003166666666</v>
       </c>
       <c r="Q44">
-        <v>5127.5761240902302</v>
+        <v>5.12757612409023</v>
       </c>
       <c r="R44">
-        <v>1238.79</v>
+        <v>1.2387900000000001</v>
       </c>
       <c r="S44">
-        <v>407.170582654523</v>
+        <v>0.40717058265452399</v>
       </c>
       <c r="T44">
-        <v>10756.963</v>
+        <v>10.756963000000001</v>
       </c>
       <c r="U44">
-        <v>3535.6427580971299</v>
+        <v>3.5356427580971301</v>
       </c>
       <c r="V44">
-        <v>3025.05</v>
+        <v>3.0250499999999998</v>
       </c>
       <c r="W44">
-        <v>994.28585237131995</v>
+        <v>0.99428585237131994</v>
       </c>
       <c r="X44">
-        <v>3450.0812500000002</v>
+        <v>3.4500812500000002</v>
       </c>
       <c r="Y44">
-        <v>1133.98686845062</v>
+        <v>1.13398686845062</v>
       </c>
       <c r="Z44" s="4"/>
       <c r="AA44" s="4"/>
@@ -5842,76 +5842,76 @@
         <v>0.4375</v>
       </c>
       <c r="B45">
-        <v>17382.669042375001</v>
+        <v>17.382669042374999</v>
       </c>
       <c r="C45">
-        <v>5713.4070198133704</v>
+        <v>5.7134070198133697</v>
       </c>
       <c r="D45">
-        <v>24919.550091733799</v>
+        <v>24.9195500917338</v>
       </c>
       <c r="E45">
-        <v>8190.6600233613799</v>
+        <v>8.1906600233613798</v>
       </c>
       <c r="F45">
-        <v>3094.78021862272</v>
+        <v>3.09478021862272</v>
       </c>
       <c r="G45">
-        <v>1017.20506688325</v>
+        <v>1.01720506688325</v>
       </c>
       <c r="H45">
-        <v>11924.4390781563</v>
+        <v>11.924439078156301</v>
       </c>
       <c r="I45">
-        <v>3919.3735881636699</v>
+        <v>3.91937358816367</v>
       </c>
       <c r="J45">
-        <v>5306.06705410821</v>
+        <v>5.30606705410821</v>
       </c>
       <c r="K45">
-        <v>1744.0199016986001</v>
+        <v>1.7440199016986</v>
       </c>
       <c r="L45">
-        <v>19086.8817985971</v>
+        <v>19.086881798597101</v>
       </c>
       <c r="M45">
-        <v>6273.5546646266403</v>
+        <v>6.2735546646266398</v>
       </c>
       <c r="N45">
-        <v>26864.393933867701</v>
+        <v>26.864393933867699</v>
       </c>
       <c r="O45">
-        <v>8829.8992813257901</v>
+        <v>8.8298992813257904</v>
       </c>
       <c r="P45">
-        <v>15796.8279559118</v>
+        <v>15.7968279559118</v>
       </c>
       <c r="Q45">
-        <v>5192.1662613533199</v>
+        <v>5.1921662613533197</v>
       </c>
       <c r="R45">
-        <v>1211.95906451612</v>
+        <v>1.21195906451612</v>
       </c>
       <c r="S45">
-        <v>398.35168063389602</v>
+        <v>0.39835168063389598</v>
       </c>
       <c r="T45">
-        <v>10892.4643947895</v>
+        <v>10.892464394789499</v>
       </c>
       <c r="U45">
-        <v>3580.1799127940399</v>
+        <v>3.5801799127940401</v>
       </c>
       <c r="V45">
-        <v>2959.5304838709599</v>
+        <v>2.9595304838709602</v>
       </c>
       <c r="W45">
-        <v>972.750628840697</v>
+        <v>0.97275062884069696</v>
       </c>
       <c r="X45">
-        <v>3375.35598790322</v>
+        <v>3.37535598790322</v>
       </c>
       <c r="Y45">
-        <v>1109.42586254408</v>
+        <v>1.10942586254408</v>
       </c>
       <c r="Z45" s="4"/>
       <c r="AA45" s="4"/>
@@ -5966,76 +5966,76 @@
         <v>0.44791666666666702</v>
       </c>
       <c r="B46">
-        <v>17627.370149912698</v>
+        <v>17.6273701499127</v>
       </c>
       <c r="C46">
-        <v>5793.8363843806601</v>
+        <v>5.7938363843806604</v>
       </c>
       <c r="D46">
-        <v>25440.674090614801</v>
+        <v>25.440674090614799</v>
       </c>
       <c r="E46">
-        <v>8361.9451986208205</v>
+        <v>8.3619451986208198</v>
       </c>
       <c r="F46">
-        <v>3135.8564027247999</v>
+        <v>3.1358564027248002</v>
       </c>
       <c r="G46">
-        <v>1030.70615569901</v>
+        <v>1.03070615569901</v>
       </c>
       <c r="H46">
-        <v>12093.0062124248</v>
+        <v>12.0930062124248</v>
       </c>
       <c r="I46">
-        <v>3974.7789258532898</v>
+        <v>3.9747789258532902</v>
       </c>
       <c r="J46">
-        <v>5381.0750701402803</v>
+        <v>5.3810750701402803</v>
       </c>
       <c r="K46">
-        <v>1768.67384432934</v>
+        <v>1.7686738443293399</v>
       </c>
       <c r="L46">
-        <v>19356.699183366702</v>
+        <v>19.3566991833667</v>
       </c>
       <c r="M46">
-        <v>6362.23935030132</v>
+        <v>6.3622393503013202</v>
       </c>
       <c r="N46">
-        <v>27244.156358717399</v>
+        <v>27.244156358717401</v>
       </c>
       <c r="O46">
-        <v>8954.7211541180695</v>
+        <v>8.9547211541180705</v>
       </c>
       <c r="P46">
-        <v>16020.1362391449</v>
+        <v>16.0201362391449</v>
       </c>
       <c r="Q46">
-        <v>5265.5641446068303</v>
+        <v>5.26556414460683</v>
       </c>
       <c r="R46">
-        <v>1227.37258064516</v>
+        <v>1.2273725806451601</v>
       </c>
       <c r="S46">
-        <v>403.417858390427</v>
+        <v>0.40341785839042699</v>
       </c>
       <c r="T46">
-        <v>11046.443252505</v>
+        <v>11.046443252505</v>
       </c>
       <c r="U46">
-        <v>3630.7903158587001</v>
+        <v>3.6307903158586998</v>
       </c>
       <c r="V46">
-        <v>2997.1693548387002</v>
+        <v>2.9971693548387002</v>
       </c>
       <c r="W46">
-        <v>985.12192746467099</v>
+        <v>0.98512192746467098</v>
       </c>
       <c r="X46">
-        <v>3418.2832661290299</v>
+        <v>3.4182832661290301</v>
       </c>
       <c r="Y46">
-        <v>1123.5353765755001</v>
+        <v>1.1235353765755001</v>
       </c>
       <c r="Z46" s="4"/>
       <c r="AA46" s="4"/>
@@ -6090,76 +6090,76 @@
         <v>0.45833333333333298</v>
       </c>
       <c r="B47">
-        <v>17966.1012646583</v>
+        <v>17.966101264658299</v>
       </c>
       <c r="C47">
-        <v>5905.1719177270697</v>
+        <v>5.9051719177270696</v>
       </c>
       <c r="D47">
-        <v>25970.368954084799</v>
+        <v>25.970368954084801</v>
       </c>
       <c r="E47">
-        <v>8536.0474808382896</v>
+        <v>8.53604748083829</v>
       </c>
       <c r="F47">
-        <v>3219.1380978893199</v>
+        <v>3.2191380978893198</v>
       </c>
       <c r="G47">
-        <v>1058.0795251519401</v>
+        <v>1.0580795251519399</v>
       </c>
       <c r="H47">
-        <v>12318.886172344601</v>
+        <v>12.3188861723446</v>
       </c>
       <c r="I47">
-        <v>4049.02207835738</v>
+        <v>4.04902207835738</v>
       </c>
       <c r="J47">
-        <v>5481.5858116232403</v>
+        <v>5.4815858116232397</v>
       </c>
       <c r="K47">
-        <v>1801.71012745453</v>
+        <v>1.80171012745453</v>
       </c>
       <c r="L47">
-        <v>19718.254478957901</v>
+        <v>19.718254478957899</v>
       </c>
       <c r="M47">
-        <v>6481.0768291053901</v>
+        <v>6.4810768291053904</v>
       </c>
       <c r="N47">
-        <v>27753.038008015999</v>
+        <v>27.753038008015999</v>
       </c>
       <c r="O47">
-        <v>9121.9824636597295</v>
+        <v>9.1219824636597302</v>
       </c>
       <c r="P47">
-        <v>16319.369338677299</v>
+        <v>16.319369338677301</v>
       </c>
       <c r="Q47">
-        <v>5363.9173081665404</v>
+        <v>5.3639173081665401</v>
       </c>
       <c r="R47">
-        <v>1266.1918064516101</v>
+        <v>1.26619180645161</v>
       </c>
       <c r="S47">
-        <v>416.177120888356</v>
+        <v>0.41617712088835601</v>
       </c>
       <c r="T47">
-        <v>11252.7749218436</v>
+        <v>11.252774921843599</v>
       </c>
       <c r="U47">
-        <v>3698.60825596534</v>
+        <v>3.6986082559653402</v>
       </c>
       <c r="V47">
-        <v>3091.9635483870902</v>
+        <v>3.0919635483870902</v>
       </c>
       <c r="W47">
-        <v>1016.27927214727</v>
+        <v>1.01627927214727</v>
       </c>
       <c r="X47">
-        <v>3526.39641129032</v>
+        <v>3.5263964112903201</v>
       </c>
       <c r="Y47">
-        <v>1159.0704489509101</v>
+        <v>1.15907044895091</v>
       </c>
       <c r="Z47" s="4"/>
       <c r="AA47" s="4"/>
@@ -6214,76 +6214,76 @@
         <v>0.46875</v>
       </c>
       <c r="B48">
-        <v>18353.636439621099</v>
+        <v>18.353636439621098</v>
       </c>
       <c r="C48">
-        <v>6032.5485699350602</v>
+        <v>6.0325485699350603</v>
       </c>
       <c r="D48">
-        <v>26481.667176574701</v>
+        <v>26.4816671765747</v>
       </c>
       <c r="E48">
-        <v>8704.1030795769493</v>
+        <v>8.7041030795769494</v>
       </c>
       <c r="F48">
-        <v>3310.28003793878</v>
+        <v>3.3102800379387798</v>
       </c>
       <c r="G48">
-        <v>1088.0364321613599</v>
+        <v>1.08803643216136</v>
       </c>
       <c r="H48">
-        <v>12578.479559118199</v>
+        <v>12.5784795591182</v>
       </c>
       <c r="I48">
-        <v>4134.3462983993904</v>
+        <v>4.1343462983993904</v>
       </c>
       <c r="J48">
-        <v>5597.0981563126197</v>
+        <v>5.5970981563126196</v>
       </c>
       <c r="K48">
-        <v>1839.6771991058799</v>
+        <v>1.83967719910587</v>
       </c>
       <c r="L48">
-        <v>20133.773251503</v>
+        <v>20.133773251503001</v>
       </c>
       <c r="M48">
-        <v>6617.6512450443897</v>
+        <v>6.6176512450443896</v>
       </c>
       <c r="N48">
-        <v>28337.872142284501</v>
+        <v>28.3378721422845</v>
       </c>
       <c r="O48">
-        <v>9314.2081477598294</v>
+        <v>9.31420814775983</v>
       </c>
       <c r="P48">
-        <v>16663.264094856298</v>
+        <v>16.663264094856299</v>
       </c>
       <c r="Q48">
-        <v>5476.9500483769398</v>
+        <v>5.4769500483769402</v>
       </c>
       <c r="R48">
-        <v>1307.8653870967701</v>
+        <v>1.30786538709677</v>
       </c>
       <c r="S48">
-        <v>429.87456445230998</v>
+        <v>0.42987456445230998</v>
       </c>
       <c r="T48">
-        <v>11489.902362725399</v>
+        <v>11.489902362725401</v>
       </c>
       <c r="U48">
-        <v>3776.54827668492</v>
+        <v>3.7765482766849199</v>
       </c>
       <c r="V48">
-        <v>3193.7279032258002</v>
+        <v>3.1937279032257999</v>
       </c>
       <c r="W48">
-        <v>1049.72759805654</v>
+        <v>1.0497275980565399</v>
       </c>
       <c r="X48">
-        <v>3642.45905241935</v>
+        <v>3.6424590524193499</v>
       </c>
       <c r="Y48">
-        <v>1197.2183942951001</v>
+        <v>1.1972183942951</v>
       </c>
       <c r="Z48" s="4"/>
       <c r="AA48" s="4"/>
@@ -6338,76 +6338,76 @@
         <v>0.47916666666666702</v>
       </c>
       <c r="B49">
-        <v>18746.4517439394</v>
+        <v>18.746451743939399</v>
       </c>
       <c r="C49">
-        <v>6161.6607167354896</v>
+        <v>6.16166071673549</v>
       </c>
       <c r="D49">
-        <v>26954.8176911552</v>
+        <v>26.954817691155199</v>
       </c>
       <c r="E49">
-        <v>8859.6201330767308</v>
+        <v>8.8596201330767297</v>
       </c>
       <c r="F49">
-        <v>3379.3743558891902</v>
+        <v>3.37937435588919</v>
       </c>
       <c r="G49">
-        <v>1110.7466362298301</v>
+        <v>1.1107466362298299</v>
       </c>
       <c r="H49">
-        <v>12848.186973947801</v>
+        <v>12.848186973947801</v>
       </c>
       <c r="I49">
-        <v>4222.9948387027898</v>
+        <v>4.22299483870278</v>
       </c>
       <c r="J49">
-        <v>5717.1109819639196</v>
+        <v>5.7171109819639199</v>
       </c>
       <c r="K49">
-        <v>1879.1235073150599</v>
+        <v>1.8791235073150601</v>
       </c>
       <c r="L49">
-        <v>20565.481067134198</v>
+        <v>20.565481067134201</v>
       </c>
       <c r="M49">
-        <v>6759.54674212388</v>
+        <v>6.75954674212388</v>
       </c>
       <c r="N49">
-        <v>28945.492022044</v>
+        <v>28.945492022044</v>
       </c>
       <c r="O49">
-        <v>9513.9231442274795</v>
+        <v>9.5139231442274799</v>
       </c>
       <c r="P49">
-        <v>17020.557348029299</v>
+        <v>17.0205573480293</v>
       </c>
       <c r="Q49">
-        <v>5594.38666158256</v>
+        <v>5.5943866615825604</v>
       </c>
       <c r="R49">
-        <v>1334.6963225806401</v>
+        <v>1.3346963225806401</v>
       </c>
       <c r="S49">
-        <v>438.69346647293798</v>
+        <v>0.438693466472938</v>
       </c>
       <c r="T49">
-        <v>11736.268535070099</v>
+        <v>11.736268535070099</v>
       </c>
       <c r="U49">
-        <v>3857.52492158837</v>
+        <v>3.8575249215883698</v>
       </c>
       <c r="V49">
-        <v>3259.2474193548301</v>
+        <v>3.2592474193548302</v>
       </c>
       <c r="W49">
-        <v>1071.26282158716</v>
+        <v>1.07126282158716</v>
       </c>
       <c r="X49">
-        <v>3717.1843145161201</v>
+        <v>3.7171843145161199</v>
       </c>
       <c r="Y49">
-        <v>1221.7794002016301</v>
+        <v>1.22177940020163</v>
       </c>
       <c r="Z49" s="4"/>
       <c r="AA49" s="4"/>
@@ -6462,76 +6462,76 @@
         <v>0.48958333333333298</v>
       </c>
       <c r="B50">
-        <v>19057.610197394701</v>
+        <v>19.057610197394698</v>
       </c>
       <c r="C50">
-        <v>6263.9335545782797</v>
+        <v>6.2639335545782799</v>
       </c>
       <c r="D50">
-        <v>27321.857722278</v>
+        <v>27.321857722278001</v>
       </c>
       <c r="E50">
-        <v>8980.2603572711705</v>
+        <v>8.9802603572711703</v>
       </c>
       <c r="F50">
-        <v>3390.7701841182302</v>
+        <v>3.3907701841182298</v>
       </c>
       <c r="G50">
-        <v>1114.4922638340699</v>
+        <v>1.11449226383407</v>
       </c>
       <c r="H50">
-        <v>13074.0669338677</v>
+        <v>13.0740669338677</v>
       </c>
       <c r="I50">
-        <v>4297.23799120688</v>
+        <v>4.2972379912068801</v>
       </c>
       <c r="J50">
-        <v>5817.6217234468904</v>
+        <v>5.8176217234468899</v>
       </c>
       <c r="K50">
-        <v>1912.1597904402499</v>
+        <v>1.9121597904402501</v>
       </c>
       <c r="L50">
-        <v>20927.036362725401</v>
+        <v>20.927036362725399</v>
       </c>
       <c r="M50">
-        <v>6878.3842209279401</v>
+        <v>6.8783842209279404</v>
       </c>
       <c r="N50">
-        <v>29454.373671342601</v>
+        <v>29.454373671342601</v>
       </c>
       <c r="O50">
-        <v>9681.1844537691395</v>
+        <v>9.6811844537691396</v>
       </c>
       <c r="P50">
-        <v>17319.7904475617</v>
+        <v>17.319790447561701</v>
       </c>
       <c r="Q50">
-        <v>5692.7398251422601</v>
+        <v>5.6927398251422598</v>
       </c>
       <c r="R50">
-        <v>1327.2750000000001</v>
+        <v>1.327275</v>
       </c>
       <c r="S50">
-        <v>436.25419570127502</v>
+        <v>0.43625419570127499</v>
       </c>
       <c r="T50">
-        <v>11942.6002044088</v>
+        <v>11.9426002044088</v>
       </c>
       <c r="U50">
-        <v>3925.34286169502</v>
+        <v>3.9253428616950199</v>
       </c>
       <c r="V50">
-        <v>3241.125</v>
+        <v>3.2411249999999998</v>
       </c>
       <c r="W50">
-        <v>1065.3062703978401</v>
+        <v>1.06530627039784</v>
       </c>
       <c r="X50">
-        <v>3696.515625</v>
+        <v>3.696515625</v>
       </c>
       <c r="Y50">
-        <v>1214.9859304828101</v>
+        <v>1.2149859304828099</v>
       </c>
       <c r="Z50" s="4"/>
       <c r="AA50" s="4"/>
@@ -6586,76 +6586,76 @@
         <v>0.5</v>
       </c>
       <c r="B51">
-        <v>19256.071906975201</v>
+        <v>19.256071906975201</v>
       </c>
       <c r="C51">
-        <v>6329.1647640040001</v>
+        <v>6.3291647640040001</v>
       </c>
       <c r="D51">
-        <v>27572.1319923913</v>
+        <v>27.572131992391299</v>
       </c>
       <c r="E51">
-        <v>9062.5215317926504</v>
+        <v>9.0625215317926493</v>
       </c>
       <c r="F51">
-        <v>3323.2315433285899</v>
+        <v>3.3232315433285899</v>
       </c>
       <c r="G51">
-        <v>1092.29338612113</v>
+        <v>1.0922933861211299</v>
       </c>
       <c r="H51">
-        <v>13239.262725450901</v>
+        <v>13.239262725450899</v>
       </c>
       <c r="I51">
-        <v>4351.5352221427001</v>
+        <v>4.3515352221426999</v>
       </c>
       <c r="J51">
-        <v>5891.1295791583098</v>
+        <v>5.89112957915831</v>
       </c>
       <c r="K51">
-        <v>1936.32065421838</v>
+        <v>1.93632065421838</v>
       </c>
       <c r="L51">
-        <v>21191.457399799601</v>
+        <v>21.191457399799599</v>
       </c>
       <c r="M51">
-        <v>6965.2952128891302</v>
+        <v>6.9652952128891297</v>
       </c>
       <c r="N51">
-        <v>29826.540847695302</v>
+        <v>29.826540847695298</v>
       </c>
       <c r="O51">
-        <v>9803.5098891055695</v>
+        <v>9.8035098891055696</v>
       </c>
       <c r="P51">
-        <v>17538.6325651302</v>
+        <v>17.5386325651302</v>
       </c>
       <c r="Q51">
-        <v>5764.6697507306999</v>
+        <v>5.7646697507307003</v>
       </c>
       <c r="R51">
-        <v>1273.04225806451</v>
+        <v>1.27304225806451</v>
       </c>
       <c r="S51">
-        <v>418.42875544681402</v>
+        <v>0.41842875544681402</v>
       </c>
       <c r="T51">
-        <v>12093.4994849699</v>
+        <v>12.0934994849699</v>
       </c>
       <c r="U51">
-        <v>3974.9410566983802</v>
+        <v>3.97494105669838</v>
       </c>
       <c r="V51">
-        <v>3108.6919354838701</v>
+        <v>3.1086919354838698</v>
       </c>
       <c r="W51">
-        <v>1021.77762709126</v>
+        <v>1.02177762709126</v>
       </c>
       <c r="X51">
-        <v>3545.4752016129</v>
+        <v>3.5454752016128999</v>
       </c>
       <c r="Y51">
-        <v>1165.34134407598</v>
+        <v>1.1653413440759799</v>
       </c>
       <c r="Z51" s="4"/>
       <c r="AA51" s="4"/>
@@ -6710,76 +6710,76 @@
         <v>0.51041666666666696</v>
       </c>
       <c r="B52">
-        <v>19298.194301603198</v>
+        <v>19.2981943016032</v>
       </c>
       <c r="C52">
-        <v>6343.0097255902801</v>
+        <v>6.3430097255902798</v>
       </c>
       <c r="D52">
-        <v>27654.4435151168</v>
+        <v>27.6544435151168</v>
       </c>
       <c r="E52">
-        <v>9089.5760209855998</v>
+        <v>9.0895760209856</v>
       </c>
       <c r="F52">
-        <v>3194.2928193887701</v>
+        <v>3.1942928193887701</v>
       </c>
       <c r="G52">
-        <v>1049.9132770200599</v>
+        <v>1.0499132770200601</v>
       </c>
       <c r="H52">
-        <v>13306.689579158299</v>
+        <v>13.3066895791583</v>
       </c>
       <c r="I52">
-        <v>4373.6973572185498</v>
+        <v>4.3736973572185498</v>
       </c>
       <c r="J52">
-        <v>5921.1327855711397</v>
+        <v>5.9211327855711398</v>
       </c>
       <c r="K52">
-        <v>1946.1822312706799</v>
+        <v>1.94618223127068</v>
       </c>
       <c r="L52">
-        <v>21299.384353707399</v>
+        <v>21.299384353707399</v>
       </c>
       <c r="M52">
-        <v>7000.7690871589903</v>
+        <v>7.000769087159</v>
       </c>
       <c r="N52">
-        <v>29978.445817635198</v>
+        <v>29.978445817635201</v>
       </c>
       <c r="O52">
-        <v>9853.4386382224802</v>
+        <v>9.8534386382224799</v>
       </c>
       <c r="P52">
-        <v>17627.955878423501</v>
+        <v>17.627955878423499</v>
       </c>
       <c r="Q52">
-        <v>5794.0289040321104</v>
+        <v>5.7940289040321096</v>
       </c>
       <c r="R52">
-        <v>1185.6990000000001</v>
+        <v>1.1856990000000001</v>
       </c>
       <c r="S52">
-        <v>389.72041482647199</v>
+        <v>0.38972041482647202</v>
       </c>
       <c r="T52">
-        <v>12155.0910280561</v>
+        <v>12.1550910280561</v>
       </c>
       <c r="U52">
-        <v>3995.1852179242501</v>
+        <v>3.99518521792425</v>
       </c>
       <c r="V52">
-        <v>2895.4050000000002</v>
+        <v>2.8954049999999998</v>
       </c>
       <c r="W52">
-        <v>951.67360155540598</v>
+        <v>0.95167360155540603</v>
       </c>
       <c r="X52">
-        <v>3302.2206249999999</v>
+        <v>3.3022206249999999</v>
       </c>
       <c r="Y52">
-        <v>1085.3874312313101</v>
+        <v>1.0853874312313101</v>
       </c>
       <c r="Z52" s="4"/>
       <c r="AA52" s="4"/>
@@ -6834,76 +6834,76 @@
         <v>0.52083333333333304</v>
       </c>
       <c r="B53">
-        <v>19145.7812618139</v>
+        <v>19.145781261813902</v>
       </c>
       <c r="C53">
-        <v>6292.9139819895599</v>
+        <v>6.2929139819895603</v>
       </c>
       <c r="D53">
-        <v>27512.735938607701</v>
+        <v>27.512735938607701</v>
       </c>
       <c r="E53">
-        <v>9042.9989930036209</v>
+        <v>9.0429989930036196</v>
       </c>
       <c r="F53">
-        <v>3035.68807558665</v>
+        <v>3.0356880755866502</v>
       </c>
       <c r="G53">
-        <v>997.78241872634499</v>
+        <v>0.99778241872634499</v>
       </c>
       <c r="H53">
-        <v>13239.262725450901</v>
+        <v>13.239262725450899</v>
       </c>
       <c r="I53">
-        <v>4351.5352221427001</v>
+        <v>4.3515352221426999</v>
       </c>
       <c r="J53">
-        <v>5891.1295791583098</v>
+        <v>5.89112957915831</v>
       </c>
       <c r="K53">
-        <v>1936.32065421838</v>
+        <v>1.93632065421838</v>
       </c>
       <c r="L53">
-        <v>21191.457399799601</v>
+        <v>21.191457399799599</v>
       </c>
       <c r="M53">
-        <v>6965.2952128891302</v>
+        <v>6.9652952128891297</v>
       </c>
       <c r="N53">
-        <v>29826.540847695302</v>
+        <v>29.826540847695298</v>
       </c>
       <c r="O53">
-        <v>9803.5098891055695</v>
+        <v>9.8035098891055696</v>
       </c>
       <c r="P53">
-        <v>17538.6325651302</v>
+        <v>17.5386325651302</v>
       </c>
       <c r="Q53">
-        <v>5764.6697507306999</v>
+        <v>5.7646697507307003</v>
       </c>
       <c r="R53">
-        <v>1088.08006451612</v>
+        <v>1.0880800645161199</v>
       </c>
       <c r="S53">
-        <v>357.63462236844299</v>
+        <v>0.35763462236844301</v>
       </c>
       <c r="T53">
-        <v>12093.4994849699</v>
+        <v>12.0934994849699</v>
       </c>
       <c r="U53">
-        <v>3974.9410566983802</v>
+        <v>3.97494105669838</v>
       </c>
       <c r="V53">
-        <v>2657.0254838709602</v>
+        <v>2.6570254838709602</v>
       </c>
       <c r="W53">
-        <v>873.322043603564</v>
+        <v>0.87332204360356402</v>
       </c>
       <c r="X53">
-        <v>3030.3478629032202</v>
+        <v>3.0303478629032199</v>
       </c>
       <c r="Y53">
-        <v>996.027175699027</v>
+        <v>0.99602717569902699</v>
       </c>
       <c r="Z53" s="4"/>
       <c r="AA53" s="4"/>
@@ -6958,76 +6958,76 @@
         <v>0.53125</v>
       </c>
       <c r="B54">
-        <v>18787.536281692399</v>
+        <v>18.7875362816924</v>
       </c>
       <c r="C54">
-        <v>6175.1645512634896</v>
+        <v>6.1751645512634896</v>
       </c>
       <c r="D54">
-        <v>27122.284155851099</v>
+        <v>27.122284155851101</v>
       </c>
       <c r="E54">
-        <v>8914.6636981727806</v>
+        <v>8.9146636981727791</v>
       </c>
       <c r="F54">
-        <v>2877.6551632700798</v>
+        <v>2.87765516327008</v>
       </c>
       <c r="G54">
-        <v>945.83951235276402</v>
+        <v>0.94583951235276398</v>
       </c>
       <c r="H54">
-        <v>13020.1254509018</v>
+        <v>13.0201254509018</v>
       </c>
       <c r="I54">
-        <v>4279.5082831461996</v>
+        <v>4.2795082831461997</v>
       </c>
       <c r="J54">
-        <v>5793.6191583166301</v>
+        <v>5.7936191583166297</v>
       </c>
       <c r="K54">
-        <v>1904.2705287984199</v>
+        <v>1.9042705287984201</v>
       </c>
       <c r="L54">
-        <v>20840.694799599201</v>
+        <v>20.840694799599198</v>
       </c>
       <c r="M54">
-        <v>6850.0051215120502</v>
+        <v>6.8500051215120497</v>
       </c>
       <c r="N54">
-        <v>29332.849695390702</v>
+        <v>29.332849695390699</v>
       </c>
       <c r="O54">
-        <v>9641.2414544755993</v>
+        <v>9.6412414544755993</v>
       </c>
       <c r="P54">
-        <v>17248.331796927101</v>
+        <v>17.248331796927101</v>
       </c>
       <c r="Q54">
-        <v>5669.25250250114</v>
+        <v>5.6692525025011404</v>
       </c>
       <c r="R54">
-        <v>1000.7368064516101</v>
+        <v>1.00073680645161</v>
       </c>
       <c r="S54">
-        <v>328.92628174810102</v>
+        <v>0.32892628174810101</v>
       </c>
       <c r="T54">
-        <v>11893.326969939801</v>
+        <v>11.8933269699398</v>
       </c>
       <c r="U54">
-        <v>3909.1475327143198</v>
+        <v>3.9091475327143299</v>
       </c>
       <c r="V54">
-        <v>2443.7385483870898</v>
+        <v>2.4437385483870901</v>
       </c>
       <c r="W54">
-        <v>803.218018067706</v>
+        <v>0.80321801806770599</v>
       </c>
       <c r="X54">
-        <v>2787.0932862903201</v>
+        <v>2.7870932862903199</v>
       </c>
       <c r="Y54">
-        <v>916.07326285435101</v>
+        <v>0.91607326285435098</v>
       </c>
       <c r="Z54" s="4"/>
       <c r="AA54" s="4"/>
@@ -7082,76 +7082,76 @@
         <v>0.54166666666666696</v>
       </c>
       <c r="B55">
-        <v>18200.3596239252</v>
+        <v>18.200359623925198</v>
       </c>
       <c r="C55">
-        <v>5982.1689169233796</v>
+        <v>5.9821689169233796</v>
       </c>
       <c r="D55">
-        <v>26448.0161243078</v>
+        <v>26.448016124307799</v>
       </c>
       <c r="E55">
-        <v>8693.0425135742607</v>
+        <v>8.6930425135742606</v>
       </c>
       <c r="F55">
-        <v>2743.53500577768</v>
+        <v>2.7435350057776802</v>
       </c>
       <c r="G55">
-        <v>901.75634840092505</v>
+        <v>0.901756348400925</v>
       </c>
       <c r="H55">
-        <v>12625.678356713401</v>
+        <v>12.625678356713401</v>
       </c>
       <c r="I55">
-        <v>4149.8597929524904</v>
+        <v>4.1498597929524896</v>
       </c>
       <c r="J55">
-        <v>5618.1004008015998</v>
+        <v>5.6181004008016</v>
       </c>
       <c r="K55">
-        <v>1846.58030304248</v>
+        <v>1.8465803030424801</v>
       </c>
       <c r="L55">
-        <v>20209.322119238401</v>
+        <v>20.209322119238401</v>
       </c>
       <c r="M55">
-        <v>6642.4829570333004</v>
+        <v>6.6424829570332999</v>
       </c>
       <c r="N55">
-        <v>28444.2056212424</v>
+        <v>28.4442056212424</v>
       </c>
       <c r="O55">
-        <v>9349.1582721416707</v>
+        <v>9.3491582721416702</v>
       </c>
       <c r="P55">
-        <v>16725.790414161602</v>
+        <v>16.725790414161601</v>
       </c>
       <c r="Q55">
-        <v>5497.5014556879296</v>
+        <v>5.4975014556879298</v>
       </c>
       <c r="R55">
-        <v>940.22448387096802</v>
+        <v>0.94022448387096802</v>
       </c>
       <c r="S55">
-        <v>309.03684314838699</v>
+        <v>0.30903684314838697</v>
       </c>
       <c r="T55">
-        <v>11533.016442885701</v>
+        <v>11.5330164428857</v>
       </c>
       <c r="U55">
-        <v>3790.7191895430201</v>
+        <v>3.7907191895430201</v>
       </c>
       <c r="V55">
-        <v>2295.9711290322498</v>
+        <v>2.29597112903225</v>
       </c>
       <c r="W55">
-        <v>754.64921606247106</v>
+        <v>0.75464921606247104</v>
       </c>
       <c r="X55">
-        <v>2618.5639717741901</v>
+        <v>2.61856397177419</v>
       </c>
       <c r="Y55">
-        <v>860.68035591621003</v>
+        <v>0.86068035591620995</v>
       </c>
       <c r="Z55" s="4"/>
       <c r="AA55" s="4"/>
@@ -7206,76 +7206,76 @@
         <v>0.55208333333333304</v>
       </c>
       <c r="B56">
-        <v>17477.434167011401</v>
+        <v>17.477434167011399</v>
       </c>
       <c r="C56">
-        <v>5744.5548100066399</v>
+        <v>5.7445548100066404</v>
       </c>
       <c r="D56">
-        <v>25586.9834658037</v>
+        <v>25.586983465803701</v>
       </c>
       <c r="E56">
-        <v>8410.0347646840801</v>
+        <v>8.4100347646840792</v>
       </c>
       <c r="F56">
-        <v>2637.5108549760798</v>
+        <v>2.63751085497608</v>
       </c>
       <c r="G56">
-        <v>866.90789526735102</v>
+        <v>0.86690789526735101</v>
       </c>
       <c r="H56">
-        <v>12123.3482965931</v>
+        <v>12.1233482965931</v>
       </c>
       <c r="I56">
-        <v>3984.7518866374198</v>
+        <v>3.9847518866374201</v>
       </c>
       <c r="J56">
-        <v>5394.5765130260497</v>
+        <v>5.3945765130260499</v>
       </c>
       <c r="K56">
-        <v>1773.11155400287</v>
+        <v>1.7731115540028799</v>
       </c>
       <c r="L56">
-        <v>19405.266312625201</v>
+        <v>19.405266312625201</v>
       </c>
       <c r="M56">
-        <v>6378.20259372276</v>
+        <v>6.3782025937227598</v>
       </c>
       <c r="N56">
-        <v>27312.513595190299</v>
+        <v>27.3125135951903</v>
       </c>
       <c r="O56">
-        <v>8977.18909122068</v>
+        <v>8.97718909122068</v>
       </c>
       <c r="P56">
-        <v>16060.3317301269</v>
+        <v>16.060331730126901</v>
       </c>
       <c r="Q56">
-        <v>5278.77576359247</v>
+        <v>5.2787757635924697</v>
       </c>
       <c r="R56">
-        <v>904.83048387096801</v>
+        <v>0.90483048387096798</v>
       </c>
       <c r="S56">
-        <v>297.40339792968598</v>
+        <v>0.29740339792968601</v>
       </c>
       <c r="T56">
-        <v>11074.1594468937</v>
+        <v>11.074159446893701</v>
       </c>
       <c r="U56">
-        <v>3639.90018841033</v>
+        <v>3.6399001884103299</v>
       </c>
       <c r="V56">
-        <v>2209.54112903225</v>
+        <v>2.20954112903225</v>
       </c>
       <c r="W56">
-        <v>726.24104885186205</v>
+        <v>0.72624104885186203</v>
       </c>
       <c r="X56">
-        <v>2519.9902217741901</v>
+        <v>2.5199902217741901</v>
       </c>
       <c r="Y56">
-        <v>828.28073110333503</v>
+        <v>0.828280731103335</v>
       </c>
       <c r="Z56" s="4"/>
       <c r="AA56" s="4"/>
@@ -7330,76 +7330,76 @@
         <v>0.5625</v>
       </c>
       <c r="B57">
-        <v>16699.458751599901</v>
+        <v>16.699458751599899</v>
       </c>
       <c r="C57">
-        <v>5488.8466567409696</v>
+        <v>5.4888466567409697</v>
       </c>
       <c r="D57">
-        <v>24621.539768115199</v>
+        <v>24.621539768115198</v>
       </c>
       <c r="E57">
-        <v>8092.7087668087597</v>
+        <v>8.0927087668087694</v>
       </c>
       <c r="F57">
-        <v>2555.0940750452501</v>
+        <v>2.55509407504525</v>
       </c>
       <c r="G57">
-        <v>839.81880970406303</v>
+        <v>0.83981880970406297</v>
       </c>
       <c r="H57">
-        <v>11573.819438877699</v>
+        <v>11.573819438877701</v>
       </c>
       <c r="I57">
-        <v>3804.1304857692598</v>
+        <v>3.8041304857692602</v>
       </c>
       <c r="J57">
-        <v>5150.0503807615196</v>
+        <v>5.1500503807615203</v>
       </c>
       <c r="K57">
-        <v>1692.73970102666</v>
+        <v>1.69273970102666</v>
       </c>
       <c r="L57">
-        <v>18525.661638276499</v>
+        <v>18.5256616382765</v>
       </c>
       <c r="M57">
-        <v>6089.0905184233197</v>
+        <v>6.0890905184233199</v>
       </c>
       <c r="N57">
-        <v>26074.488090180301</v>
+        <v>26.074488090180299</v>
       </c>
       <c r="O57">
-        <v>8570.2697859178497</v>
+        <v>8.5702697859178496</v>
       </c>
       <c r="P57">
-        <v>15332.3467267869</v>
+        <v>15.3323467267869</v>
       </c>
       <c r="Q57">
-        <v>5039.4986641860196</v>
+        <v>5.03949866418602</v>
       </c>
       <c r="R57">
-        <v>887.70435483870904</v>
+        <v>0.88770435483870902</v>
       </c>
       <c r="S57">
-        <v>291.77431153354098</v>
+        <v>0.291774311533541</v>
       </c>
       <c r="T57">
-        <v>10572.1883707414</v>
+        <v>10.572188370741401</v>
       </c>
       <c r="U57">
-        <v>3474.9102744195402</v>
+        <v>3.4749102744195399</v>
       </c>
       <c r="V57">
-        <v>2167.72016129032</v>
+        <v>2.1677201612903199</v>
       </c>
       <c r="W57">
-        <v>712.49516149189003</v>
+        <v>0.71249516149188996</v>
       </c>
       <c r="X57">
-        <v>2472.2932459677399</v>
+        <v>2.47229324596774</v>
       </c>
       <c r="Y57">
-        <v>812.603493290654</v>
+        <v>0.81260349329065396</v>
       </c>
       <c r="Z57" s="4"/>
       <c r="AA57" s="4"/>
@@ -7454,76 +7454,76 @@
         <v>0.57291666666666696</v>
       </c>
       <c r="B58">
-        <v>15974.372235115299</v>
+        <v>15.9743722351153</v>
       </c>
       <c r="C58">
-        <v>5250.5222438929704</v>
+        <v>5.25052224389297</v>
       </c>
       <c r="D58">
-        <v>23667.146060514198</v>
+        <v>23.667146060514199</v>
       </c>
       <c r="E58">
-        <v>7779.0147250375803</v>
+        <v>7.7790147250375803</v>
       </c>
       <c r="F58">
-        <v>2491.18729806386</v>
+        <v>2.4911872980638599</v>
       </c>
       <c r="G58">
-        <v>818.81366789707204</v>
+        <v>0.818813667897072</v>
       </c>
       <c r="H58">
-        <v>11058.004008016</v>
+        <v>11.058004008016001</v>
       </c>
       <c r="I58">
-        <v>3634.5901524390301</v>
+        <v>3.6345901524390301</v>
       </c>
       <c r="J58">
-        <v>4920.5258517033999</v>
+        <v>4.9205258517033998</v>
       </c>
       <c r="K58">
-        <v>1617.2986365765901</v>
+        <v>1.61729863657659</v>
       </c>
       <c r="L58">
-        <v>17700.020440881701</v>
+        <v>17.700020440881701</v>
       </c>
       <c r="M58">
-        <v>5817.7153802588</v>
+        <v>5.8177153802588002</v>
       </c>
       <c r="N58">
-        <v>24912.4150701402</v>
+        <v>24.912415070140199</v>
       </c>
       <c r="O58">
-        <v>8188.3148551734803</v>
+        <v>8.1883148551734806</v>
       </c>
       <c r="P58">
-        <v>14649.0233800935</v>
+        <v>14.649023380093499</v>
       </c>
       <c r="Q58">
-        <v>4814.9011414302804</v>
+        <v>4.8149011414302798</v>
       </c>
       <c r="R58">
-        <v>880.28303225806405</v>
+        <v>0.88028303225806404</v>
       </c>
       <c r="S58">
-        <v>289.33504076187802</v>
+        <v>0.28933504076187799</v>
       </c>
       <c r="T58">
-        <v>10101.0130661322</v>
+        <v>10.1010130661322</v>
       </c>
       <c r="U58">
-        <v>3320.0424410416799</v>
+        <v>3.32004244104168</v>
       </c>
       <c r="V58">
-        <v>2149.5977419354799</v>
+        <v>2.1495977419354801</v>
       </c>
       <c r="W58">
-        <v>706.53861030256905</v>
+        <v>0.70653861030256904</v>
       </c>
       <c r="X58">
-        <v>2451.6245564516098</v>
+        <v>2.4516245564516099</v>
       </c>
       <c r="Y58">
-        <v>805.81002357182501</v>
+        <v>0.80581002357182496</v>
       </c>
       <c r="Z58" s="4"/>
       <c r="AA58" s="4"/>
@@ -7578,76 +7578,76 @@
         <v>0.58333333333333304</v>
       </c>
       <c r="B59">
-        <v>15365.0538502488</v>
+        <v>15.365053850248801</v>
       </c>
       <c r="C59">
-        <v>5050.2489757941003</v>
+        <v>5.0502489757940996</v>
       </c>
       <c r="D59">
-        <v>22794.4546950248</v>
+        <v>22.7944546950248</v>
       </c>
       <c r="E59">
-        <v>7492.17494447438</v>
+        <v>7.4921749444743799</v>
       </c>
       <c r="F59">
-        <v>2442.5951894514801</v>
+        <v>2.4425951894514801</v>
       </c>
       <c r="G59">
-        <v>802.84221415905597</v>
+        <v>0.80284221415905599</v>
       </c>
       <c r="H59">
-        <v>10623.100801603199</v>
+        <v>10.623100801603201</v>
       </c>
       <c r="I59">
-        <v>3491.6443811998101</v>
+        <v>3.4916443811998099</v>
       </c>
       <c r="J59">
-        <v>4727.0051703406798</v>
+        <v>4.7270051703406804</v>
       </c>
       <c r="K59">
-        <v>1553.69146458928</v>
+        <v>1.5536914645892801</v>
       </c>
       <c r="L59">
-        <v>17003.891588176299</v>
+        <v>17.003891588176302</v>
       </c>
       <c r="M59">
-        <v>5588.9088912181396</v>
+        <v>5.5889088912181402</v>
       </c>
       <c r="N59">
-        <v>23932.628014028</v>
+        <v>23.932628014028001</v>
       </c>
       <c r="O59">
-        <v>7866.2744233694002</v>
+        <v>7.8662744233693997</v>
       </c>
       <c r="P59">
-        <v>14072.888009352</v>
+        <v>14.072888009352001</v>
       </c>
       <c r="Q59">
-        <v>4625.5346026362204</v>
+        <v>4.6255346026362201</v>
       </c>
       <c r="R59">
-        <v>877.42867741935402</v>
+        <v>0.87742867741935404</v>
       </c>
       <c r="S59">
-        <v>288.396859695854</v>
+        <v>0.28839685969585399</v>
       </c>
       <c r="T59">
-        <v>9703.7476132264492</v>
+        <v>9.7037476132264509</v>
       </c>
       <c r="U59">
-        <v>3189.4676011348602</v>
+        <v>3.1894676011348602</v>
       </c>
       <c r="V59">
-        <v>2142.6275806451599</v>
+        <v>2.14262758064516</v>
       </c>
       <c r="W59">
-        <v>704.24762907590696</v>
+        <v>0.70424762907590699</v>
       </c>
       <c r="X59">
-        <v>2443.6750604838699</v>
+        <v>2.4436750604838702</v>
       </c>
       <c r="Y59">
-        <v>803.19715060304497</v>
+        <v>0.80319715060304497</v>
       </c>
       <c r="Z59" s="4"/>
       <c r="AA59" s="4"/>
@@ -7702,76 +7702,76 @@
         <v>0.59375</v>
       </c>
       <c r="B60">
-        <v>14884.6130005494</v>
+        <v>14.8846130005494</v>
       </c>
       <c r="C60">
-        <v>4892.3357050192799</v>
+        <v>4.8923357050192804</v>
       </c>
       <c r="D60">
-        <v>22037.2254790115</v>
+        <v>22.0372254790115</v>
       </c>
       <c r="E60">
-        <v>7243.2857371937598</v>
+        <v>7.2432857371937596</v>
       </c>
       <c r="F60">
-        <v>2407.68216339937</v>
+        <v>2.4076821633993699</v>
       </c>
       <c r="G60">
-        <v>791.36685743203395</v>
+        <v>0.79136685743203405</v>
       </c>
       <c r="H60">
-        <v>10279.223847695301</v>
+        <v>10.279223847695301</v>
       </c>
       <c r="I60">
-        <v>3378.6174923129802</v>
+        <v>3.3786174923129799</v>
       </c>
       <c r="J60">
-        <v>4573.9888176352697</v>
+        <v>4.5739888176352697</v>
       </c>
       <c r="K60">
-        <v>1503.3974216225699</v>
+        <v>1.5033974216225701</v>
       </c>
       <c r="L60">
-        <v>16453.464123246398</v>
+        <v>16.453464123246398</v>
       </c>
       <c r="M60">
-        <v>5407.9921324418001</v>
+        <v>5.4079921324417999</v>
       </c>
       <c r="N60">
-        <v>23157.9126673346</v>
+        <v>23.1579126673346</v>
       </c>
       <c r="O60">
-        <v>7611.6378028731497</v>
+        <v>7.6116378028731502</v>
       </c>
       <c r="P60">
-        <v>13617.339111556401</v>
+        <v>13.617339111556401</v>
       </c>
       <c r="Q60">
-        <v>4475.8029207990603</v>
+        <v>4.4758029207990599</v>
       </c>
       <c r="R60">
-        <v>877.42867741935402</v>
+        <v>0.87742867741935404</v>
       </c>
       <c r="S60">
-        <v>288.396859695854</v>
+        <v>0.28839685969585399</v>
       </c>
       <c r="T60">
-        <v>9389.6307434869705</v>
+        <v>9.3896307434869701</v>
       </c>
       <c r="U60">
-        <v>3086.2223788829501</v>
+        <v>3.0862223788829501</v>
       </c>
       <c r="V60">
-        <v>2142.6275806451599</v>
+        <v>2.14262758064516</v>
       </c>
       <c r="W60">
-        <v>704.24762907590696</v>
+        <v>0.70424762907590699</v>
       </c>
       <c r="X60">
-        <v>2443.6750604838699</v>
+        <v>2.4436750604838702</v>
       </c>
       <c r="Y60">
-        <v>803.19715060304497</v>
+        <v>0.80319715060304497</v>
       </c>
       <c r="Z60" s="4"/>
       <c r="AA60" s="4"/>
@@ -7826,76 +7826,76 @@
         <v>0.60416666666666696</v>
       </c>
       <c r="B61">
-        <v>14474.1444105307</v>
+        <v>14.4741444105307</v>
       </c>
       <c r="C61">
-        <v>4757.42120380493</v>
+        <v>4.7574212038049399</v>
       </c>
       <c r="D61">
-        <v>21362.639168825001</v>
+        <v>21.362639168825002</v>
       </c>
       <c r="E61">
-        <v>7021.5599394642004</v>
+        <v>7.0215599394641997</v>
       </c>
       <c r="F61">
-        <v>2376.1284462069202</v>
+        <v>2.3761284462069199</v>
       </c>
       <c r="G61">
-        <v>780.995652131567</v>
+        <v>0.78099565213156696</v>
       </c>
       <c r="H61">
-        <v>9985.9170340681303</v>
+        <v>9.9859170340681302</v>
       </c>
       <c r="I61">
-        <v>3282.2122047330499</v>
+        <v>3.28221220473305</v>
       </c>
       <c r="J61">
-        <v>4443.4748697394698</v>
+        <v>4.4434748697394699</v>
       </c>
       <c r="K61">
-        <v>1460.49956144508</v>
+        <v>1.46049956144508</v>
       </c>
       <c r="L61">
-        <v>15983.9818737474</v>
+        <v>15.9839818737474</v>
       </c>
       <c r="M61">
-        <v>5253.6807793678599</v>
+        <v>5.2536807793678602</v>
       </c>
       <c r="N61">
-        <v>22497.126048096099</v>
+        <v>22.497126048096099</v>
       </c>
       <c r="O61">
-        <v>7394.4477442145899</v>
+        <v>7.3944477442145899</v>
       </c>
       <c r="P61">
-        <v>13228.7826987307</v>
+        <v>13.228782698730701</v>
       </c>
       <c r="Q61">
-        <v>4348.0906039379497</v>
+        <v>4.3480906039379503</v>
       </c>
       <c r="R61">
-        <v>876.28693548387105</v>
+        <v>0.87628693548387104</v>
       </c>
       <c r="S61">
-        <v>288.02158726944401</v>
+        <v>0.28802158726944399</v>
       </c>
       <c r="T61">
-        <v>9121.7075310621203</v>
+        <v>9.1217075310621194</v>
       </c>
       <c r="U61">
-        <v>2998.1602775504498</v>
+        <v>2.9981602775504501</v>
       </c>
       <c r="V61">
-        <v>2139.83951612903</v>
+        <v>2.13983951612903</v>
       </c>
       <c r="W61">
-        <v>703.33123658524198</v>
+        <v>0.70333123658524199</v>
       </c>
       <c r="X61">
-        <v>2440.4952620967701</v>
+        <v>2.4404952620967699</v>
       </c>
       <c r="Y61">
-        <v>802.15200141553305</v>
+        <v>0.802152001415533</v>
       </c>
       <c r="Z61" s="4"/>
       <c r="AA61" s="4"/>
@@ -7950,76 +7950,76 @@
         <v>0.61458333333333304</v>
       </c>
       <c r="B62">
-        <v>14124.227671375</v>
+        <v>14.124227671374999</v>
       </c>
       <c r="C62">
-        <v>4642.4091335084304</v>
+        <v>4.6424091335084299</v>
       </c>
       <c r="D62">
-        <v>20784.2267824675</v>
+        <v>20.784226782467499</v>
       </c>
       <c r="E62">
-        <v>6831.4449818298899</v>
+        <v>6.8314449818298897</v>
       </c>
       <c r="F62">
-        <v>2347.2494687358499</v>
+        <v>2.3472494687358498</v>
       </c>
       <c r="G62">
-        <v>771.50359126300702</v>
+        <v>0.77150359126300705</v>
       </c>
       <c r="H62">
-        <v>9736.4376753507004</v>
+        <v>9.7364376753507003</v>
       </c>
       <c r="I62">
-        <v>3200.2123049524098</v>
+        <v>3.20021230495241</v>
       </c>
       <c r="J62">
-        <v>4332.4630060120198</v>
+        <v>4.3324630060120199</v>
       </c>
       <c r="K62">
-        <v>1424.0117263515899</v>
+        <v>1.4240117263515899</v>
       </c>
       <c r="L62">
-        <v>15584.6521442885</v>
+        <v>15.5846521442885</v>
       </c>
       <c r="M62">
-        <v>5122.42744456934</v>
+        <v>5.1224274445693396</v>
       </c>
       <c r="N62">
-        <v>21935.077659318598</v>
+        <v>21.935077659318601</v>
       </c>
       <c r="O62">
-        <v>7209.7113724820101</v>
+        <v>7.2097113724820101</v>
       </c>
       <c r="P62">
-        <v>12898.2864395457</v>
+        <v>12.8982864395457</v>
       </c>
       <c r="Q62">
-        <v>4239.4617367227602</v>
+        <v>4.2394617367227596</v>
       </c>
       <c r="R62">
-        <v>874.00345161290295</v>
+        <v>0.87400345161290305</v>
       </c>
       <c r="S62">
-        <v>287.27104241662499</v>
+        <v>0.28727104241662499</v>
       </c>
       <c r="T62">
-        <v>8893.8188216432809</v>
+        <v>8.8938188216432792</v>
       </c>
       <c r="U62">
-        <v>2923.25688101475</v>
+        <v>2.9232568810147499</v>
       </c>
       <c r="V62">
-        <v>2134.2633870967702</v>
+        <v>2.13426338709677</v>
       </c>
       <c r="W62">
-        <v>701.49845160391203</v>
+        <v>0.701498451603912</v>
       </c>
       <c r="X62">
-        <v>2434.1356653225798</v>
+        <v>2.4341356653225801</v>
       </c>
       <c r="Y62">
-        <v>800.06170304050897</v>
+        <v>0.80006170304050905</v>
       </c>
       <c r="Z62" s="4"/>
       <c r="AA62" s="4"/>
@@ -8074,76 +8074,76 @@
         <v>0.625</v>
       </c>
       <c r="B63">
-        <v>13800.5297393173</v>
+        <v>13.8005297393173</v>
       </c>
       <c r="C63">
-        <v>4536.0147683618097</v>
+        <v>4.5360147683618104</v>
       </c>
       <c r="D63">
-        <v>20288.291938630198</v>
+        <v>20.288291938630199</v>
       </c>
       <c r="E63">
-        <v>6668.4390814562203</v>
+        <v>6.6684390814562198</v>
       </c>
       <c r="F63">
-        <v>2315.0993196473501</v>
+        <v>2.3150993196473499</v>
       </c>
       <c r="G63">
-        <v>760.936348278487</v>
+        <v>0.760936348278487</v>
       </c>
       <c r="H63">
-        <v>9507.1863727454893</v>
+        <v>9.5071863727454904</v>
       </c>
       <c r="I63">
-        <v>3124.8610456945298</v>
+        <v>3.12486104569453</v>
       </c>
       <c r="J63">
-        <v>4230.4521042084098</v>
+        <v>4.2304521042084096</v>
       </c>
       <c r="K63">
-        <v>1390.48236437378</v>
+        <v>1.39048236437378</v>
       </c>
       <c r="L63">
-        <v>15217.700501002</v>
+        <v>15.217700501002</v>
       </c>
       <c r="M63">
-        <v>5001.8162720517803</v>
+        <v>5.00181627205178</v>
       </c>
       <c r="N63">
-        <v>21418.600761523001</v>
+        <v>21.418600761522999</v>
       </c>
       <c r="O63">
-        <v>7039.9536254845198</v>
+        <v>7.0399536254845199</v>
       </c>
       <c r="P63">
-        <v>12594.5871743486</v>
+        <v>12.5945871743486</v>
       </c>
       <c r="Q63">
-        <v>4139.6406154979804</v>
+        <v>4.1396406154979797</v>
       </c>
       <c r="R63">
-        <v>868.29474193548401</v>
+        <v>0.86829474193548395</v>
       </c>
       <c r="S63">
-        <v>285.394680284576</v>
+        <v>0.28539468028457599</v>
       </c>
       <c r="T63">
-        <v>8684.4075751503005</v>
+        <v>8.6844075751502992</v>
       </c>
       <c r="U63">
-        <v>2854.42673284681</v>
+        <v>2.85442673284681</v>
       </c>
       <c r="V63">
-        <v>2120.3230645161202</v>
+        <v>2.12032306451612</v>
       </c>
       <c r="W63">
-        <v>696.91648915058795</v>
+        <v>0.69691648915058801</v>
       </c>
       <c r="X63">
-        <v>2418.2366733870899</v>
+        <v>2.4182366733870899</v>
       </c>
       <c r="Y63">
-        <v>794.83595710294799</v>
+        <v>0.79483595710294797</v>
       </c>
       <c r="Z63" s="4"/>
       <c r="AA63" s="4"/>
@@ -8198,76 +8198,76 @@
         <v>0.63541666666666696</v>
       </c>
       <c r="B64">
-        <v>13494.6514152175</v>
+        <v>13.494651415217501</v>
       </c>
       <c r="C64">
-        <v>4435.4774251114504</v>
+        <v>4.4354774251114497</v>
       </c>
       <c r="D64">
-        <v>19850.563091453299</v>
+        <v>19.850563091453299</v>
       </c>
       <c r="E64">
-        <v>6524.5645670108997</v>
+        <v>6.5245645670109003</v>
       </c>
       <c r="F64">
-        <v>2281.6558693192801</v>
+        <v>2.2816558693192799</v>
       </c>
       <c r="G64">
-        <v>749.94401773331003</v>
+        <v>0.74994401773330999</v>
       </c>
       <c r="H64">
-        <v>9291.4204408817604</v>
+        <v>9.29142044088176</v>
       </c>
       <c r="I64">
-        <v>3053.94221345182</v>
+        <v>3.0539422134518199</v>
       </c>
       <c r="J64">
-        <v>4134.4418436873702</v>
+        <v>4.1344418436873704</v>
       </c>
       <c r="K64">
-        <v>1358.92531780643</v>
+        <v>1.35892531780643</v>
       </c>
       <c r="L64">
-        <v>14872.3342484969</v>
+        <v>14.8723342484969</v>
       </c>
       <c r="M64">
-        <v>4888.2998743881899</v>
+        <v>4.8882998743881902</v>
       </c>
       <c r="N64">
-        <v>20932.504857715401</v>
+        <v>20.932504857715401</v>
       </c>
       <c r="O64">
-        <v>6880.1816283103999</v>
+        <v>6.8801816283103996</v>
       </c>
       <c r="P64">
-        <v>12308.752571810201</v>
+        <v>12.308752571810199</v>
       </c>
       <c r="Q64">
-        <v>4045.6913249334898</v>
+        <v>4.0456913249334896</v>
       </c>
       <c r="R64">
-        <v>860.87341935483801</v>
+        <v>0.86087341935483896</v>
       </c>
       <c r="S64">
-        <v>282.95540951291298</v>
+        <v>0.28295540951291298</v>
       </c>
       <c r="T64">
-        <v>8487.3146372745396</v>
+        <v>8.4873146372745492</v>
       </c>
       <c r="U64">
-        <v>2789.6454169240501</v>
+        <v>2.7896454169240501</v>
       </c>
       <c r="V64">
-        <v>2102.2006451612901</v>
+        <v>2.10220064516129</v>
       </c>
       <c r="W64">
-        <v>690.95993796126697</v>
+        <v>0.69095993796126698</v>
       </c>
       <c r="X64">
-        <v>2397.5679838709598</v>
+        <v>2.3975679838709598</v>
       </c>
       <c r="Y64">
-        <v>788.04248738412002</v>
+        <v>0.78804248738411997</v>
       </c>
       <c r="Z64" s="4"/>
       <c r="AA64" s="4"/>
@@ -8322,76 +8322,76 @@
         <v>0.64583333333333304</v>
       </c>
       <c r="B65">
-        <v>13207.2735055271</v>
+        <v>13.2072735055271</v>
       </c>
       <c r="C65">
-        <v>4341.02087401671</v>
+        <v>4.34102087401671</v>
       </c>
       <c r="D65">
-        <v>19451.368166803899</v>
+        <v>19.451368166803899</v>
       </c>
       <c r="E65">
-        <v>6393.35554041056</v>
+        <v>6.3933555404105604</v>
       </c>
       <c r="F65">
-        <v>2248.6940774290501</v>
+        <v>2.2486940774290498</v>
       </c>
       <c r="G65">
-        <v>739.11000066077702</v>
+        <v>0.73911000066077703</v>
       </c>
       <c r="H65">
-        <v>9089.1398797595193</v>
+        <v>9.0891398797595198</v>
       </c>
       <c r="I65">
-        <v>2987.4558082242702</v>
+        <v>2.9874558082242699</v>
       </c>
       <c r="J65">
-        <v>4044.4322244488899</v>
+        <v>4.0444322244488902</v>
       </c>
       <c r="K65">
-        <v>1329.34058664954</v>
+        <v>1.32934058664954</v>
       </c>
       <c r="L65">
-        <v>14548.553386773499</v>
+        <v>14.5485533867735</v>
       </c>
       <c r="M65">
-        <v>4781.8782515785797</v>
+        <v>4.78187825157858</v>
       </c>
       <c r="N65">
-        <v>20476.789947895701</v>
+        <v>20.4767899478957</v>
       </c>
       <c r="O65">
-        <v>6730.3953809596596</v>
+        <v>6.7303953809596599</v>
       </c>
       <c r="P65">
-        <v>12040.7826319305</v>
+        <v>12.040782631930499</v>
       </c>
       <c r="Q65">
-        <v>3957.6138650292801</v>
+        <v>3.95761386502928</v>
       </c>
       <c r="R65">
-        <v>852.88122580645097</v>
+        <v>0.85288122580645098</v>
       </c>
       <c r="S65">
-        <v>280.32850252804502</v>
+        <v>0.28032850252804498</v>
       </c>
       <c r="T65">
-        <v>8302.5400080160307</v>
+        <v>8.3025400080160292</v>
       </c>
       <c r="U65">
-        <v>2728.9129332464599</v>
+        <v>2.7289129332464599</v>
       </c>
       <c r="V65">
-        <v>2082.6841935483799</v>
+        <v>2.08268419354838</v>
       </c>
       <c r="W65">
-        <v>684.54519052661306</v>
+        <v>0.684545190526613</v>
       </c>
       <c r="X65">
-        <v>2375.30939516129</v>
+        <v>2.37530939516129</v>
       </c>
       <c r="Y65">
-        <v>780.72644307153496</v>
+        <v>0.78072644307153505</v>
       </c>
       <c r="Z65" s="4"/>
       <c r="AA65" s="4"/>
@@ -8446,76 +8446,76 @@
         <v>0.65625</v>
       </c>
       <c r="B66">
-        <v>12930.6776175576</v>
+        <v>12.930677617557601</v>
       </c>
       <c r="C66">
-        <v>4250.1082020833001</v>
+        <v>4.2501082020833003</v>
       </c>
       <c r="D66">
-        <v>19061.7940820443</v>
+        <v>19.061794082044301</v>
       </c>
       <c r="E66">
-        <v>6265.3087309604798</v>
+        <v>6.2653087309604798</v>
       </c>
       <c r="F66">
-        <v>2219.9667740319301</v>
+        <v>2.21996677403193</v>
       </c>
       <c r="G66">
-        <v>729.66779264949298</v>
+        <v>0.729667792649493</v>
       </c>
       <c r="H66">
-        <v>8893.6020040080093</v>
+        <v>8.8936020040080095</v>
       </c>
       <c r="I66">
-        <v>2923.18561650431</v>
+        <v>2.92318561650431</v>
       </c>
       <c r="J66">
-        <v>3957.4229258516998</v>
+        <v>3.9574229258517</v>
       </c>
       <c r="K66">
-        <v>1300.7420131978799</v>
+        <v>1.30074201319788</v>
       </c>
       <c r="L66">
-        <v>14235.5652204408</v>
+        <v>14.235565220440799</v>
       </c>
       <c r="M66">
-        <v>4679.0040161959496</v>
+        <v>4.6790040161959503</v>
       </c>
       <c r="N66">
-        <v>20036.265535070099</v>
+        <v>20.0362655350701</v>
       </c>
       <c r="O66">
-        <v>6585.6020085206201</v>
+        <v>6.5856020085206204</v>
       </c>
       <c r="P66">
-        <v>11781.745023379999</v>
+        <v>11.781745023379999</v>
       </c>
       <c r="Q66">
-        <v>3872.4723204552101</v>
+        <v>3.8724723204552101</v>
       </c>
       <c r="R66">
-        <v>847.17251612903203</v>
+        <v>0.84717251612903199</v>
       </c>
       <c r="S66">
-        <v>278.45214039599699</v>
+        <v>0.27845214039599703</v>
       </c>
       <c r="T66">
-        <v>8123.9245330661297</v>
+        <v>8.1239245330661305</v>
       </c>
       <c r="U66">
-        <v>2670.2048656914499</v>
+        <v>2.6702048656914501</v>
       </c>
       <c r="V66">
-        <v>2068.7438709677399</v>
+        <v>2.0687438709677402</v>
       </c>
       <c r="W66">
-        <v>679.96322807328897</v>
+        <v>0.67996322807328902</v>
       </c>
       <c r="X66">
-        <v>2359.4104032258001</v>
+        <v>2.3594104032257999</v>
       </c>
       <c r="Y66">
-        <v>775.50069713397397</v>
+        <v>0.77550069713397396</v>
       </c>
       <c r="Z66" s="4"/>
       <c r="AA66" s="4"/>
@@ -8570,76 +8570,76 @@
         <v>0.66666666666666696</v>
       </c>
       <c r="B67">
-        <v>12674.284160126699</v>
+        <v>12.6742841601267</v>
       </c>
       <c r="C67">
-        <v>4165.8357479538799</v>
+        <v>4.1658357479538797</v>
       </c>
       <c r="D67">
-        <v>18677.4476736006</v>
+        <v>18.6774476736006</v>
       </c>
       <c r="E67">
-        <v>6138.9801756224597</v>
+        <v>6.1389801756224598</v>
       </c>
       <c r="F67">
-        <v>2196.1585282661999</v>
+        <v>2.1961585282662002</v>
       </c>
       <c r="G67">
-        <v>721.84240069410703</v>
+        <v>0.72184240069410799</v>
       </c>
       <c r="H67">
-        <v>8711.5494989979907</v>
+        <v>8.7115494989979894</v>
       </c>
       <c r="I67">
-        <v>2863.34785179953</v>
+        <v>2.8633478517995301</v>
       </c>
       <c r="J67">
-        <v>3876.4142685370698</v>
+        <v>3.8764142685370699</v>
       </c>
       <c r="K67">
-        <v>1274.1157551566801</v>
+        <v>1.27411575515668</v>
       </c>
       <c r="L67">
-        <v>13944.1624448897</v>
+        <v>13.944162444889701</v>
       </c>
       <c r="M67">
-        <v>4583.2245556672997</v>
+        <v>4.5832245556673001</v>
       </c>
       <c r="N67">
-        <v>19626.1221162324</v>
+        <v>19.626122116232398</v>
       </c>
       <c r="O67">
-        <v>6450.7943859049601</v>
+        <v>6.4507943859049597</v>
       </c>
       <c r="P67">
-        <v>11540.572077488299</v>
+        <v>11.540572077488299</v>
       </c>
       <c r="Q67">
-        <v>3793.2026065414102</v>
+        <v>3.7932026065414099</v>
       </c>
       <c r="R67">
-        <v>843.74729032258006</v>
+        <v>0.84374729032258</v>
       </c>
       <c r="S67">
-        <v>277.32632311676701</v>
+        <v>0.27732632311676703</v>
       </c>
       <c r="T67">
-        <v>7957.6273667334599</v>
+        <v>7.9576273667334601</v>
       </c>
       <c r="U67">
-        <v>2615.54563038162</v>
+        <v>2.6155456303816198</v>
       </c>
       <c r="V67">
-        <v>2060.3796774193502</v>
+        <v>2.0603796774193501</v>
       </c>
       <c r="W67">
-        <v>677.21405060129496</v>
+        <v>0.67721405060129503</v>
       </c>
       <c r="X67">
-        <v>2349.8710080645101</v>
+        <v>2.3498710080645102</v>
       </c>
       <c r="Y67">
-        <v>772.36524957143797</v>
+        <v>0.77236524957143804</v>
       </c>
       <c r="Z67" s="4"/>
       <c r="AA67" s="4"/>
@@ -8694,76 +8694,76 @@
         <v>0.67708333333333304</v>
       </c>
       <c r="B68">
-        <v>12462.665364955699</v>
+        <v>12.462665364955701</v>
       </c>
       <c r="C68">
-        <v>4096.2800136240703</v>
+        <v>4.0962800136240798</v>
       </c>
       <c r="D68">
-        <v>18351.048488279699</v>
+        <v>18.351048488279702</v>
       </c>
       <c r="E68">
-        <v>6031.6979514641498</v>
+        <v>6.0316979514641504</v>
       </c>
       <c r="F68">
-        <v>2181.6432024936898</v>
+        <v>2.18164320249369</v>
       </c>
       <c r="G68">
-        <v>717.07144383118998</v>
+        <v>0.71707144383119004</v>
       </c>
       <c r="H68">
-        <v>8559.8390781563103</v>
+        <v>8.5598390781563101</v>
       </c>
       <c r="I68">
-        <v>2813.4830478788699</v>
+        <v>2.8134830478788699</v>
       </c>
       <c r="J68">
-        <v>3808.9070541082101</v>
+        <v>3.80890705410821</v>
       </c>
       <c r="K68">
-        <v>1251.9272067890099</v>
+        <v>1.2519272067890099</v>
       </c>
       <c r="L68">
-        <v>13701.3267985971</v>
+        <v>13.701326798597099</v>
       </c>
       <c r="M68">
-        <v>4503.4083385600898</v>
+        <v>4.5034083385600896</v>
       </c>
       <c r="N68">
-        <v>19284.3359338677</v>
+        <v>19.284335933867698</v>
       </c>
       <c r="O68">
-        <v>6338.4547003919097</v>
+        <v>6.3384547003919103</v>
       </c>
       <c r="P68">
-        <v>11339.594622578399</v>
+        <v>11.339594622578399</v>
       </c>
       <c r="Q68">
-        <v>3727.14451161325</v>
+        <v>3.72714451161325</v>
       </c>
       <c r="R68">
-        <v>844.318161290322</v>
+        <v>0.844318161290322</v>
       </c>
       <c r="S68">
-        <v>277.51395932997201</v>
+        <v>0.27751395932997203</v>
       </c>
       <c r="T68">
-        <v>7819.0463947895696</v>
+        <v>7.8190463947895701</v>
       </c>
       <c r="U68">
-        <v>2569.99626762342</v>
+        <v>2.56999626762342</v>
       </c>
       <c r="V68">
-        <v>2061.7737096774099</v>
+        <v>2.0617737096774098</v>
       </c>
       <c r="W68">
-        <v>677.67224684662699</v>
+        <v>0.67767224684662697</v>
       </c>
       <c r="X68">
-        <v>2351.4609072580602</v>
+        <v>2.3514609072580601</v>
       </c>
       <c r="Y68">
-        <v>772.88782416519405</v>
+        <v>0.77288782416519397</v>
       </c>
       <c r="Z68" s="4"/>
       <c r="AA68" s="4"/>
@@ -8818,76 +8818,76 @@
         <v>0.6875</v>
       </c>
       <c r="B69">
-        <v>12318.3510444114</v>
+        <v>12.318351044411401</v>
       </c>
       <c r="C69">
-        <v>4048.8461903114699</v>
+        <v>4.0488461903114699</v>
       </c>
       <c r="D69">
-        <v>18136.712438164799</v>
+        <v>18.1367124381648</v>
       </c>
       <c r="E69">
-        <v>5961.2490986245602</v>
+        <v>5.9612490986245597</v>
       </c>
       <c r="F69">
-        <v>2175.4697800439499</v>
+        <v>2.17546978004395</v>
       </c>
       <c r="G69">
-        <v>715.04233799740598</v>
+        <v>0.71504233799740602</v>
       </c>
       <c r="H69">
-        <v>8455.3274549098205</v>
+        <v>8.4553274549098205</v>
       </c>
       <c r="I69">
-        <v>2779.1317385112998</v>
+        <v>2.7791317385113001</v>
       </c>
       <c r="J69">
-        <v>3762.40208416833</v>
+        <v>3.7624020841683299</v>
       </c>
       <c r="K69">
-        <v>1236.64176235795</v>
+        <v>1.23664176235795</v>
       </c>
       <c r="L69">
-        <v>13534.04002004</v>
+        <v>13.534040020040001</v>
       </c>
       <c r="M69">
-        <v>4448.4238334417896</v>
+        <v>4.4484238334417903</v>
       </c>
       <c r="N69">
-        <v>19048.883230460899</v>
+        <v>19.048883230460898</v>
       </c>
       <c r="O69">
-        <v>6261.0651392606997</v>
+        <v>6.2610651392607002</v>
       </c>
       <c r="P69">
-        <v>11201.143486973901</v>
+        <v>11.201143486973899</v>
       </c>
       <c r="Q69">
-        <v>3681.63782399608</v>
+        <v>3.6816378239960801</v>
       </c>
       <c r="R69">
-        <v>847.17251612903203</v>
+        <v>0.84717251612903199</v>
       </c>
       <c r="S69">
-        <v>278.45214039599699</v>
+        <v>0.27845214039599703</v>
       </c>
       <c r="T69">
-        <v>7723.5795030060099</v>
+        <v>7.7235795030060101</v>
       </c>
       <c r="U69">
-        <v>2538.6178177233301</v>
+        <v>2.5386178177233401</v>
       </c>
       <c r="V69">
-        <v>2068.7438709677399</v>
+        <v>2.0687438709677402</v>
       </c>
       <c r="W69">
-        <v>679.96322807328897</v>
+        <v>0.67996322807328902</v>
       </c>
       <c r="X69">
-        <v>2359.4104032258001</v>
+        <v>2.3594104032257999</v>
       </c>
       <c r="Y69">
-        <v>775.50069713397397</v>
+        <v>0.77550069713397496</v>
       </c>
       <c r="Z69" s="4"/>
       <c r="AA69" s="4"/>
@@ -8942,76 +8942,76 @@
         <v>0.69791666666666696</v>
       </c>
       <c r="B70">
-        <v>12270.2832313982</v>
+        <v>12.270283231398199</v>
       </c>
       <c r="C70">
-        <v>4033.0470642033501</v>
+        <v>4.03304706420335</v>
       </c>
       <c r="D70">
-        <v>18099.585281247299</v>
+        <v>18.0995852812473</v>
       </c>
       <c r="E70">
-        <v>5949.0459922753198</v>
+        <v>5.9490459922753196</v>
       </c>
       <c r="F70">
-        <v>2181.4669280092398</v>
+        <v>2.18146692800924</v>
       </c>
       <c r="G70">
-        <v>717.01350521000097</v>
+        <v>0.71701350521000096</v>
       </c>
       <c r="H70">
-        <v>8418.2426853707402</v>
+        <v>8.4182426853707408</v>
       </c>
       <c r="I70">
-        <v>2766.9425642195902</v>
+        <v>2.76694256421959</v>
       </c>
       <c r="J70">
-        <v>3745.9003206412799</v>
+        <v>3.74590032064128</v>
       </c>
       <c r="K70">
-        <v>1231.2178949791901</v>
+        <v>1.2312178949791901</v>
       </c>
       <c r="L70">
-        <v>13474.6801953907</v>
+        <v>13.4746801953907</v>
       </c>
       <c r="M70">
-        <v>4428.9132025933604</v>
+        <v>4.4289132025933604</v>
       </c>
       <c r="N70">
-        <v>18965.335496993899</v>
+        <v>18.965335496993902</v>
       </c>
       <c r="O70">
-        <v>6233.6043272463903</v>
+        <v>6.2336043272463897</v>
       </c>
       <c r="P70">
-        <v>11152.0156646626</v>
+        <v>11.152015664662599</v>
       </c>
       <c r="Q70">
-        <v>3665.4902896803101</v>
+        <v>3.6654902896803101</v>
       </c>
       <c r="R70">
-        <v>853.45209677419302</v>
+        <v>0.85345209677419298</v>
       </c>
       <c r="S70">
-        <v>280.51613874125002</v>
+        <v>0.28051613874124998</v>
       </c>
       <c r="T70">
-        <v>7689.7041543086098</v>
+        <v>7.6897041543086102</v>
       </c>
       <c r="U70">
-        <v>2527.4835290491101</v>
+        <v>2.52748352904911</v>
       </c>
       <c r="V70">
-        <v>2084.0782258064501</v>
+        <v>2.0840782258064499</v>
       </c>
       <c r="W70">
-        <v>685.003386771946</v>
+        <v>0.68500338677194605</v>
       </c>
       <c r="X70">
-        <v>2376.8992943548301</v>
+        <v>2.3768992943548302</v>
       </c>
       <c r="Y70">
-        <v>781.24901766529103</v>
+        <v>0.78124901766529098</v>
       </c>
       <c r="Z70" s="4"/>
       <c r="AA70" s="4"/>
@@ -9066,76 +9066,76 @@
         <v>0.70833333333333304</v>
       </c>
       <c r="B71">
-        <v>12340.3663725838</v>
+        <v>12.3403663725838</v>
       </c>
       <c r="C71">
-        <v>4056.0822787520601</v>
+        <v>4.0560822787520596</v>
       </c>
       <c r="D71">
-        <v>18282.535255011298</v>
+        <v>18.2825352550113</v>
       </c>
       <c r="E71">
-        <v>6009.1787406944304</v>
+        <v>6.0091787406944297</v>
       </c>
       <c r="F71">
-        <v>2208.9911032144901</v>
+        <v>2.20899110321449</v>
       </c>
       <c r="G71">
-        <v>726.06026410812501</v>
+        <v>0.72606026410812496</v>
       </c>
       <c r="H71">
-        <v>8462.0701402805607</v>
+        <v>8.4620701402805594</v>
       </c>
       <c r="I71">
-        <v>2781.3479520188898</v>
+        <v>2.7813479520188902</v>
       </c>
       <c r="J71">
-        <v>3765.4024048096098</v>
+        <v>3.7654024048096102</v>
       </c>
       <c r="K71">
-        <v>1237.62792006318</v>
+        <v>1.2376279200631799</v>
       </c>
       <c r="L71">
-        <v>13544.832715430801</v>
+        <v>13.5448327154308</v>
       </c>
       <c r="M71">
-        <v>4451.9712208687797</v>
+        <v>4.4519712208687796</v>
       </c>
       <c r="N71">
-        <v>19064.073727454899</v>
+        <v>19.0640737274549</v>
       </c>
       <c r="O71">
-        <v>6266.0580141723904</v>
+        <v>6.2660580141723896</v>
       </c>
       <c r="P71">
-        <v>11210.075818303199</v>
+        <v>11.210075818303199</v>
       </c>
       <c r="Q71">
-        <v>3684.5737393262202</v>
+        <v>3.6845737393262201</v>
       </c>
       <c r="R71">
-        <v>868.29474193548401</v>
+        <v>0.86829474193548395</v>
       </c>
       <c r="S71">
-        <v>285.394680284576</v>
+        <v>0.28539468028457599</v>
       </c>
       <c r="T71">
-        <v>7729.7386573146296</v>
+        <v>7.7297386573146296</v>
       </c>
       <c r="U71">
-        <v>2540.6422338459201</v>
+        <v>2.54064223384592</v>
       </c>
       <c r="V71">
-        <v>2120.3230645161202</v>
+        <v>2.12032306451612</v>
       </c>
       <c r="W71">
-        <v>696.91648915058795</v>
+        <v>0.69691648915058801</v>
       </c>
       <c r="X71">
-        <v>2418.2366733870899</v>
+        <v>2.4182366733870899</v>
       </c>
       <c r="Y71">
-        <v>794.83595710294799</v>
+        <v>0.79483595710294797</v>
       </c>
       <c r="Z71" s="4"/>
       <c r="AA71" s="4"/>
@@ -9190,76 +9190,76 @@
         <v>0.71875</v>
       </c>
       <c r="B72">
-        <v>12538.8680054948</v>
+        <v>12.5388680054948</v>
       </c>
       <c r="C72">
-        <v>4121.3266103419501</v>
+        <v>4.1213266103419501</v>
       </c>
       <c r="D72">
-        <v>18662.076878055199</v>
+        <v>18.662076878055199</v>
       </c>
       <c r="E72">
-        <v>6133.9280394427296</v>
+        <v>6.13392803944273</v>
       </c>
       <c r="F72">
-        <v>2296.7491339937901</v>
+        <v>2.29674913399379</v>
       </c>
       <c r="G72">
-        <v>754.90493392707901</v>
+        <v>0.75490493392707902</v>
       </c>
       <c r="H72">
-        <v>8583.4384769538992</v>
+        <v>8.5834384769538996</v>
       </c>
       <c r="I72">
-        <v>2821.2397951554099</v>
+        <v>2.8212397951554098</v>
       </c>
       <c r="J72">
-        <v>3819.4081763527001</v>
+        <v>3.8194081763527001</v>
       </c>
       <c r="K72">
-        <v>1255.3787587573199</v>
+        <v>1.25537875875732</v>
       </c>
       <c r="L72">
-        <v>13739.1012324649</v>
+        <v>13.7391012324649</v>
       </c>
       <c r="M72">
-        <v>4515.8241945545496</v>
+        <v>4.5158241945545496</v>
       </c>
       <c r="N72">
-        <v>19337.5026733466</v>
+        <v>19.337502673346599</v>
       </c>
       <c r="O72">
-        <v>6355.9297625828303</v>
+        <v>6.3559297625828304</v>
       </c>
       <c r="P72">
-        <v>11370.8577822311</v>
+        <v>11.3708577822311</v>
       </c>
       <c r="Q72">
-        <v>3737.4202152687499</v>
+        <v>3.7374202152687501</v>
       </c>
       <c r="R72">
-        <v>916.81877419354805</v>
+        <v>0.91681877419354796</v>
       </c>
       <c r="S72">
-        <v>301.343758406988</v>
+        <v>0.30134375840698802</v>
       </c>
       <c r="T72">
-        <v>7840.6034348697303</v>
+        <v>7.84060343486974</v>
       </c>
       <c r="U72">
-        <v>2577.0817240524798</v>
+        <v>2.5770817240524799</v>
       </c>
       <c r="V72">
-        <v>2238.8158064516101</v>
+        <v>2.2388158064516102</v>
       </c>
       <c r="W72">
-        <v>735.86317000384304</v>
+        <v>0.73586317000384305</v>
       </c>
       <c r="X72">
-        <v>2553.37810483871</v>
+        <v>2.5533781048387101</v>
       </c>
       <c r="Y72">
-        <v>839.25479757221206</v>
+        <v>0.839254797572212</v>
       </c>
       <c r="Z72" s="4"/>
       <c r="AA72" s="4"/>
@@ -9314,76 +9314,76 @@
         <v>0.72916666666666696</v>
       </c>
       <c r="B73">
-        <v>12880.140506367499</v>
+        <v>12.8801405063675</v>
       </c>
       <c r="C73">
-        <v>4233.4974569134502</v>
+        <v>4.23349745691345</v>
       </c>
       <c r="D73">
-        <v>19210.010522635799</v>
+        <v>19.210010522635798</v>
       </c>
       <c r="E73">
-        <v>6314.0251191091102</v>
+        <v>6.3140251191091101</v>
       </c>
       <c r="F73">
-        <v>2494.09760674574</v>
+        <v>2.4940976067457399</v>
       </c>
       <c r="G73">
-        <v>819.77024010196999</v>
+        <v>0.81977024010196997</v>
       </c>
       <c r="H73">
-        <v>8778.9763527054092</v>
+        <v>8.7789763527054099</v>
       </c>
       <c r="I73">
-        <v>2885.50998687537</v>
+        <v>2.8855099868753702</v>
       </c>
       <c r="J73">
-        <v>3906.4174749498902</v>
+        <v>3.9064174749498899</v>
       </c>
       <c r="K73">
-        <v>1283.97733220898</v>
+        <v>1.28397733220898</v>
       </c>
       <c r="L73">
-        <v>14052.0893987975</v>
+        <v>14.0520893987975</v>
       </c>
       <c r="M73">
-        <v>4618.6984299371697</v>
+        <v>4.6186984299371696</v>
       </c>
       <c r="N73">
-        <v>19778.0270861723</v>
+        <v>19.778027086172301</v>
       </c>
       <c r="O73">
-        <v>6500.7231350218699</v>
+        <v>6.5007231350218699</v>
       </c>
       <c r="P73">
-        <v>11629.895390781499</v>
+        <v>11.629895390781501</v>
       </c>
       <c r="Q73">
-        <v>3822.5617598428198</v>
+        <v>3.8225617598428201</v>
       </c>
       <c r="R73">
-        <v>1030.99296774193</v>
+        <v>1.0309929677419301</v>
       </c>
       <c r="S73">
-        <v>338.87100104795798</v>
+        <v>0.33887100104795798</v>
       </c>
       <c r="T73">
-        <v>8019.2189098196304</v>
+        <v>8.0192189098196298</v>
       </c>
       <c r="U73">
-        <v>2635.7897916074799</v>
+        <v>2.6357897916074799</v>
       </c>
       <c r="V73">
-        <v>2517.6222580645099</v>
+        <v>2.51762225806451</v>
       </c>
       <c r="W73">
-        <v>827.50241907032398</v>
+        <v>0.82750241907032396</v>
       </c>
       <c r="X73">
-        <v>2871.3579435483798</v>
+        <v>2.87135794354838</v>
       </c>
       <c r="Y73">
-        <v>943.76971632342202</v>
+        <v>0.94376971632342199</v>
       </c>
       <c r="Z73" s="4"/>
       <c r="AA73" s="4"/>
@@ -9438,76 +9438,76 @@
         <v>0.73958333333333304</v>
       </c>
       <c r="B74">
-        <v>13363.0440253086</v>
+        <v>13.3630440253086</v>
       </c>
       <c r="C74">
-        <v>4392.2201679243299</v>
+        <v>4.3922201679243296</v>
       </c>
       <c r="D74">
-        <v>19877.8657065972</v>
+        <v>19.877865706597198</v>
       </c>
       <c r="E74">
-        <v>6533.5385026385102</v>
+        <v>6.5335385026385104</v>
       </c>
       <c r="F74">
-        <v>2845.8163348067101</v>
+        <v>2.84581633480671</v>
       </c>
       <c r="G74">
-        <v>935.37459550933499</v>
+        <v>0.93537459550933499</v>
       </c>
       <c r="H74">
-        <v>9035.1983967935794</v>
+        <v>9.0351983967935894</v>
       </c>
       <c r="I74">
-        <v>2969.7261001635902</v>
+        <v>2.96972610016359</v>
       </c>
       <c r="J74">
-        <v>4020.42965931863</v>
+        <v>4.0204296593186299</v>
       </c>
       <c r="K74">
-        <v>1321.4513250077</v>
+        <v>1.3214513250077</v>
       </c>
       <c r="L74">
-        <v>14462.2118236472</v>
+        <v>14.4622118236472</v>
       </c>
       <c r="M74">
-        <v>4753.4991521626798</v>
+        <v>4.7534991521626804</v>
       </c>
       <c r="N74">
-        <v>20355.265971943802</v>
+        <v>20.355265971943801</v>
       </c>
       <c r="O74">
-        <v>6690.4523816661303</v>
+        <v>6.6904523816661303</v>
       </c>
       <c r="P74">
-        <v>11969.3239812959</v>
+        <v>11.969323981295901</v>
       </c>
       <c r="Q74">
-        <v>3934.12654238815</v>
+        <v>3.93412654238815</v>
       </c>
       <c r="R74">
-        <v>1240.5026129032201</v>
+        <v>1.2405026129032199</v>
       </c>
       <c r="S74">
-        <v>407.73349129413799</v>
+        <v>0.407733491294138</v>
       </c>
       <c r="T74">
-        <v>8253.2667735470895</v>
+        <v>8.2532667735470895</v>
       </c>
       <c r="U74">
-        <v>2712.7176042657602</v>
+        <v>2.7127176042657601</v>
       </c>
       <c r="V74">
-        <v>3029.2320967741898</v>
+        <v>3.0292320967741899</v>
       </c>
       <c r="W74">
-        <v>995.66044110731696</v>
+        <v>0.995660441107317</v>
       </c>
       <c r="X74">
-        <v>3454.85094758064</v>
+        <v>3.4548509475806402</v>
       </c>
       <c r="Y74">
-        <v>1135.55459223189</v>
+        <v>1.1355545922318899</v>
       </c>
       <c r="Z74" s="4"/>
       <c r="AA74" s="4"/>
@@ -9562,76 +9562,76 @@
         <v>0.75</v>
       </c>
       <c r="B75">
-        <v>13982.2984329627</v>
+        <v>13.9822984329627</v>
       </c>
       <c r="C75">
-        <v>4595.7592487821603</v>
+        <v>4.5957592487821604</v>
       </c>
       <c r="D75">
-        <v>20629.089892021999</v>
+        <v>20.629089892022002</v>
       </c>
       <c r="E75">
-        <v>6780.4539518135898</v>
+        <v>6.7804539518135902</v>
       </c>
       <c r="F75">
-        <v>3373.9529402757098</v>
+        <v>3.3739529402757098</v>
       </c>
       <c r="G75">
-        <v>1108.9647030901101</v>
+        <v>1.10896470309011</v>
       </c>
       <c r="H75">
-        <v>9341.9905811623194</v>
+        <v>9.3419905811623192</v>
       </c>
       <c r="I75">
-        <v>3070.5638147587001</v>
+        <v>3.0705638147587</v>
       </c>
       <c r="J75">
-        <v>4156.9442484969904</v>
+        <v>4.1569442484969903</v>
       </c>
       <c r="K75">
-        <v>1366.3215005956499</v>
+        <v>1.3663215005956499</v>
       </c>
       <c r="L75">
-        <v>14953.2794639278</v>
+        <v>14.953279463927799</v>
       </c>
       <c r="M75">
-        <v>4914.9052800905902</v>
+        <v>4.9149052800905899</v>
       </c>
       <c r="N75">
-        <v>21046.4335851703</v>
+        <v>21.046433585170298</v>
       </c>
       <c r="O75">
-        <v>6917.6281901480797</v>
+        <v>6.9176281901480801</v>
       </c>
       <c r="P75">
-        <v>12375.745056780201</v>
+        <v>12.3757450567802</v>
       </c>
       <c r="Q75">
-        <v>4067.7106899095402</v>
+        <v>4.0677106899095401</v>
       </c>
       <c r="R75">
-        <v>1560.1903548386999</v>
+        <v>1.5601903548386999</v>
       </c>
       <c r="S75">
-        <v>512.80977068885397</v>
+        <v>0.51280977068885403</v>
       </c>
       <c r="T75">
-        <v>8533.50829458917</v>
+        <v>8.5335082945891791</v>
       </c>
       <c r="U75">
-        <v>2804.8285378434498</v>
+        <v>2.8048285378434499</v>
       </c>
       <c r="V75">
-        <v>3809.8901612903201</v>
+        <v>3.80989016129032</v>
       </c>
       <c r="W75">
-        <v>1252.25033849346</v>
+        <v>1.25225033849346</v>
       </c>
       <c r="X75">
-        <v>4345.1944959677403</v>
+        <v>4.34519449596774</v>
       </c>
       <c r="Y75">
-        <v>1428.19636473527</v>
+        <v>1.42819636473527</v>
       </c>
       <c r="Z75" s="4"/>
       <c r="AA75" s="4"/>
@@ -9686,76 +9686,76 @@
         <v>0.76041666666666696</v>
       </c>
       <c r="B76">
-        <v>14688.0307773934</v>
+        <v>14.688030777393401</v>
       </c>
       <c r="C76">
-        <v>4827.7222529071796</v>
+        <v>4.8277222529071802</v>
       </c>
       <c r="D76">
-        <v>21426.985321865799</v>
+        <v>21.4269853218658</v>
       </c>
       <c r="E76">
-        <v>7042.7094971981096</v>
+        <v>7.0427094971981097</v>
       </c>
       <c r="F76">
-        <v>3984.2951863808198</v>
+        <v>3.98429518638082</v>
       </c>
       <c r="G76">
-        <v>1309.57449810403</v>
+        <v>1.30957449810403</v>
       </c>
       <c r="H76">
-        <v>9689.2388777555097</v>
+        <v>9.6892388777555105</v>
       </c>
       <c r="I76">
-        <v>3184.6988103993199</v>
+        <v>3.1846988103993201</v>
       </c>
       <c r="J76">
-        <v>4311.4607615230398</v>
+        <v>4.3114607615230396</v>
       </c>
       <c r="K76">
-        <v>1417.1086224149799</v>
+        <v>1.41710862241498</v>
       </c>
       <c r="L76">
-        <v>15509.1032765531</v>
+        <v>15.5091032765531</v>
       </c>
       <c r="M76">
-        <v>5097.5957325804302</v>
+        <v>5.0975957325804302</v>
       </c>
       <c r="N76">
-        <v>21828.7441803607</v>
+        <v>21.828744180360701</v>
       </c>
       <c r="O76">
-        <v>7174.7612481001797</v>
+        <v>7.1747612481001797</v>
       </c>
       <c r="P76">
-        <v>12835.7601202404</v>
+        <v>12.835760120240399</v>
       </c>
       <c r="Q76">
-        <v>4218.9103294117704</v>
+        <v>4.21891032941177</v>
       </c>
       <c r="R76">
-        <v>1930.11474193548</v>
+        <v>1.93011474193548</v>
       </c>
       <c r="S76">
-        <v>634.39803684559695</v>
+        <v>0.63439803684559704</v>
       </c>
       <c r="T76">
-        <v>8850.7047414829594</v>
+        <v>8.8507047414829607</v>
       </c>
       <c r="U76">
-        <v>2909.0859681566399</v>
+        <v>2.9090859681566399</v>
       </c>
       <c r="V76">
-        <v>4713.2230645161198</v>
+        <v>4.7132230645161197</v>
       </c>
       <c r="W76">
-        <v>1549.16150546886</v>
+        <v>1.5491615054688599</v>
       </c>
       <c r="X76">
-        <v>5375.44917338709</v>
+        <v>5.3754491733870902</v>
       </c>
       <c r="Y76">
-        <v>1766.8247014891899</v>
+        <v>1.76682470148919</v>
       </c>
       <c r="Z76" s="4"/>
       <c r="AA76" s="4"/>
@@ -9810,76 +9810,76 @@
         <v>0.77083333333333304</v>
       </c>
       <c r="B77">
-        <v>15412.4376172021</v>
+        <v>15.4124376172021</v>
       </c>
       <c r="C77">
-        <v>5065.8232668351302</v>
+        <v>5.06582326683513</v>
       </c>
       <c r="D77">
-        <v>22227.607255931602</v>
+        <v>22.227607255931598</v>
       </c>
       <c r="E77">
-        <v>7305.8612011831101</v>
+        <v>7.3058612011831103</v>
       </c>
       <c r="F77">
-        <v>4559.7592712441001</v>
+        <v>4.5597592712440997</v>
       </c>
       <c r="G77">
-        <v>1498.72039589989</v>
+        <v>1.49872039589989</v>
       </c>
       <c r="H77">
-        <v>10060.0865731462</v>
+        <v>10.060086573146201</v>
       </c>
       <c r="I77">
-        <v>3306.5905533164801</v>
+        <v>3.3065905533164801</v>
       </c>
       <c r="J77">
-        <v>4476.47839679358</v>
+        <v>4.4764783967935804</v>
       </c>
       <c r="K77">
-        <v>1471.3472962026101</v>
+        <v>1.47134729620261</v>
       </c>
       <c r="L77">
-        <v>16102.701523046</v>
+        <v>16.102701523046001</v>
       </c>
       <c r="M77">
-        <v>5292.7020410647201</v>
+        <v>5.2927020410647199</v>
       </c>
       <c r="N77">
-        <v>22664.22151503</v>
+        <v>22.66422151503</v>
       </c>
       <c r="O77">
-        <v>7449.3693682431904</v>
+        <v>7.4493693682431896</v>
       </c>
       <c r="P77">
-        <v>13327.038343353301</v>
+        <v>13.3270383433533</v>
       </c>
       <c r="Q77">
-        <v>4380.3856725694995</v>
+        <v>4.3803856725695001</v>
       </c>
       <c r="R77">
-        <v>2276.0625483870899</v>
+        <v>2.27606254838709</v>
       </c>
       <c r="S77">
-        <v>748.10558204773599</v>
+        <v>0.74810558204773503</v>
       </c>
       <c r="T77">
-        <v>9189.4582284569096</v>
+        <v>9.1894582284569104</v>
       </c>
       <c r="U77">
-        <v>3020.4288548989002</v>
+        <v>3.0204288548989</v>
       </c>
       <c r="V77">
-        <v>5558.0066129032202</v>
+        <v>5.5580066129032204</v>
       </c>
       <c r="W77">
-        <v>1826.8284301403</v>
+        <v>1.8268284301402999</v>
       </c>
       <c r="X77">
-        <v>6338.92808467741</v>
+        <v>6.3389280846774101</v>
       </c>
       <c r="Y77">
-        <v>2083.5049053053599</v>
+        <v>2.08350490530536</v>
       </c>
       <c r="Z77" s="4"/>
       <c r="AA77" s="4"/>
@@ -9934,76 +9934,76 @@
         <v>0.78125</v>
       </c>
       <c r="B78">
-        <v>16090.7236992695</v>
+        <v>16.0907236992695</v>
       </c>
       <c r="C78">
-        <v>5288.7651207747203</v>
+        <v>5.2887651207747197</v>
       </c>
       <c r="D78">
-        <v>22990.081482088</v>
+        <v>22.990081482088002</v>
       </c>
       <c r="E78">
-        <v>7556.4743599292397</v>
+        <v>7.5564743599292399</v>
       </c>
       <c r="F78">
-        <v>4979.16627836317</v>
+        <v>4.9791662783631701</v>
       </c>
       <c r="G78">
-        <v>1636.57281274057</v>
+        <v>1.6365728127405701</v>
       </c>
       <c r="H78">
-        <v>10441.048296593101</v>
+        <v>10.441048296593101</v>
       </c>
       <c r="I78">
-        <v>3431.8066164950201</v>
+        <v>3.4318066164950198</v>
       </c>
       <c r="J78">
-        <v>4645.9965130260498</v>
+        <v>4.6459965130260503</v>
       </c>
       <c r="K78">
-        <v>1527.0652065480799</v>
+        <v>1.5270652065480801</v>
       </c>
       <c r="L78">
-        <v>16712.488812625201</v>
+        <v>16.7124888126252</v>
       </c>
       <c r="M78">
-        <v>5493.1294306894897</v>
+        <v>5.49312943068949</v>
       </c>
       <c r="N78">
-        <v>23522.484595190301</v>
+        <v>23.522484595190299</v>
       </c>
       <c r="O78">
-        <v>7731.4668007537402</v>
+        <v>7.7314668007537399</v>
       </c>
       <c r="P78">
-        <v>13831.7150634602</v>
+        <v>13.8317150634602</v>
       </c>
       <c r="Q78">
-        <v>4546.2648887224304</v>
+        <v>4.5462648887224297</v>
       </c>
       <c r="R78">
-        <v>2520.96619354838</v>
+        <v>2.52096619354838</v>
       </c>
       <c r="S78">
-        <v>828.60151751261606</v>
+        <v>0.82860151751261601</v>
       </c>
       <c r="T78">
-        <v>9537.4504468937794</v>
+        <v>9.5374504468937893</v>
       </c>
       <c r="U78">
-        <v>3134.8083658250298</v>
+        <v>3.1348083658250299</v>
       </c>
       <c r="V78">
-        <v>6156.0464516128995</v>
+        <v>6.1560464516128999</v>
       </c>
       <c r="W78">
-        <v>2023.3946193879001</v>
+        <v>2.0233946193879002</v>
       </c>
       <c r="X78">
-        <v>7020.9948387096701</v>
+        <v>7.0209948387096697</v>
       </c>
       <c r="Y78">
-        <v>2307.6894060267</v>
+        <v>2.3076894060267001</v>
       </c>
       <c r="Z78" s="4"/>
       <c r="AA78" s="4"/>
@@ -10058,76 +10058,76 @@
         <v>0.79166666666666696</v>
       </c>
       <c r="B79">
-        <v>16656.558076604801</v>
+        <v>16.656558076604799</v>
       </c>
       <c r="C79">
-        <v>5474.74588676862</v>
+        <v>5.4747458867686198</v>
       </c>
       <c r="D79">
-        <v>23670.5779347522</v>
+        <v>23.670577934752199</v>
       </c>
       <c r="E79">
-        <v>7780.1427275505903</v>
+        <v>7.7801427275505901</v>
       </c>
       <c r="F79">
-        <v>5153.1471915605398</v>
+        <v>5.1531471915605396</v>
       </c>
       <c r="G79">
-        <v>1693.7575735130399</v>
+        <v>1.6937575735130399</v>
       </c>
       <c r="H79">
-        <v>10808.524649298501</v>
+        <v>10.8085246492985</v>
       </c>
       <c r="I79">
-        <v>3552.59025265839</v>
+        <v>3.5525902526583901</v>
       </c>
       <c r="J79">
-        <v>4809.5139879759499</v>
+        <v>4.8095139879759499</v>
       </c>
       <c r="K79">
-        <v>1580.8108014831</v>
+        <v>1.5808108014830999</v>
       </c>
       <c r="L79">
-        <v>17300.690711422802</v>
+        <v>17.300690711422799</v>
       </c>
       <c r="M79">
-        <v>5686.46204546028</v>
+        <v>5.6864620454602797</v>
       </c>
       <c r="N79">
-        <v>24350.366681362699</v>
+        <v>24.350366681362701</v>
       </c>
       <c r="O79">
-        <v>8003.5784834409096</v>
+        <v>8.0035784834409096</v>
       </c>
       <c r="P79">
-        <v>14318.5271209084</v>
+        <v>14.318527120908399</v>
       </c>
       <c r="Q79">
-        <v>4706.27227421508</v>
+        <v>4.7062722742150802</v>
       </c>
       <c r="R79">
-        <v>2608.88032258064</v>
+        <v>2.6088803225806401</v>
       </c>
       <c r="S79">
-        <v>857.49749434616297</v>
+        <v>0.85749749434616296</v>
       </c>
       <c r="T79">
-        <v>9873.1243567134206</v>
+        <v>9.8731243567134204</v>
       </c>
       <c r="U79">
-        <v>3245.1390445059901</v>
+        <v>3.24513904450599</v>
       </c>
       <c r="V79">
-        <v>6370.7274193548301</v>
+        <v>6.3707274193548296</v>
       </c>
       <c r="W79">
-        <v>2093.9568411690898</v>
+        <v>2.0939568411690899</v>
       </c>
       <c r="X79">
-        <v>7265.8393145161199</v>
+        <v>7.2658393145161204</v>
       </c>
       <c r="Y79">
-        <v>2388.16589346513</v>
+        <v>2.3881658934651302</v>
       </c>
       <c r="Z79" s="4"/>
       <c r="AA79" s="4"/>
@@ -10182,76 +10182,76 @@
         <v>0.80208333333333304</v>
       </c>
       <c r="B80">
-        <v>17083.492420389099</v>
+        <v>17.083492420389099</v>
       </c>
       <c r="C80">
-        <v>5615.0724195254998</v>
+        <v>5.6150724195255002</v>
       </c>
       <c r="D80">
-        <v>24235.377751406599</v>
+        <v>24.235377751406599</v>
       </c>
       <c r="E80">
-        <v>7965.7834498928196</v>
+        <v>7.9657834498928199</v>
       </c>
       <c r="F80">
-        <v>5108.2505689604995</v>
+        <v>5.1082505689605</v>
       </c>
       <c r="G80">
-        <v>1679.0007672882</v>
+        <v>1.6790007672881999</v>
       </c>
       <c r="H80">
-        <v>11135.544889779499</v>
+        <v>11.135544889779499</v>
       </c>
       <c r="I80">
-        <v>3660.0766077762501</v>
+        <v>3.6600766077762499</v>
       </c>
       <c r="J80">
-        <v>4955.0295390781503</v>
+        <v>4.9550295390781498</v>
       </c>
       <c r="K80">
-        <v>1628.6394501867301</v>
+        <v>1.6286394501867301</v>
       </c>
       <c r="L80">
-        <v>17824.136437875699</v>
+        <v>17.824136437875701</v>
       </c>
       <c r="M80">
-        <v>5858.5103356691598</v>
+        <v>5.8585103356691599</v>
       </c>
       <c r="N80">
-        <v>25087.105785571101</v>
+        <v>25.087105785571101</v>
       </c>
       <c r="O80">
-        <v>8245.7329166579293</v>
+        <v>8.2457329166579303</v>
       </c>
       <c r="P80">
-        <v>14751.7451903807</v>
+        <v>14.751745190380699</v>
       </c>
       <c r="Q80">
-        <v>4848.6641677268899</v>
+        <v>4.8486641677268896</v>
       </c>
       <c r="R80">
-        <v>2558.6436774193498</v>
+        <v>2.5586436774193499</v>
       </c>
       <c r="S80">
-        <v>840.98550758413603</v>
+        <v>0.84098550758413604</v>
       </c>
       <c r="T80">
-        <v>10171.8433406813</v>
+        <v>10.171843340681299</v>
       </c>
       <c r="U80">
-        <v>3343.3232264514299</v>
+        <v>3.3433232264514299</v>
       </c>
       <c r="V80">
-        <v>6248.0525806451597</v>
+        <v>6.2480525806451599</v>
       </c>
       <c r="W80">
-        <v>2053.63557157984</v>
+        <v>2.0536355715798398</v>
       </c>
       <c r="X80">
-        <v>7125.92818548387</v>
+        <v>7.1259281854838701</v>
       </c>
       <c r="Y80">
-        <v>2342.1793292145999</v>
+        <v>2.3421793292145998</v>
       </c>
       <c r="Z80" s="4"/>
       <c r="AA80" s="4"/>
@@ -10306,76 +10306,76 @@
         <v>0.8125</v>
       </c>
       <c r="B81">
-        <v>17332.420282985298</v>
+        <v>17.3324202829853</v>
       </c>
       <c r="C81">
-        <v>5696.8910512970097</v>
+        <v>5.6968910512970004</v>
       </c>
       <c r="D81">
-        <v>24630.8237184256</v>
+        <v>24.630823718425599</v>
       </c>
       <c r="E81">
-        <v>8095.7602537090597</v>
+        <v>8.0957602537090594</v>
       </c>
       <c r="F81">
-        <v>4897.7129006803898</v>
+        <v>4.8977129006803901</v>
       </c>
       <c r="G81">
-        <v>1609.8003821831001</v>
+        <v>1.6098003821831</v>
       </c>
       <c r="H81">
-        <v>11378.2815631262</v>
+        <v>11.378281563126199</v>
       </c>
       <c r="I81">
-        <v>3739.8602940493001</v>
+        <v>3.7398602940493002</v>
       </c>
       <c r="J81">
-        <v>5063.04108216432</v>
+        <v>5.0630410821643199</v>
       </c>
       <c r="K81">
-        <v>1664.1411275749999</v>
+        <v>1.664141127575</v>
       </c>
       <c r="L81">
-        <v>18212.673471943799</v>
+        <v>18.212673471943798</v>
       </c>
       <c r="M81">
-        <v>5986.2162830406896</v>
+        <v>5.9862162830406902</v>
       </c>
       <c r="N81">
-        <v>25633.963677354699</v>
+        <v>25.6339636773547</v>
       </c>
       <c r="O81">
-        <v>8425.4764134788093</v>
+        <v>8.42547641347881</v>
       </c>
       <c r="P81">
-        <v>15073.309118236401</v>
+        <v>15.0733091182364</v>
       </c>
       <c r="Q81">
-        <v>4954.3571196119501</v>
+        <v>4.9543571196119496</v>
       </c>
       <c r="R81">
-        <v>2407.36287096774</v>
+        <v>2.4073628709677402</v>
       </c>
       <c r="S81">
-        <v>791.26191108485102</v>
+        <v>0.791261911084851</v>
       </c>
       <c r="T81">
-        <v>10393.5728957915</v>
+        <v>10.3935728957915</v>
       </c>
       <c r="U81">
-        <v>3416.2022068645401</v>
+        <v>3.4162022068645399</v>
       </c>
       <c r="V81">
-        <v>5878.63403225806</v>
+        <v>5.8786340322580601</v>
       </c>
       <c r="W81">
-        <v>1932.2135665667499</v>
+        <v>1.9322135665667499</v>
       </c>
       <c r="X81">
-        <v>6704.6048991935404</v>
+        <v>6.7046048991935399</v>
       </c>
       <c r="Y81">
-        <v>2203.6970618692499</v>
+        <v>2.2036970618692502</v>
       </c>
       <c r="Z81" s="4"/>
       <c r="AA81" s="4"/>
@@ -10430,76 +10430,76 @@
         <v>0.82291666666666696</v>
       </c>
       <c r="B82">
-        <v>17379.727442885702</v>
+        <v>17.379727442885699</v>
       </c>
       <c r="C82">
-        <v>5712.4401628174401</v>
+        <v>5.7124401628174404</v>
       </c>
       <c r="D82">
-        <v>24820.954574735199</v>
+        <v>24.8209545747352</v>
       </c>
       <c r="E82">
-        <v>8158.2532440820696</v>
+        <v>8.1582532440820703</v>
       </c>
       <c r="F82">
-        <v>4579.3474498997903</v>
+        <v>4.5793474498997897</v>
       </c>
       <c r="G82">
-        <v>1505.15871887342</v>
+        <v>1.5051587188734199</v>
       </c>
       <c r="H82">
-        <v>11503.0212424849</v>
+        <v>11.5030212424849</v>
       </c>
       <c r="I82">
-        <v>3780.86024393962</v>
+        <v>3.7808602439396202</v>
       </c>
       <c r="J82">
-        <v>5118.5470140280504</v>
+        <v>5.1185470140280502</v>
       </c>
       <c r="K82">
-        <v>1682.38504512175</v>
+        <v>1.6823850451217499</v>
       </c>
       <c r="L82">
-        <v>18412.3383366733</v>
+        <v>18.412338336673301</v>
       </c>
       <c r="M82">
-        <v>6051.8429504399501</v>
+        <v>6.0518429504399496</v>
       </c>
       <c r="N82">
-        <v>25914.9878717434</v>
+        <v>25.914987871743399</v>
       </c>
       <c r="O82">
-        <v>8517.8445993451005</v>
+        <v>8.5178445993451</v>
       </c>
       <c r="P82">
-        <v>15238.5572478289</v>
+        <v>15.238557247828901</v>
       </c>
       <c r="Q82">
-        <v>5008.6715532195503</v>
+        <v>5.0086715532195498</v>
       </c>
       <c r="R82">
-        <v>2194.4279999999999</v>
+        <v>2.1944279999999998</v>
       </c>
       <c r="S82">
-        <v>721.27360355944199</v>
+        <v>0.72127360355944203</v>
       </c>
       <c r="T82">
-        <v>10507.517250501</v>
+        <v>10.507517250500999</v>
       </c>
       <c r="U82">
-        <v>3453.6539051323898</v>
+        <v>3.45365390513239</v>
       </c>
       <c r="V82">
-        <v>5358.6599999999899</v>
+        <v>5.3586599999999898</v>
       </c>
       <c r="W82">
-        <v>1761.3063670577601</v>
+        <v>1.76130636705776</v>
       </c>
       <c r="X82">
-        <v>6111.5724999999902</v>
+        <v>6.1115724999999896</v>
       </c>
       <c r="Y82">
-        <v>2008.77673839824</v>
+        <v>2.00877673839824</v>
       </c>
       <c r="Z82" s="4"/>
       <c r="AA82" s="4"/>
@@ -10554,76 +10554,76 @@
         <v>0.83333333333333304</v>
       </c>
       <c r="B83">
-        <v>17212.526259551301</v>
+        <v>17.2125262595513</v>
       </c>
       <c r="C83">
-        <v>5657.4837914883201</v>
+        <v>5.6574837914883203</v>
       </c>
       <c r="D83">
-        <v>24777.624278180901</v>
+        <v>24.777624278180902</v>
       </c>
       <c r="E83">
-        <v>8144.0112643319899</v>
+        <v>8.14401126433199</v>
       </c>
       <c r="F83">
-        <v>4203.1195351186198</v>
+        <v>4.2031195351186197</v>
       </c>
       <c r="G83">
-        <v>1381.49858336026</v>
+        <v>1.38149858336026</v>
       </c>
       <c r="H83">
-        <v>11486.1645290581</v>
+        <v>11.486164529058099</v>
       </c>
       <c r="I83">
-        <v>3775.3197101706601</v>
+        <v>3.7753197101706601</v>
       </c>
       <c r="J83">
-        <v>5111.0462124248497</v>
+        <v>5.1110462124248501</v>
       </c>
       <c r="K83">
-        <v>1679.9196508586699</v>
+        <v>1.67991965085867</v>
       </c>
       <c r="L83">
-        <v>18385.3565981963</v>
+        <v>18.385356598196299</v>
       </c>
       <c r="M83">
-        <v>6042.9744818724803</v>
+        <v>6.0429744818724798</v>
       </c>
       <c r="N83">
-        <v>25877.011629258501</v>
+        <v>25.877011629258501</v>
       </c>
       <c r="O83">
-        <v>8505.3624120658696</v>
+        <v>8.5053624120658693</v>
       </c>
       <c r="P83">
-        <v>15216.2264195056</v>
+        <v>15.216226419505601</v>
       </c>
       <c r="Q83">
-        <v>5001.3317648942002</v>
+        <v>5.0013317648941999</v>
       </c>
       <c r="R83">
-        <v>1953.5204516128999</v>
+        <v>1.9535204516129001</v>
       </c>
       <c r="S83">
-        <v>642.091121586996</v>
+        <v>0.64209112158699599</v>
       </c>
       <c r="T83">
-        <v>10492.1193647294</v>
+        <v>10.492119364729399</v>
       </c>
       <c r="U83">
-        <v>3448.5928648259201</v>
+        <v>3.4485928648259199</v>
       </c>
       <c r="V83">
-        <v>4770.37838709677</v>
+        <v>4.7703783870967698</v>
       </c>
       <c r="W83">
-        <v>1567.9475515274901</v>
+        <v>1.5679475515274901</v>
       </c>
       <c r="X83">
-        <v>5440.6350403225797</v>
+        <v>5.4406350403225803</v>
       </c>
       <c r="Y83">
-        <v>1788.2502598331901</v>
+        <v>1.78825025983319</v>
       </c>
       <c r="Z83" s="4"/>
       <c r="AA83" s="4"/>
@@ -10678,76 +10678,76 @@
         <v>0.84375</v>
       </c>
       <c r="B84">
-        <v>16868.324287284198</v>
+        <v>16.868324287284199</v>
       </c>
       <c r="C84">
-        <v>5544.3500742328997</v>
+        <v>5.5443500742329004</v>
       </c>
       <c r="D84">
-        <v>24525.7757644665</v>
+        <v>24.525775764466498</v>
       </c>
       <c r="E84">
-        <v>8061.23266096114</v>
+        <v>8.0612326609611493</v>
       </c>
       <c r="F84">
-        <v>3807.12725256965</v>
+        <v>3.80712725256965</v>
       </c>
       <c r="G84">
-        <v>1251.3422143129201</v>
+        <v>1.25134221431292</v>
       </c>
       <c r="H84">
-        <v>11344.568136272501</v>
+        <v>11.3445681362725</v>
       </c>
       <c r="I84">
-        <v>3728.7792265113799</v>
+        <v>3.7287792265113802</v>
       </c>
       <c r="J84">
-        <v>5048.0394789579104</v>
+        <v>5.0480394789579099</v>
       </c>
       <c r="K84">
-        <v>1659.2103390488501</v>
+        <v>1.65921033904885</v>
       </c>
       <c r="L84">
-        <v>18158.709994989898</v>
+        <v>18.158709994989898</v>
       </c>
       <c r="M84">
-        <v>5968.4793459057601</v>
+        <v>5.9684793459057603</v>
       </c>
       <c r="N84">
-        <v>25558.0111923847</v>
+        <v>25.558011192384701</v>
       </c>
       <c r="O84">
-        <v>8400.5120389203494</v>
+        <v>8.4005120389203505</v>
       </c>
       <c r="P84">
-        <v>15028.647461589801</v>
+        <v>15.0286474615898</v>
       </c>
       <c r="Q84">
-        <v>4939.6775429612499</v>
+        <v>4.9396775429612498</v>
       </c>
       <c r="R84">
-        <v>1708.0459354838699</v>
+        <v>1.70804593548387</v>
       </c>
       <c r="S84">
-        <v>561.40754990891003</v>
+        <v>0.56140754990890995</v>
       </c>
       <c r="T84">
-        <v>10362.7771242484</v>
+        <v>10.362777124248399</v>
       </c>
       <c r="U84">
-        <v>3406.0801262516102</v>
+        <v>3.4060801262516098</v>
       </c>
       <c r="V84">
-        <v>4170.9445161290296</v>
+        <v>4.1709445161290297</v>
       </c>
       <c r="W84">
-        <v>1370.9231660345499</v>
+        <v>1.37092316603455</v>
       </c>
       <c r="X84">
-        <v>4756.9783870967703</v>
+        <v>4.7569783870967699</v>
       </c>
       <c r="Y84">
-        <v>1563.5431845180899</v>
+        <v>1.56354318451809</v>
       </c>
       <c r="Z84" s="4"/>
       <c r="AA84" s="4"/>
@@ -10802,76 +10802,76 @@
         <v>0.85416666666666696</v>
       </c>
       <c r="B85">
-        <v>16424.6380974852</v>
+        <v>16.4246380974852</v>
       </c>
       <c r="C85">
-        <v>5398.5174759586098</v>
+        <v>5.3985174759586201</v>
       </c>
       <c r="D85">
-        <v>24120.360578621501</v>
+        <v>24.120360578621501</v>
       </c>
       <c r="E85">
-        <v>7927.9791333757403</v>
+        <v>7.9279791333757297</v>
       </c>
       <c r="F85">
-        <v>3426.3369007369502</v>
+        <v>3.42633690073695</v>
       </c>
       <c r="G85">
-        <v>1126.1824782600399</v>
+        <v>1.12618247826004</v>
       </c>
       <c r="H85">
-        <v>11125.4308617234</v>
+        <v>11.1254308617234</v>
       </c>
       <c r="I85">
-        <v>3656.7522875148702</v>
+        <v>3.6567522875148799</v>
       </c>
       <c r="J85">
-        <v>4950.5290581162299</v>
+        <v>4.9505290581162296</v>
       </c>
       <c r="K85">
-        <v>1627.16021362889</v>
+        <v>1.6271602136288901</v>
       </c>
       <c r="L85">
-        <v>17807.947394789499</v>
+        <v>17.807947394789501</v>
       </c>
       <c r="M85">
-        <v>5853.1892545286801</v>
+        <v>5.8531892545286803</v>
       </c>
       <c r="N85">
-        <v>25064.3200400801</v>
+        <v>25.064320040080101</v>
       </c>
       <c r="O85">
-        <v>8238.2436042903901</v>
+        <v>8.2382436042903908</v>
       </c>
       <c r="P85">
-        <v>14738.3466933867</v>
+        <v>14.738346693386699</v>
       </c>
       <c r="Q85">
-        <v>4844.26029473168</v>
+        <v>4.8442602947316802</v>
       </c>
       <c r="R85">
-        <v>1477.4140645161201</v>
+        <v>1.47741406451612</v>
       </c>
       <c r="S85">
-        <v>485.60251977415101</v>
+        <v>0.48560251977415098</v>
       </c>
       <c r="T85">
-        <v>10162.604609218401</v>
+        <v>10.1626046092184</v>
       </c>
       <c r="U85">
-        <v>3340.2866022675498</v>
+        <v>3.3402866022675499</v>
       </c>
       <c r="V85">
-        <v>3607.7554838709598</v>
+        <v>3.6077554838709598</v>
       </c>
       <c r="W85">
-        <v>1185.8118829202599</v>
+        <v>1.18581188292026</v>
       </c>
       <c r="X85">
-        <v>4114.6591129032204</v>
+        <v>4.1146591129032197</v>
       </c>
       <c r="Y85">
-        <v>1352.42304864065</v>
+        <v>1.3524230486406501</v>
       </c>
       <c r="Z85" s="4"/>
       <c r="AA85" s="4"/>
@@ -10926,76 +10926,76 @@
         <v>0.86458333333333304</v>
       </c>
       <c r="B86">
-        <v>15935.092836285399</v>
+        <v>15.935092836285399</v>
       </c>
       <c r="C86">
-        <v>5237.6117298365998</v>
+        <v>5.2376117298366003</v>
       </c>
       <c r="D86">
-        <v>23599.2740382507</v>
+        <v>23.599274038250702</v>
       </c>
       <c r="E86">
-        <v>7756.7062701331997</v>
+        <v>7.7567062701331997</v>
       </c>
       <c r="F86">
-        <v>3093.1158754201902</v>
+        <v>3.0931158754201902</v>
       </c>
       <c r="G86">
-        <v>1016.65802372702</v>
+        <v>1.01665802372702</v>
       </c>
       <c r="H86">
-        <v>10859.0947895791</v>
+        <v>10.8590947895791</v>
       </c>
       <c r="I86">
-        <v>3569.2118539652802</v>
+        <v>3.56921185396528</v>
       </c>
       <c r="J86">
-        <v>4832.0163927855701</v>
+        <v>4.8320163927855697</v>
       </c>
       <c r="K86">
-        <v>1588.2069842723199</v>
+        <v>1.5882069842723201</v>
       </c>
       <c r="L86">
-        <v>17381.635926853702</v>
+        <v>17.381635926853701</v>
       </c>
       <c r="M86">
-        <v>5713.0674511626903</v>
+        <v>5.71306745116269</v>
       </c>
       <c r="N86">
-        <v>24464.295408817601</v>
+        <v>24.464295408817598</v>
       </c>
       <c r="O86">
-        <v>8041.0250452785904</v>
+        <v>8.0410250452785892</v>
       </c>
       <c r="P86">
-        <v>14385.5196058784</v>
+        <v>14.3855196058784</v>
       </c>
       <c r="Q86">
-        <v>4728.2916391911403</v>
+        <v>4.7282916391911396</v>
       </c>
       <c r="R86">
-        <v>1280.4635806451599</v>
+        <v>1.2804635806451601</v>
       </c>
       <c r="S86">
-        <v>420.86802621847801</v>
+        <v>0.42086802621847802</v>
       </c>
       <c r="T86">
-        <v>9919.3180140280492</v>
+        <v>9.9193180140280504</v>
       </c>
       <c r="U86">
-        <v>3260.3221654253898</v>
+        <v>3.26032216542538</v>
       </c>
       <c r="V86">
-        <v>3126.8143548387002</v>
+        <v>3.12681435483871</v>
       </c>
       <c r="W86">
-        <v>1027.73417828058</v>
+        <v>1.02773417828058</v>
       </c>
       <c r="X86">
-        <v>3566.1438911290302</v>
+        <v>3.56614389112903</v>
       </c>
       <c r="Y86">
-        <v>1172.13481379481</v>
+        <v>1.17213481379481</v>
       </c>
       <c r="Z86" s="4"/>
       <c r="AA86" s="4"/>
@@ -11050,76 +11050,76 @@
         <v>0.875</v>
       </c>
       <c r="B87">
-        <v>15465.401843687299</v>
+        <v>15.4654018436873</v>
       </c>
       <c r="C87">
-        <v>5083.2317662239202</v>
+        <v>5.0832317662239204</v>
       </c>
       <c r="D87">
-        <v>23012.505168838099</v>
+        <v>23.0125051688381</v>
       </c>
       <c r="E87">
-        <v>7563.8446693435399</v>
+        <v>7.5638446693435304</v>
       </c>
       <c r="F87">
-        <v>2835.53354709418</v>
+        <v>2.83553354709418</v>
       </c>
       <c r="G87">
-        <v>931.994806631301</v>
+        <v>0.93199480663130096</v>
       </c>
       <c r="H87">
-        <v>10586.016032064101</v>
+        <v>10.5860160320641</v>
       </c>
       <c r="I87">
-        <v>3479.4552069080901</v>
+        <v>3.47945520690809</v>
       </c>
       <c r="J87">
-        <v>4710.5034068136201</v>
+        <v>4.7105034068136202</v>
       </c>
       <c r="K87">
-        <v>1548.2675972105201</v>
+        <v>1.54826759721052</v>
       </c>
       <c r="L87">
-        <v>16944.531763527</v>
+        <v>16.944531763526999</v>
       </c>
       <c r="M87">
-        <v>5569.3982603697104</v>
+        <v>5.5693982603697103</v>
       </c>
       <c r="N87">
-        <v>23849.080280561098</v>
+        <v>23.8490802805611</v>
       </c>
       <c r="O87">
-        <v>7838.8136113551</v>
+        <v>7.8388136113550999</v>
       </c>
       <c r="P87">
-        <v>14023.7601870407</v>
+        <v>14.0237601870407</v>
       </c>
       <c r="Q87">
-        <v>4609.3870683204505</v>
+        <v>4.6093870683204496</v>
       </c>
       <c r="R87">
-        <v>1132.6079999999999</v>
+        <v>1.1326080000000001</v>
       </c>
       <c r="S87">
-        <v>372.27024699842099</v>
+        <v>0.37227024699842098</v>
       </c>
       <c r="T87">
-        <v>9669.8722645290509</v>
+        <v>9.6698722645290491</v>
       </c>
       <c r="U87">
-        <v>3178.3333124606402</v>
+        <v>3.1783333124606399</v>
       </c>
       <c r="V87">
-        <v>2765.76</v>
+        <v>2.7657600000000002</v>
       </c>
       <c r="W87">
-        <v>909.06135073949201</v>
+        <v>0.90906135073949201</v>
       </c>
       <c r="X87">
-        <v>3154.36</v>
+        <v>3.1543600000000001</v>
       </c>
       <c r="Y87">
-        <v>1036.7879940119899</v>
+        <v>1.03678799401199</v>
       </c>
       <c r="Z87" s="4"/>
       <c r="AA87" s="4"/>
@@ -11174,76 +11174,76 @@
         <v>0.88541666666666696</v>
       </c>
       <c r="B88">
-        <v>15053.872120660601</v>
+        <v>15.0538721206606</v>
       </c>
       <c r="C88">
-        <v>4947.96848745639</v>
+        <v>4.9479684874563903</v>
       </c>
       <c r="D88">
-        <v>22416.079777718001</v>
+        <v>22.416079777718</v>
       </c>
       <c r="E88">
-        <v>7367.8091233572604</v>
+        <v>7.3678091233572598</v>
       </c>
       <c r="F88">
-        <v>2646.0207188166601</v>
+        <v>2.64602071881666</v>
       </c>
       <c r="G88">
-        <v>869.70495224898696</v>
+        <v>0.86970495224898703</v>
       </c>
       <c r="H88">
-        <v>10336.5366733466</v>
+        <v>10.3365366733466</v>
       </c>
       <c r="I88">
-        <v>3397.4553071274599</v>
+        <v>3.3974553071274598</v>
       </c>
       <c r="J88">
-        <v>4599.4915430861702</v>
+        <v>4.5994915430861703</v>
       </c>
       <c r="K88">
-        <v>1511.77976211702</v>
+        <v>1.5117797621170199</v>
       </c>
       <c r="L88">
-        <v>16545.202034068101</v>
+        <v>16.545202034068101</v>
       </c>
       <c r="M88">
-        <v>5438.1449255711896</v>
+        <v>5.4381449255711898</v>
       </c>
       <c r="N88">
-        <v>23287.031891783499</v>
+        <v>23.287031891783499</v>
       </c>
       <c r="O88">
-        <v>7654.0772396225302</v>
+        <v>7.6540772396225298</v>
       </c>
       <c r="P88">
-        <v>13693.2639278557</v>
+        <v>13.6932639278557</v>
       </c>
       <c r="Q88">
-        <v>4500.75820110525</v>
+        <v>4.50075820110525</v>
       </c>
       <c r="R88">
-        <v>1026.9968709677401</v>
+        <v>1.0269968709677399</v>
       </c>
       <c r="S88">
-        <v>337.55754755552402</v>
+        <v>0.33755754755552397</v>
       </c>
       <c r="T88">
-        <v>9441.9835551102205</v>
+        <v>9.4419835551102196</v>
       </c>
       <c r="U88">
-        <v>3103.4299159249399</v>
+        <v>3.1034299159249401</v>
       </c>
       <c r="V88">
-        <v>2507.86403225806</v>
+        <v>2.5078640322580599</v>
       </c>
       <c r="W88">
-        <v>824.29504535299702</v>
+        <v>0.82429504535299702</v>
       </c>
       <c r="X88">
-        <v>2860.2286491935402</v>
+        <v>2.86022864919354</v>
       </c>
       <c r="Y88">
-        <v>940.11169416712903</v>
+        <v>0.94011169416712903</v>
       </c>
       <c r="Z88" s="4"/>
       <c r="AA88" s="4"/>
@@ -11298,76 +11298,76 @@
         <v>0.89583333333333304</v>
       </c>
       <c r="B89">
-        <v>14717.5870279591</v>
+        <v>14.7175870279591</v>
       </c>
       <c r="C89">
-        <v>4837.4369226767903</v>
+        <v>4.8374369226767904</v>
       </c>
       <c r="D89">
-        <v>21840.615654829799</v>
+        <v>21.840615654829801</v>
       </c>
       <c r="E89">
-        <v>7178.6632130632097</v>
+        <v>7.17866321306321</v>
       </c>
       <c r="F89">
-        <v>2509.4266964978301</v>
+        <v>2.50942669649783</v>
       </c>
       <c r="G89">
-        <v>824.80866825034104</v>
+        <v>0.82480866825034105</v>
       </c>
       <c r="H89">
-        <v>10127.5134268537</v>
+        <v>10.127513426853699</v>
       </c>
       <c r="I89">
-        <v>3328.7526883923301</v>
+        <v>3.32875268839233</v>
       </c>
       <c r="J89">
-        <v>4506.48160320641</v>
+        <v>4.5064816032064101</v>
       </c>
       <c r="K89">
-        <v>1481.2088732549</v>
+        <v>1.4812088732549</v>
       </c>
       <c r="L89">
-        <v>16210.6284769539</v>
+        <v>16.2106284769539</v>
       </c>
       <c r="M89">
-        <v>5328.1759153345902</v>
+        <v>5.3281759153345902</v>
       </c>
       <c r="N89">
-        <v>22816.1264849699</v>
+        <v>22.816126484969899</v>
       </c>
       <c r="O89">
-        <v>7499.2981173601002</v>
+        <v>7.4992981173600999</v>
       </c>
       <c r="P89">
-        <v>13416.361656646601</v>
+        <v>13.4163616566466</v>
       </c>
       <c r="Q89">
-        <v>4409.7448258709001</v>
+        <v>4.4097448258709004</v>
       </c>
       <c r="R89">
-        <v>952.78364516129</v>
+        <v>0.95278364516128999</v>
       </c>
       <c r="S89">
-        <v>313.16483983889401</v>
+        <v>0.31316483983889398</v>
       </c>
       <c r="T89">
-        <v>9251.0497715430793</v>
+        <v>9.2510497715430802</v>
       </c>
       <c r="U89">
-        <v>3040.6730161247601</v>
+        <v>3.0406730161247602</v>
       </c>
       <c r="V89">
-        <v>2326.6398387096701</v>
+        <v>2.3266398387096698</v>
       </c>
       <c r="W89">
-        <v>764.72953345978397</v>
+        <v>0.76472953345978401</v>
       </c>
       <c r="X89">
-        <v>2653.5417540322501</v>
+        <v>2.6535417540322501</v>
       </c>
       <c r="Y89">
-        <v>872.17699697884302</v>
+        <v>0.87217699697884299</v>
       </c>
       <c r="Z89" s="4"/>
       <c r="AA89" s="4"/>
@@ -11422,76 +11422,76 @@
         <v>0.90625</v>
       </c>
       <c r="B90">
-        <v>14493.151550423399</v>
+        <v>14.4931515504234</v>
       </c>
       <c r="C90">
-        <v>4763.6685485725702</v>
+        <v>4.7636685485725696</v>
       </c>
       <c r="D90">
-        <v>21345.5289981364</v>
+        <v>21.345528998136398</v>
       </c>
       <c r="E90">
-        <v>7015.9360983219403</v>
+        <v>7.0159360983219399</v>
       </c>
       <c r="F90">
-        <v>2413.7448840018701</v>
+        <v>2.4137448840018698</v>
       </c>
       <c r="G90">
-        <v>793.35957732821396</v>
+        <v>0.79335957732821405</v>
       </c>
       <c r="H90">
-        <v>9989.2883767535004</v>
+        <v>9.9892883767534997</v>
       </c>
       <c r="I90">
-        <v>3283.3203114868402</v>
+        <v>3.2833203114868401</v>
       </c>
       <c r="J90">
-        <v>4444.9750300601199</v>
+        <v>4.4449750300601201</v>
       </c>
       <c r="K90">
-        <v>1460.9926402977001</v>
+        <v>1.4609926402977</v>
       </c>
       <c r="L90">
-        <v>15989.378221442799</v>
+        <v>15.9893782214428</v>
       </c>
       <c r="M90">
-        <v>5255.4544730813504</v>
+        <v>5.2554544730813504</v>
       </c>
       <c r="N90">
-        <v>22504.721296593099</v>
+        <v>22.5047212965931</v>
       </c>
       <c r="O90">
-        <v>7396.9441816704302</v>
+        <v>7.3969441816704302</v>
       </c>
       <c r="P90">
-        <v>13233.2488643954</v>
+        <v>13.233248864395399</v>
       </c>
       <c r="Q90">
-        <v>4349.5585616030203</v>
+        <v>4.3495585616030201</v>
       </c>
       <c r="R90">
-        <v>900.26351612903204</v>
+        <v>0.90026351612903199</v>
       </c>
       <c r="S90">
-        <v>295.902308224048</v>
+        <v>0.29590230822404801</v>
       </c>
       <c r="T90">
-        <v>9124.7871082164293</v>
+        <v>9.1247871082164291</v>
       </c>
       <c r="U90">
-        <v>2999.1724856117398</v>
+        <v>2.9991724856117399</v>
       </c>
       <c r="V90">
-        <v>2198.3888709677399</v>
+        <v>2.1983888709677402</v>
       </c>
       <c r="W90">
-        <v>722.57547888920305</v>
+        <v>0.72257547888920304</v>
       </c>
       <c r="X90">
-        <v>2507.2710282257999</v>
+        <v>2.5072710282258002</v>
       </c>
       <c r="Y90">
-        <v>824.10013435328699</v>
+        <v>0.82410013435328699</v>
       </c>
       <c r="Z90" s="4"/>
       <c r="AA90" s="4"/>
@@ -11546,76 +11546,76 @@
         <v>0.91666666666666696</v>
       </c>
       <c r="B91">
-        <v>14374.0980267632</v>
+        <v>14.3740980267632</v>
       </c>
       <c r="C91">
-        <v>4724.53754767992</v>
+        <v>4.7245375476799198</v>
       </c>
       <c r="D91">
-        <v>20934.137588702801</v>
+        <v>20.9341375887028</v>
       </c>
       <c r="E91">
-        <v>6880.71828103399</v>
+        <v>6.8807182810339897</v>
       </c>
       <c r="F91">
-        <v>2342.1131643932999</v>
+        <v>2.3421131643933002</v>
       </c>
       <c r="G91">
-        <v>769.81536966624799</v>
+        <v>0.76981536966624797</v>
       </c>
       <c r="H91">
-        <v>9921.8615230460891</v>
+        <v>9.9218615230460898</v>
       </c>
       <c r="I91">
-        <v>3261.1581764109901</v>
+        <v>3.2611581764109898</v>
       </c>
       <c r="J91">
-        <v>4414.97182364729</v>
+        <v>4.4149718236472903</v>
       </c>
       <c r="K91">
-        <v>1451.1310632453999</v>
+        <v>1.4511310632454</v>
       </c>
       <c r="L91">
-        <v>15881.451267535</v>
+        <v>15.881451267535001</v>
       </c>
       <c r="M91">
-        <v>5219.9805988114804</v>
+        <v>5.21998059881148</v>
       </c>
       <c r="N91">
-        <v>22352.816326653301</v>
+        <v>22.352816326653301</v>
       </c>
       <c r="O91">
-        <v>7347.0154325535204</v>
+        <v>7.34701543255352</v>
       </c>
       <c r="P91">
-        <v>13143.9255511022</v>
+        <v>13.1439255511022</v>
       </c>
       <c r="Q91">
-        <v>4320.1994083016198</v>
+        <v>4.3201994083016197</v>
       </c>
       <c r="R91">
-        <v>858.58993548387105</v>
+        <v>0.85858993548387097</v>
       </c>
       <c r="S91">
-        <v>282.20486466009402</v>
+        <v>0.28220486466009398</v>
       </c>
       <c r="T91">
-        <v>9063.1955651302596</v>
+        <v>9.0631955651302594</v>
       </c>
       <c r="U91">
-        <v>2978.9283243858799</v>
+        <v>2.9789283243858802</v>
       </c>
       <c r="V91">
-        <v>2096.6245161290299</v>
+        <v>2.09662451612903</v>
       </c>
       <c r="W91">
-        <v>689.12715297993702</v>
+        <v>0.68912715297993699</v>
       </c>
       <c r="X91">
-        <v>2391.2083870967699</v>
+        <v>2.39120838709677</v>
       </c>
       <c r="Y91">
-        <v>785.95218900909504</v>
+        <v>0.78595218900909503</v>
       </c>
       <c r="Z91" s="4"/>
       <c r="AA91" s="4"/>
@@ -11670,76 +11670,76 @@
         <v>0.92708333333333304</v>
       </c>
       <c r="B92">
-        <v>14273.259955039101</v>
+        <v>14.2732599550391</v>
       </c>
       <c r="C92">
-        <v>4691.3936763073298</v>
+        <v>4.6913936763073298</v>
       </c>
       <c r="D92">
-        <v>20518.485594080601</v>
+        <v>20.518485594080602</v>
       </c>
       <c r="E92">
-        <v>6744.1000771157896</v>
+        <v>6.7441000771157897</v>
       </c>
       <c r="F92">
-        <v>2282.1580565566601</v>
+        <v>2.2821580565566602</v>
       </c>
       <c r="G92">
-        <v>750.10907869605899</v>
+        <v>0.75010907869605903</v>
       </c>
       <c r="H92">
-        <v>9864.54869739479</v>
+        <v>9.86454869739479</v>
       </c>
       <c r="I92">
-        <v>3242.3203615965199</v>
+        <v>3.2423203615965202</v>
       </c>
       <c r="J92">
-        <v>4389.4690981963904</v>
+        <v>4.3894690981963898</v>
       </c>
       <c r="K92">
-        <v>1442.74872275095</v>
+        <v>1.4427487227509499</v>
       </c>
       <c r="L92">
-        <v>15789.713356713401</v>
+        <v>15.789713356713399</v>
       </c>
       <c r="M92">
-        <v>5189.82780568209</v>
+        <v>5.1898278056820901</v>
       </c>
       <c r="N92">
-        <v>22223.697102204402</v>
+        <v>22.223697102204401</v>
       </c>
       <c r="O92">
-        <v>7304.5759958041499</v>
+        <v>7.3045759958041501</v>
       </c>
       <c r="P92">
-        <v>13068.000734802899</v>
+        <v>13.068000734802901</v>
       </c>
       <c r="Q92">
-        <v>4295.2441279954301</v>
+        <v>4.2952441279954297</v>
       </c>
       <c r="R92">
-        <v>823.76680645161298</v>
+        <v>0.82376680645161304</v>
       </c>
       <c r="S92">
-        <v>270.759055654598</v>
+        <v>0.27075905565459801</v>
       </c>
       <c r="T92">
-        <v>9010.8427535070095</v>
+        <v>9.0108427535070099</v>
       </c>
       <c r="U92">
-        <v>2961.7207873438902</v>
+        <v>2.9617207873438902</v>
       </c>
       <c r="V92">
-        <v>2011.58854838709</v>
+        <v>2.0115885483870901</v>
       </c>
       <c r="W92">
-        <v>661.17718201466096</v>
+        <v>0.66117718201466102</v>
       </c>
       <c r="X92">
-        <v>2294.22453629032</v>
+        <v>2.29422453629032</v>
       </c>
       <c r="Y92">
-        <v>754.07513878997702</v>
+        <v>0.75407513878997601</v>
       </c>
       <c r="Z92" s="4"/>
       <c r="AA92" s="4"/>
@@ -11794,76 +11794,76 @@
         <v>0.9375</v>
       </c>
       <c r="B93">
-        <v>14066.129601267001</v>
+        <v>14.066129601267001</v>
       </c>
       <c r="C93">
-        <v>4623.3132213223798</v>
+        <v>4.6233132213223698</v>
       </c>
       <c r="D93">
-        <v>19971.2960746313</v>
+        <v>19.971296074631301</v>
       </c>
       <c r="E93">
-        <v>6564.2475795523596</v>
+        <v>6.5642475795523598</v>
       </c>
       <c r="F93">
-        <v>2219.65528266209</v>
+        <v>2.2196552826620901</v>
       </c>
       <c r="G93">
-        <v>729.56541038732803</v>
+        <v>0.72956541038732803</v>
       </c>
       <c r="H93">
-        <v>9729.6949899799602</v>
+        <v>9.7296949899799596</v>
       </c>
       <c r="I93">
-        <v>3197.9960914448302</v>
+        <v>3.1979960914448302</v>
       </c>
       <c r="J93">
-        <v>4329.4626853707396</v>
+        <v>4.3294626853707401</v>
       </c>
       <c r="K93">
-        <v>1423.0255686463599</v>
+        <v>1.42302556864636</v>
       </c>
       <c r="L93">
-        <v>15573.8594488977</v>
+        <v>15.5738594488977</v>
       </c>
       <c r="M93">
-        <v>5118.8800571423499</v>
+        <v>5.1188800571423503</v>
       </c>
       <c r="N93">
-        <v>21919.887162324601</v>
+        <v>21.919887162324599</v>
       </c>
       <c r="O93">
-        <v>7204.7184975703203</v>
+        <v>7.2047184975703198</v>
       </c>
       <c r="P93">
-        <v>12889.354108216399</v>
+        <v>12.8893541082164</v>
       </c>
       <c r="Q93">
-        <v>4236.5258213926199</v>
+        <v>4.23652582139262</v>
       </c>
       <c r="R93">
-        <v>792.36890322580598</v>
+        <v>0.792368903225806</v>
       </c>
       <c r="S93">
-        <v>260.439063928331</v>
+        <v>0.26043906392833099</v>
       </c>
       <c r="T93">
-        <v>8887.6596673346703</v>
+        <v>8.8876596673346704</v>
       </c>
       <c r="U93">
-        <v>2921.2324648921599</v>
+        <v>2.9212324648921602</v>
       </c>
       <c r="V93">
-        <v>1934.91677419354</v>
+        <v>1.93491677419354</v>
       </c>
       <c r="W93">
-        <v>635.976388521378</v>
+        <v>0.63597638852137806</v>
       </c>
       <c r="X93">
-        <v>2206.7800806451601</v>
+        <v>2.2067800806451601</v>
       </c>
       <c r="Y93">
-        <v>725.33353613339398</v>
+        <v>0.72533353613339402</v>
       </c>
       <c r="Z93" s="4"/>
       <c r="AA93" s="4"/>
@@ -11918,76 +11918,76 @@
         <v>0.94791666666666696</v>
       </c>
       <c r="B94">
-        <v>13627.8588282371</v>
+        <v>13.6278588282371</v>
       </c>
       <c r="C94">
-        <v>4479.2605844629798</v>
+        <v>4.4792605844629803</v>
       </c>
       <c r="D94">
-        <v>19160.505334811402</v>
+        <v>19.160505334811401</v>
       </c>
       <c r="E94">
-        <v>6297.7535507473403</v>
+        <v>6.2977535507473403</v>
       </c>
       <c r="F94">
-        <v>2139.4930850410401</v>
+        <v>2.1394930850410399</v>
       </c>
       <c r="G94">
-        <v>703.21737019308205</v>
+        <v>0.70321737019308195</v>
       </c>
       <c r="H94">
-        <v>9429.6454909819604</v>
+        <v>9.4296454909819598</v>
       </c>
       <c r="I94">
-        <v>3099.3745903572999</v>
+        <v>3.0993745903573</v>
       </c>
       <c r="J94">
-        <v>4195.9484168336603</v>
+        <v>4.1959484168336596</v>
       </c>
       <c r="K94">
-        <v>1379.14155076364</v>
+        <v>1.37914155076364</v>
       </c>
       <c r="L94">
-        <v>15093.584504008</v>
+        <v>15.093584504008</v>
       </c>
       <c r="M94">
-        <v>4961.0213166414296</v>
+        <v>4.9610213166414301</v>
       </c>
       <c r="N94">
-        <v>21243.9100460921</v>
+        <v>21.2439100460921</v>
       </c>
       <c r="O94">
-        <v>6982.5355640000698</v>
+        <v>6.9825355640000701</v>
       </c>
       <c r="P94">
-        <v>12491.865364061399</v>
+        <v>12.4918653640614</v>
       </c>
       <c r="Q94">
-        <v>4105.87758920137</v>
+        <v>4.1058775892013699</v>
       </c>
       <c r="R94">
-        <v>760.40012903225795</v>
+        <v>0.76040012903225795</v>
       </c>
       <c r="S94">
-        <v>249.93143598885899</v>
+        <v>0.249931435988859</v>
       </c>
       <c r="T94">
-        <v>8613.5773006012005</v>
+        <v>8.6135773006012002</v>
       </c>
       <c r="U94">
-        <v>2831.1459474370699</v>
+        <v>2.8311459474370699</v>
       </c>
       <c r="V94">
-        <v>1856.8509677419299</v>
+        <v>1.85685096774193</v>
       </c>
       <c r="W94">
-        <v>610.31739878276403</v>
+        <v>0.61031739878276403</v>
       </c>
       <c r="X94">
-        <v>2117.7457258064501</v>
+        <v>2.1177457258064498</v>
       </c>
       <c r="Y94">
-        <v>696.06935888305497</v>
+        <v>0.69606935888305499</v>
       </c>
       <c r="Z94" s="4"/>
       <c r="AA94" s="4"/>
@@ -12042,76 +12042,76 @@
         <v>0.95833333333333304</v>
       </c>
       <c r="B95">
-        <v>12877.6933545478</v>
+        <v>12.8776933545478</v>
       </c>
       <c r="C95">
-        <v>4232.6931170073303</v>
+        <v>4.2326931170073303</v>
       </c>
       <c r="D95">
-        <v>18005.8696070156</v>
+        <v>18.005869607015601</v>
       </c>
       <c r="E95">
-        <v>5918.2431397492201</v>
+        <v>5.9182431397492197</v>
       </c>
       <c r="F95">
-        <v>2034.0776663407401</v>
+        <v>2.0340776663407398</v>
       </c>
       <c r="G95">
-        <v>668.56899762551802</v>
+        <v>0.66856899762551802</v>
       </c>
       <c r="H95">
-        <v>8907.0873747495007</v>
+        <v>8.9070873747494996</v>
       </c>
       <c r="I95">
-        <v>2927.6180435194801</v>
+        <v>2.9276180435194799</v>
       </c>
       <c r="J95">
-        <v>3963.4235671342599</v>
+        <v>3.9634235671342601</v>
       </c>
       <c r="K95">
-        <v>1302.7143286083401</v>
+        <v>1.30271432860834</v>
       </c>
       <c r="L95">
-        <v>14257.1506112224</v>
+        <v>14.2571506112224</v>
       </c>
       <c r="M95">
-        <v>4686.0987910499298</v>
+        <v>4.6860987910499299</v>
       </c>
       <c r="N95">
-        <v>20066.6465290581</v>
+        <v>20.066646529058101</v>
       </c>
       <c r="O95">
-        <v>6595.5877583439997</v>
+        <v>6.5955877583440001</v>
       </c>
       <c r="P95">
-        <v>11799.609686038701</v>
+        <v>11.7996096860387</v>
       </c>
       <c r="Q95">
-        <v>3878.3441511154901</v>
+        <v>3.8783441511154901</v>
       </c>
       <c r="R95">
-        <v>726.71874193548399</v>
+        <v>0.72671874193548402</v>
       </c>
       <c r="S95">
-        <v>238.860899409773</v>
+        <v>0.23886089940977301</v>
       </c>
       <c r="T95">
-        <v>8136.24284168336</v>
+        <v>8.1362428416833694</v>
       </c>
       <c r="U95">
-        <v>2674.25369793662</v>
+        <v>2.6742536979366198</v>
       </c>
       <c r="V95">
-        <v>1774.60306451612</v>
+        <v>1.7746030645161199</v>
       </c>
       <c r="W95">
-        <v>583.28382030815203</v>
+        <v>0.58328382030815196</v>
       </c>
       <c r="X95">
-        <v>2023.9416733870901</v>
+        <v>2.0239416733870899</v>
       </c>
       <c r="Y95">
-        <v>665.23745785144797</v>
+        <v>0.66523745785144806</v>
       </c>
       <c r="Z95" s="4"/>
       <c r="AA95" s="4"/>
@@ -12166,76 +12166,76 @@
         <v>0.96875</v>
       </c>
       <c r="B96">
-        <v>11910.8584780528</v>
+        <v>11.9108584780528</v>
       </c>
       <c r="C96">
-        <v>3914.9098607708802</v>
+        <v>3.9149098607708801</v>
       </c>
       <c r="D96">
-        <v>16624.257806329901</v>
+        <v>16.624257806329901</v>
       </c>
       <c r="E96">
-        <v>5464.1293013363002</v>
+        <v>5.4641293013362997</v>
       </c>
       <c r="F96">
-        <v>1912.91715746008</v>
+        <v>1.9129171574600801</v>
       </c>
       <c r="G96">
-        <v>628.74546418106104</v>
+        <v>0.62874546418106103</v>
       </c>
       <c r="H96">
-        <v>8229.4474949899795</v>
+        <v>8.2294474949899801</v>
       </c>
       <c r="I96">
-        <v>2704.8885860072101</v>
+        <v>2.7048885860072098</v>
       </c>
       <c r="J96">
-        <v>3661.8913426853701</v>
+        <v>3.6618913426853701</v>
       </c>
       <c r="K96">
-        <v>1203.60547923276</v>
+        <v>1.20360547923276</v>
       </c>
       <c r="L96">
-        <v>13172.484724448799</v>
+        <v>13.1724847244488</v>
       </c>
       <c r="M96">
-        <v>4329.5863546377204</v>
+        <v>4.32958635463772</v>
       </c>
       <c r="N96">
-        <v>18540.001581162302</v>
+        <v>18.540001581162301</v>
       </c>
       <c r="O96">
-        <v>6093.8038297190396</v>
+        <v>6.0938038297190404</v>
       </c>
       <c r="P96">
-        <v>10901.9103874415</v>
+        <v>10.9019103874415</v>
       </c>
       <c r="Q96">
-        <v>3583.2846604363699</v>
+        <v>3.58328466043637</v>
       </c>
       <c r="R96">
-        <v>693.03735483870901</v>
+        <v>0.69303735483870899</v>
       </c>
       <c r="S96">
-        <v>227.790362830687</v>
+        <v>0.22779036283068699</v>
       </c>
       <c r="T96">
-        <v>7517.2478336673303</v>
+        <v>7.5172478336673301</v>
       </c>
       <c r="U96">
-        <v>2470.7998776166901</v>
+        <v>2.47079987761669</v>
       </c>
       <c r="V96">
-        <v>1692.35516129032</v>
+        <v>1.69235516129032</v>
       </c>
       <c r="W96">
-        <v>556.25024183354003</v>
+        <v>0.55625024183353999</v>
       </c>
       <c r="X96">
-        <v>1930.1376209677401</v>
+        <v>1.9301376209677401</v>
       </c>
       <c r="Y96">
-        <v>634.40555681984199</v>
+        <v>0.63440555681984201</v>
       </c>
       <c r="Z96" s="4"/>
       <c r="AA96" s="4"/>
@@ -12290,76 +12290,76 @@
         <v>0.97916666666666696</v>
       </c>
       <c r="B97">
-        <v>10852.2023359622</v>
+        <v>10.8522023359622</v>
       </c>
       <c r="C97">
-        <v>3566.9464140157102</v>
+        <v>3.5669464140157099</v>
       </c>
       <c r="D97">
-        <v>15166.4449945366</v>
+        <v>15.166444994536601</v>
       </c>
       <c r="E97">
-        <v>4984.9694017737202</v>
+        <v>4.9849694017737196</v>
       </c>
       <c r="F97">
-        <v>1791.1233160676099</v>
+        <v>1.7911233160676101</v>
       </c>
       <c r="G97">
-        <v>588.71376440668303</v>
+        <v>0.58871376440668299</v>
       </c>
       <c r="H97">
-        <v>7484.3807615230398</v>
+        <v>7.48438076152304</v>
       </c>
       <c r="I97">
-        <v>2459.9969934190999</v>
+        <v>2.4599969934191002</v>
       </c>
       <c r="J97">
-        <v>3330.3559118236399</v>
+        <v>3.3303559118236401</v>
       </c>
       <c r="K97">
-        <v>1094.6350528048899</v>
+        <v>1.09463505280489</v>
       </c>
       <c r="L97">
-        <v>11979.891883767499</v>
+        <v>11.9798918837675</v>
       </c>
       <c r="M97">
-        <v>3937.6000439556501</v>
+        <v>3.93760004395565</v>
       </c>
       <c r="N97">
-        <v>16861.451663326599</v>
+        <v>16.861451663326601</v>
       </c>
       <c r="O97">
-        <v>5542.0911519771698</v>
+        <v>5.5420911519771696</v>
       </c>
       <c r="P97">
-        <v>9914.8877755511003</v>
+        <v>9.9148877755510991</v>
       </c>
       <c r="Q97">
-        <v>3258.8660164558601</v>
+        <v>3.25886601645586</v>
       </c>
       <c r="R97">
-        <v>663.35206451612896</v>
+        <v>0.66335206451612905</v>
       </c>
       <c r="S97">
-        <v>218.03327974403501</v>
+        <v>0.218033279744035</v>
       </c>
       <c r="T97">
-        <v>6836.66128256513</v>
+        <v>6.8366612825651298</v>
       </c>
       <c r="U97">
-        <v>2247.1018960708898</v>
+        <v>2.2471018960708902</v>
       </c>
       <c r="V97">
-        <v>1619.8654838709599</v>
+        <v>1.6198654838709601</v>
       </c>
       <c r="W97">
-        <v>532.42403707625499</v>
+        <v>0.53242403707625496</v>
       </c>
       <c r="X97">
-        <v>1847.46286290322</v>
+        <v>1.8474628629032199</v>
       </c>
       <c r="Y97">
-        <v>607.23167794452695</v>
+        <v>0.60723167794452704</v>
       </c>
       <c r="Z97" s="4"/>
       <c r="AA97" s="4"/>
@@ -12414,76 +12414,76 @@
         <v>0.98958333333333304</v>
       </c>
       <c r="B98">
-        <v>9830.2620602171992</v>
+        <v>9.8302620602171995</v>
       </c>
       <c r="C98">
-        <v>3231.05088893622</v>
+        <v>3.2310508889362199</v>
       </c>
       <c r="D98">
-        <v>13792.7671044858</v>
+        <v>13.792767104485799</v>
       </c>
       <c r="E98">
-        <v>4533.4633136783896</v>
+        <v>4.5334633136783902</v>
       </c>
       <c r="F98">
-        <v>1681.48774488493</v>
+        <v>1.6814877448849299</v>
       </c>
       <c r="G98">
-        <v>552.67829479672798</v>
+        <v>0.55267829479672803</v>
       </c>
       <c r="H98">
-        <v>6762.9134268537</v>
+        <v>6.7629134268537001</v>
       </c>
       <c r="I98">
-        <v>2222.8621481075202</v>
+        <v>2.2228621481075299</v>
       </c>
       <c r="J98">
-        <v>3009.3216032064101</v>
+        <v>3.0093216032064101</v>
       </c>
       <c r="K98">
-        <v>989.11617834532103</v>
+        <v>0.98911617834532095</v>
       </c>
       <c r="L98">
-        <v>10825.073476953899</v>
+        <v>10.8250734769539</v>
       </c>
       <c r="M98">
-        <v>3558.0295892680401</v>
+        <v>3.55802958926804</v>
       </c>
       <c r="N98">
-        <v>15236.068484969899</v>
+        <v>15.2360684849699</v>
       </c>
       <c r="O98">
-        <v>5007.8535364262198</v>
+        <v>5.0078535364262198</v>
       </c>
       <c r="P98">
-        <v>8959.1283233132908</v>
+        <v>8.9591283233132906</v>
       </c>
       <c r="Q98">
-        <v>2944.7230761308301</v>
+        <v>2.9447230761308298</v>
       </c>
       <c r="R98">
-        <v>639.946354838709</v>
+        <v>0.63994635483870899</v>
       </c>
       <c r="S98">
-        <v>210.34019500263599</v>
+        <v>0.21034019500263601</v>
       </c>
       <c r="T98">
-        <v>6177.6317715430796</v>
+        <v>6.17763177154308</v>
       </c>
       <c r="U98">
-        <v>2030.48937095415</v>
+        <v>2.0304893709541498</v>
       </c>
       <c r="V98">
-        <v>1562.71016129032</v>
+        <v>1.56271016129032</v>
       </c>
       <c r="W98">
-        <v>513.63799101762595</v>
+        <v>0.51363799101762597</v>
       </c>
       <c r="X98">
-        <v>1782.27699596774</v>
+        <v>1.78227699596774</v>
       </c>
       <c r="Y98">
-        <v>585.80611960052897</v>
+        <v>0.58580611960052897</v>
       </c>
     </row>
   </sheetData>
@@ -12498,6 +12498,14 @@
     <protectedRange sqref="T3:W97" name="Plage1_13"/>
   </protectedRanges>
   <mergeCells count="20">
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:C1"/>
@@ -12510,14 +12518,6 @@
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="T1:U1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AH1:AI1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12852,6 +12852,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:C1"/>
@@ -12864,14 +12872,6 @@
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="T1:U1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AH1:AI1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
